--- a/fhf_cardiologie.xlsx
+++ b/fhf_cardiologie.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>benedicte.point@ch-laon.fr</t>
+          <t>moudo.megherbi@ch-laon.fr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>c.balluais@ch-compiegnenoyon.fr</t>
+          <t>e.deliancourt@ch-compiegnenoyon.fr</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">

--- a/fhf_cardiologie.xlsx
+++ b/fhf_cardiologie.xlsx
@@ -6220,12 +6220,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>M. Alexandru MISCHIE</t>
+          <t>M. Valentin KITINGE</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>alexandru.mischie@ch-chateauroux.fr</t>
+          <t>valentin.kitinge@ch-chateauroux.fr</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>

--- a/fhf_cardiologie.xlsx
+++ b/fhf_cardiologie.xlsx
@@ -1459,7 +1459,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>a.guiraud@ch-privas.fr</t>
+          <t>secretariat.drh@ch-privas.fr</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1664,12 +1664,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dr Youcef AFIFI</t>
+          <t>Dr Karim BEN BRAHIM</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>youcef.afifi@ch-carcassonne.fr</t>
+          <t>karim.benbrahim@ch-carcassonne.fr</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -4602,11 +4602,7 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>louisa.atmani@ch-eureseine.fr</t>
-        </is>
-      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -4641,11 +4637,7 @@
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>louisa.atmani@ch-eureseine.fr</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -7740,16 +7732,8 @@
           <t>Cardiologie</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Dr Fabrice PRUNIER</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>affaires-medicales@ch-saumur.fr</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
           <t>laurent.renaut@ch-saumur.fr</t>
@@ -10975,7 +10959,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Dr Majdi ABDENNADHER</t>
+          <t>Mme Christine LEONARD</t>
         </is>
       </c>
       <c r="G254" t="inlineStr"/>
@@ -11625,7 +11609,7 @@
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>cpicherel@hno.fr</t>
+          <t>direction-generale@hno.fr</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -18995,663 +18979,660 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId205"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G356" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D361" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G369" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D373" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G373" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G376" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G378" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G386" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G387" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G395" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G396" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D397" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D398" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G398" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D399" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G399" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D400" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G400" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D401" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D402" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D403" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G408" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G409" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G410" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D411" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G411" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D412" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G412" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D413" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G413" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D414" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D415" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G415" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D416" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G416" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D417" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D418" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D419" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D420" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D421" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D422" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D423" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D424" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D425" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D426" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G426" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D427" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G427" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D428" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D429" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D430" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G430" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D431" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G431" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D432" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G432" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D433" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D434" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G434" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D435" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G435" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D436" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G436" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D437" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G437" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D438" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D439" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G439" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D440" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G440" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D441" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G441" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D442" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G442" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G356" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D361" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G369" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D373" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G373" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G376" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G378" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G386" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G387" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G395" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G396" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D397" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D398" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G398" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D399" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G399" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D400" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G400" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D401" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D402" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D403" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G408" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G409" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G410" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D411" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G411" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D412" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G412" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D413" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G413" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D414" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D415" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G415" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D416" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G416" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D417" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D418" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D419" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D420" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D421" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D422" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D423" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D424" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D425" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D426" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G426" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D427" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G427" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D428" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D429" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D430" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G430" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D431" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G431" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D432" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G432" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D433" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D434" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G434" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D435" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G435" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D436" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G436" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D437" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G437" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D438" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D439" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G439" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D440" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G440" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D441" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G441" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D442" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G442" r:id="rId861"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fhf_cardiologie.xlsx
+++ b/fhf_cardiologie.xlsx
@@ -3445,12 +3445,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dr Alain BERENFELD</t>
+          <t>Dr Racine LY</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>a.berenfeld@chussel.fr</t>
+          <t>r.ly@ch-ussel.fr</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>cardio-neuro.cadre@ch-dole.fr</t>
+          <t>bettinger.christelle@ch-dole.fr</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7179,7 +7179,11 @@
           <t>Dr Simon SAAD</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>nolwenn.perpina@ch-cnp.fr</t>
+        </is>
+      </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
           <t>celine.reuze@ch-cnp.fr</t>
@@ -7338,7 +7342,7 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>sgrzesiak@ch-montargis.fr</t>
+          <t>jperret@ch-montargis.fr</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8000,12 +8004,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Pr Claude MARCUS</t>
+          <t>Mme Fabienne MENU</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>cmarcus@chu-reims.fr</t>
+          <t>fmenu@chu-reims.fr</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
@@ -12684,11 +12688,7 @@
           <t>secretariat-cardiologie@ch-hopitauxduleman.fr</t>
         </is>
       </c>
-      <c r="H297" s="2" t="inlineStr">
-        <is>
-          <t>affaires-medicales@ch-hopitauxduleman.fr</t>
-        </is>
-      </c>
+      <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12723,19 +12723,15 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Mme Hélène VIVET</t>
+          <t>Mme Myriam MOUCHET</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>h-vivet@hopitauxduleman.fr</t>
-        </is>
-      </c>
-      <c r="H298" s="2" t="inlineStr">
-        <is>
-          <t>affaires-medicales@ch-hopitauxduleman.fr</t>
-        </is>
-      </c>
+          <t>m-mouchet@ch-hopitauxduleman.fr</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16723,7 +16719,11 @@
           <t>dpacaud@ch-sens.fr</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr"/>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>drh@ch-sens.fr</t>
+        </is>
+      </c>
       <c r="I394" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17204,7 +17204,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Hôpital d'instruction des Armées PERCY (CLAMART)</t>
+          <t>Hôpital National d'Instruction des Armées PERCY (CLAMART)</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Hôpital d'instruction des Armées PERCY (CLAMART)</t>
+          <t>Hôpital National d'Instruction des Armées PERCY (CLAMART)</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
@@ -19100,443 +19100,443 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId327"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId581"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId582"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G356" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D361" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G369" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D373" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G373" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G376" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G378" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G386" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G387" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G356" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D361" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G369" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D373" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G373" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G376" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G378" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G386" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G387" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId765"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId766"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G395" r:id="rId767"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId768"/>

--- a/fhf_cardiologie.xlsx
+++ b/fhf_cardiologie.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I442"/>
+  <dimension ref="A1:I440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1362,11 +1362,7 @@
           <t>Dr Vincent AUDIGIER</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>nor.el.houda.zelazli@ch-ardeche-meridionale.fr</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
@@ -2464,7 +2460,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hopital d'Instruction des Armées LAVERAN (MARSEILLE)</t>
+          <t>Hopital National d'Instruction des Armées LAVERAN (MARSEILLE)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3490,7 +3486,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>relations.humaines@ch-bastia.fr</t>
+          <t>sec-ressources-humaines@ch-bastia.fr</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3529,7 +3525,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>relations.humaines@ch-bastia.fr</t>
+          <t>sec-ressources-humaines@ch-bastia.fr</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3568,7 +3564,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>relations.humaines@ch-bastia.fr</t>
+          <t>sec-ressources-humaines@ch-bastia.fr</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3607,7 +3603,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>relations.humaines@ch-bastia.fr</t>
+          <t>sec-ressources-humaines@ch-bastia.fr</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4962,7 +4958,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hôpital d'Instruction des Armées CLERMONT-TONNERRE (BREST)</t>
+          <t>Hôpital Régional d'Instruction des Armées CLERMONT-TONNERRE (BREST)</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -9149,7 +9145,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Hopital d'Instruction des Armees LEGOUEST (METZ)</t>
+          <t>Hopital Régional d'Instruction des Armees LEGOUEST (METZ)</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -10602,44 +10598,40 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Pas-de-Calais</t>
+          <t>Puy-de-Dôme</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Centre Hospitalier d'Arras (Arras)</t>
+          <t>CHRU Clermont- Ferrand Gabriel-Montpied (Clermont-Ferrand)</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1656-establishment5419</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1688-establishment2931</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Cardiologie / USIC / Explorations fonctionnelles cardio.</t>
+          <t>Cardiologie médicale et médecine vasculaire</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Dr Francesco FAVATA</t>
+          <t>M. Romain ESCHALIER</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>Francesco.FAVATA@gh-artoisternois.fr</t>
-        </is>
-      </c>
-      <c r="H246" s="2" t="inlineStr">
-        <is>
-          <t>secretariat.direction@gh-artoisternois.fr</t>
-        </is>
-      </c>
+          <t>reschalier@chu-clermontferrand.fr</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -10649,44 +10641,40 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Pas-de-Calais</t>
+          <t>Puy-de-Dôme</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Centre Hospitalier d'Arras (Arras)</t>
+          <t>CHRU Clermont- Ferrand Gabriel-Montpied (Clermont-Ferrand)</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1656-establishment5419</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1688-establishment2931</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>SSR Cardio - Pneumo (Éole)</t>
+          <t>Chirurgie Cardio-Vasculaire</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Dr Philippe PAUQUET</t>
+          <t>Pr Lionel CAMILLERI</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>Philippe.PAUQUET@gh-artoisternois.fr</t>
-        </is>
-      </c>
-      <c r="H247" s="2" t="inlineStr">
-        <is>
-          <t>secretariat.direction@gh-artoisternois.fr</t>
-        </is>
-      </c>
+          <t>lcamilleri@chu-clermontferrand.fr</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -10706,27 +10694,27 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>CHRU Clermont- Ferrand Gabriel-Montpied (Clermont-Ferrand)</t>
+          <t>Centre hospitalier Guy Thomas (Riom)</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1688-establishment2931</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1694-establishment5455</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Cardiologie médicale et médecine vasculaire</t>
+          <t>Médecine à orientation cardiologique</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>M. Romain ESCHALIER</t>
+          <t>Dr Pascale HAUMONT</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>reschalier@chu-clermontferrand.fr</t>
+          <t>p.haumont@ch-riom.fr</t>
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
@@ -10739,39 +10727,31 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Puy-de-Dôme</t>
+          <t>Pyrénées-Atlantiques</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>CHRU Clermont- Ferrand Gabriel-Montpied (Clermont-Ferrand)</t>
+          <t>Centre hospitalier (Pau)</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1688-establishment2931</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1731-establishment5490</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Chirurgie Cardio-Vasculaire</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>Pr Lionel CAMILLERI</t>
-        </is>
-      </c>
-      <c r="G249" s="2" t="inlineStr">
-        <is>
-          <t>lcamilleri@chu-clermontferrand.fr</t>
-        </is>
-      </c>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
@@ -10782,40 +10762,40 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Puy-de-Dôme</t>
+          <t>Pyrénées-Atlantiques</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Centre hospitalier Guy Thomas (Riom)</t>
+          <t>Centre hospitalier de la Côte Basque - Saint-Léon (Bayonne)</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1694-establishment5455</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1733-establishment5492</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Médecine à orientation cardiologique</t>
+          <t>Cardiologie Consultations</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Dr Pascale HAUMONT</t>
-        </is>
-      </c>
-      <c r="G250" s="2" t="inlineStr">
-        <is>
-          <t>p.haumont@ch-riom.fr</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr"/>
+          <t>Dr Jean-Baptiste BERNEAU</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>jdaeschler@ch-cotebasque.fr</t>
+        </is>
+      </c>
       <c r="I250" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -10835,17 +10815,17 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Pau)</t>
+          <t>Centre hospitalier (Orthez)</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1731-establishment5490</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1738-establishment5497</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>MEDECINE POLYVALENTE à orientations Cardiologie, Médecine, Pneumologie et Gastroentérologie</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -10860,40 +10840,36 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Pyrénées-Atlantiques</t>
+          <t>Hautes-Pyrénées</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Centre hospitalier de la Côte Basque - Saint-Léon (Bayonne)</t>
+          <t>Centre Hospitalier de Bigorre site de la Gespe (MCO) (Tarbes)</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1733-establishment5492</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1746-establishment5505</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Cardiologie Consultations</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Dr Jean-Baptiste BERNEAU</t>
+          <t>Mme Christine LEONARD</t>
         </is>
       </c>
       <c r="G252" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr">
-        <is>
-          <t>jdaeschler@ch-cotebasque.fr</t>
-        </is>
-      </c>
+      <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -10903,30 +10879,34 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Pyrénées-Atlantiques</t>
+          <t>Hautes-Pyrénées</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Orthez)</t>
+          <t>Centre Hospitalier de Bigorre site de la Gespe (MCO) (Tarbes)</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1738-establishment5497</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1746-establishment5505</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>MEDECINE POLYVALENTE à orientations Cardiologie, Médecine, Pneumologie et Gastroentérologie</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr"/>
+          <t>Réanimation spécialisée en cardiologie</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>M. Michel SERRANO</t>
+        </is>
+      </c>
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
@@ -10948,22 +10928,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de Bigorre site de la Gespe (MCO) (Tarbes)</t>
+          <t>CENTRE HOSPITALIER (Lourdes)</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1746-establishment5505</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1746-establishment5506</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie et maladies vasculaires</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Mme Christine LEONARD</t>
+          <t>M. Christian DEMASLES</t>
         </is>
       </c>
       <c r="G254" t="inlineStr"/>
@@ -10977,34 +10957,30 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Hautes-Pyrénées</t>
+          <t>Pyrénées-Orientales</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de Bigorre site de la Gespe (MCO) (Tarbes)</t>
+          <t>Centre Hospitalier de Perpignan (Perpignan)</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1746-establishment5505</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1761-establishment5519</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Réanimation spécialisée en cardiologie</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>M. Michel SERRANO</t>
-        </is>
-      </c>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
@@ -11016,36 +10992,44 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Hautes-Pyrénées</t>
+          <t>Bas-Rhin</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER (Lourdes)</t>
+          <t>Centre hospitalier (Haguenau)</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1746-establishment5506</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1806-establishment5561</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Cardiologie et maladies vasculaires</t>
+          <t>Service de Cardiologie</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>M. Christian DEMASLES</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr"/>
-      <c r="H256" t="inlineStr"/>
+          <t>Dr Philippe COUPPIE</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>sec.cardiologie@ch-haguenau.fr</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>Valentine.SCHALLER@ch-haguenau.fr</t>
+        </is>
+      </c>
       <c r="I256" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -11055,32 +11039,44 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Pyrénées-Orientales</t>
+          <t>Bas-Rhin</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de Perpignan (Perpignan)</t>
+          <t>CENTRE HOSPITALIER SELESTAT (SELESTAT)</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1761-establishment5519</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1811-establishment5566</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
+          <t>Consultations externes de cardiologie et explorations cardiovasculaires</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Dr Mounzer MANSOUR</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>Mounzer.MANSOUR@ghso.fr</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>agnes.schreiner@ghso.fr</t>
+        </is>
+      </c>
       <c r="I257" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -11100,32 +11096,32 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Haguenau)</t>
+          <t>Centre hospitalier (Wissembourg)</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1806-establishment5561</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1786-establishment5544</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Service de Cardiologie</t>
+          <t>Plateau technique de cardiologie</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Dr Philippe COUPPIE</t>
+          <t>Dr Rodolphe THEOLADE</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>sec.cardiologie@ch-haguenau.fr</t>
+          <t>rtheolade@ch-wissembourg.fr</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>Valentine.SCHALLER@ch-haguenau.fr</t>
+          <t>dam@ch-haguenau.fr</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -11147,32 +11143,32 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER SELESTAT (SELESTAT)</t>
+          <t>Centre hospitalier (Wissembourg)</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1811-establishment5566</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1786-establishment5544</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Consultations externes de cardiologie et explorations cardiovasculaires</t>
+          <t>SSR Cardiologique</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Dr Mounzer MANSOUR</t>
+          <t>Dr Rodolphe THEOLADE</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Mounzer.MANSOUR@ghso.fr</t>
+          <t>rtheolade@ch-wissembourg.fr</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>agnes.schreiner@ghso.fr</t>
+          <t>dam@ch-haguenau.fr</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -11194,32 +11190,24 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Wissembourg)</t>
+          <t>Hôpital Civil (Strasbourg)</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1786-establishment5544</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1777-establishment1331</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Plateau technique de cardiologie</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>Dr Rodolphe THEOLADE</t>
-        </is>
-      </c>
-      <c r="G260" s="2" t="inlineStr">
-        <is>
-          <t>rtheolade@ch-wissembourg.fr</t>
-        </is>
-      </c>
+          <t>Cardiologie - NHC</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>dam@ch-haguenau.fr</t>
+          <t>armelle.drexler@chru-strasbourg.fr</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -11241,32 +11229,24 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Wissembourg)</t>
+          <t>Hôpital Civil (Strasbourg)</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1786-establishment5544</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1777-establishment1331</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>SSR Cardiologique</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>Dr Rodolphe THEOLADE</t>
-        </is>
-      </c>
-      <c r="G261" s="2" t="inlineStr">
-        <is>
-          <t>rtheolade@ch-wissembourg.fr</t>
-        </is>
-      </c>
+          <t>Chirurgie cardio vasculaire - transplantation et assistance cardiaque - NHC</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>dam@ch-haguenau.fr</t>
+          <t>armelle.drexler@chru-strasbourg.fr</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -11278,34 +11258,38 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Bas-Rhin</t>
+          <t>Haut-Rhin</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Hôpital Civil (Strasbourg)</t>
+          <t>Hôpital Louis Pasteur (Colmar)</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1777-establishment1331</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1817-establishment5572</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Cardiologie - NHC</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr"/>
+          <t>Cardiologie (Médecine C)</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Dr Laszlo LEVAI</t>
+        </is>
+      </c>
       <c r="G262" t="inlineStr"/>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>armelle.drexler@chru-strasbourg.fr</t>
+          <t>affairesmedicales.dirg@ch-colmar.fr</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -11317,34 +11301,34 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Bas-Rhin</t>
+          <t>Haut-Rhin</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Hôpital Civil (Strasbourg)</t>
+          <t>Hôpital Louis Pasteur (Colmar)</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1777-establishment1331</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1817-establishment5572</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Chirurgie cardio vasculaire - transplantation et assistance cardiaque - NHC</t>
+          <t>Explorations fonctionnelles cardio-vasculaires</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr"/>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>armelle.drexler@chru-strasbourg.fr</t>
+          <t>affairesmedicales.dirg@ch-colmar.fr</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -11366,30 +11350,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Hôpital Louis Pasteur (Colmar)</t>
+          <t>Hôpital Emile Muller (Mulhouse)</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1817-establishment5572</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1818-establishment9947</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Cardiologie (Médecine C)</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>Dr Laszlo LEVAI</t>
-        </is>
-      </c>
+          <t>Radiologie cardio-interventionnelle</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr"/>
-      <c r="H264" s="2" t="inlineStr">
-        <is>
-          <t>affairesmedicales.dirg@ch-colmar.fr</t>
-        </is>
-      </c>
+      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -11409,26 +11385,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Hôpital Louis Pasteur (Colmar)</t>
+          <t>Hôpital Hasenrain (Mulhouse)</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1817-establishment5572</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1818-establishment5573</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Explorations fonctionnelles cardio-vasculaires</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr"/>
-      <c r="H265" s="2" t="inlineStr">
-        <is>
-          <t>affairesmedicales.dirg@ch-colmar.fr</t>
-        </is>
-      </c>
+      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -11438,27 +11410,27 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Haut-Rhin</t>
+          <t>Rhône</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Hôpital Emile Muller (Mulhouse)</t>
+          <t>Hôpital de la Croix-Rousse - HCL (Lyon)</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1818-establishment9947</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1860-establishment5607</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Radiologie cardio-interventionnelle</t>
+          <t>Consultation de Cardiologie Pédiatrique</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -11473,27 +11445,27 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Haut-Rhin</t>
+          <t>Rhône</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Hôpital Hasenrain (Mulhouse)</t>
+          <t>Hôpital de la Croix-Rousse - HCL (Lyon)</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1818-establishment5573</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1860-establishment5607</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Service de Cardiologie</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -11518,25 +11490,37 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Hôpital de la Croix-Rousse - HCL (Lyon)</t>
+          <t>Hôpital de Villefranche-sur-Saône - HNO (Villefranche-sur-Saône Cedex)</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1860-establishment5607</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1887-establishment5630</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Consultation de Cardiologie Pédiatrique</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
-      <c r="H268" t="inlineStr"/>
+          <t>CARDIOLOGIE, CARDIOLOGIE INTERVENTIONNELLE ET UNITE DE SOINS INTENSIFS DE CARDIOLOGIE</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Dr Olivier LE VAVASSEUR</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>secretariat.cardio@hno.fr</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>direction-generale@hno.fr</t>
+        </is>
+      </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Non spécifié / Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -11553,17 +11537,17 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Hôpital de la Croix-Rousse - HCL (Lyon)</t>
+          <t>Hôpital Femme Mère-Enfant -HCL (BRON)</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1860-establishment5607</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1867-establishment6722</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Service de Cardiologie</t>
+          <t>Consultation de Cardiologie Pédiatrique</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -11588,37 +11572,25 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Hôpital de Villefranche-sur-Saône - HNO (Villefranche-sur-Saône Cedex)</t>
+          <t>Hôpital Louis Pradel - HCL (Bron)</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1887-establishment5630</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1867-establishment5613</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE, CARDIOLOGIE INTERVENTIONNELLE ET UNITE DE SOINS INTENSIFS DE CARDIOLOGIE</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>Dr Olivier LE VAVASSEUR</t>
-        </is>
-      </c>
-      <c r="G270" s="2" t="inlineStr">
-        <is>
-          <t>secretariat.cardio@hno.fr</t>
-        </is>
-      </c>
-      <c r="H270" s="2" t="inlineStr">
-        <is>
-          <t>direction-generale@hno.fr</t>
-        </is>
-      </c>
+          <t>Plateau ambulatoire cardiologique</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non spécifié / Non</t>
         </is>
       </c>
     </row>
@@ -11635,17 +11607,17 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Hôpital Femme Mère-Enfant -HCL (BRON)</t>
+          <t>Hôpital Louis Pradel - HCL (Bron)</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1867-establishment6722</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1867-establishment5613</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Consultation de Cardiologie Pédiatrique</t>
+          <t>Plateau Urgences Cardiologiques</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -11680,7 +11652,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Plateau ambulatoire cardiologique</t>
+          <t>Service d'Hémodynamique et de Cardiologie Interventionnelle</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -11688,7 +11660,7 @@
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Non spécifié / Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -11715,7 +11687,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Plateau Urgences Cardiologiques</t>
+          <t>Service d'Imagerie cardio-vasculaire et thoracique</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -11750,7 +11722,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Service d'Hémodynamique et de Cardiologie Interventionnelle</t>
+          <t>Service de Cardiologie : filière coronaires et valves</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -11758,7 +11730,7 @@
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non spécifié / Non</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11757,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Service d'Imagerie cardio-vasculaire et thoracique</t>
+          <t>Service de Cardiologie congénitale adultes et enfants</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -11820,7 +11792,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Service de Cardiologie : filière coronaires et valves</t>
+          <t>Service de Cardiologie E (cardiologie générale)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -11855,7 +11827,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Service de Cardiologie congénitale adultes et enfants</t>
+          <t>Service de Chirurgie Cardio-Vasculaire A</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -11890,7 +11862,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Service de Cardiologie E (cardiologie générale)</t>
+          <t>Service de Chirurgie Cardio-Vasculaire B</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -11925,7 +11897,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Service de Chirurgie Cardio-Vasculaire A</t>
+          <t>Service de Chirurgie Cardio-Vasculaire C</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -11950,17 +11922,17 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Hôpital Louis Pradel - HCL (Bron)</t>
+          <t>Hôpital Saint Joseph Saint Luc (Lyon)</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1867-establishment5613</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3208-establishment7212</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Service de Chirurgie Cardio-Vasculaire B</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -11985,21 +11957,29 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Hôpital Louis Pradel - HCL (Bron)</t>
+          <t>Hopital spécialisé des Armées DESGENETTES (LYON 3)</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1867-establishment5613</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8038</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Service de Chirurgie Cardio-Vasculaire C</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr"/>
+          <t>CARDIOLOGIE ET PATHOLOGIE VASCULAIRE 69</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Dr Delphine MIOULET</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>cardiologie@hiadcssa.org</t>
+        </is>
+      </c>
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
@@ -12020,21 +12000,29 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Hôpital Saint Joseph Saint Luc (Lyon)</t>
+          <t>Hôpital Lyon Sud HCL (Pierre-Bénite)</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3208-establishment7212</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1878-establishment5623</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
+          <t>Consultations de cardiologie - Explorations fonctionnelles cardiologiques</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Pr Pierre LANTELME</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>pierre.lantelme@chu-lyon.fr</t>
+        </is>
+      </c>
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
@@ -12045,37 +12033,37 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Rhône</t>
+          <t>Haute-Saône</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Hopital spécialisé des Armées DESGENETTES (LYON 3)</t>
+          <t>GROUPE HOSPITALIER DE LA HAUTE-SAONE site de Vesoul (VESOUL)</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8038</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1902-establishment8474</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE ET PATHOLOGIE VASCULAIRE 69</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Dr Delphine MIOULET</t>
+          <t>Dr Lisbeth CART</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>cardiologie@hiadcssa.org</t>
+          <t>l.cart@gh70.fr</t>
         </is>
       </c>
       <c r="H283" t="inlineStr"/>
@@ -12088,39 +12076,31 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Rhône</t>
+          <t>Saône-et-Loire</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Hôpital Lyon Sud HCL (Pierre-Bénite)</t>
+          <t>Centre hospitalier (MACON)</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1878-establishment5623</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1908-establishment5650</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Consultations de cardiologie - Explorations fonctionnelles cardiologiques</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>Pr Pierre LANTELME</t>
-        </is>
-      </c>
-      <c r="G284" s="2" t="inlineStr">
-        <is>
-          <t>pierre.lantelme@chu-lyon.fr</t>
-        </is>
-      </c>
+          <t>CARDIOLOGIE</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
@@ -12131,37 +12111,37 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Haute-Saône</t>
+          <t>Saône-et-Loire</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>GROUPE HOSPITALIER DE LA HAUTE-SAONE site de Vesoul (VESOUL)</t>
+          <t>Hôpital Fondation Hôtel-Dieu du Creusot (LE CREUSOT)</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1902-establishment8474</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3155-establishment7870</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Consultations Cardiologie</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Dr Lisbeth CART</t>
+          <t>Dr Ghassan YANNI</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>l.cart@gh70.fr</t>
+          <t>ghyanni@hoteldieu-creusot.fr</t>
         </is>
       </c>
       <c r="H285" t="inlineStr"/>
@@ -12184,21 +12164,29 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Centre hospitalier (MACON)</t>
+          <t>Centre hospitalier EHPAD (AUTUN)</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1908-establishment5650</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1935-establishment5674</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
+          <t>Consultations Cardiologie</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Dr Patrick BUTTARD</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>P.BUTTARD@ch-autun.fr</t>
+        </is>
+      </c>
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
@@ -12219,30 +12207,34 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Hôpital Fondation Hôtel-Dieu du Creusot (LE CREUSOT)</t>
+          <t>Centre hospitalier (CHALON-SUR-SAONE)</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3155-establishment7870</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1927-establishment5666</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Consultations Cardiologie</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Dr Ghassan YANNI</t>
+          <t>Dr Patrick BUTTARD</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>ghyanni@hoteldieu-creusot.fr</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr"/>
+          <t>patrick.buttard@ch-chalon71.fr</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>sylvain.rollot@ch-chalon71.fr</t>
+        </is>
+      </c>
       <c r="I287" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12252,37 +12244,37 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Saône-et-Loire</t>
+          <t>Savoie</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Centre hospitalier EHPAD (AUTUN)</t>
+          <t>Centre hospitalier Métropole Savoie (CHAMBERY)</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1935-establishment5674</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1996-establishment5735</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Consultations Cardiologie</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Dr Patrick BUTTARD</t>
+          <t>Dr Vincent DESCOTES-GENON</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>P.BUTTARD@ch-autun.fr</t>
+          <t>vincent.descotes-genon@ch-metropole-savoie.fr</t>
         </is>
       </c>
       <c r="H288" t="inlineStr"/>
@@ -12295,44 +12287,40 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Saône-et-Loire</t>
+          <t>Savoie</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Centre hospitalier (CHALON-SUR-SAONE)</t>
+          <t>Centre hospitalier Métropole Savoie (AIX-LES-BAINS)</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1927-establishment5666</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1996-establishment5736</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Médecine polyvalente à orientation gastro-entérologie et cardiologie</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Dr Patrick BUTTARD</t>
+          <t>Dr Léa CARBONE</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>patrick.buttard@ch-chalon71.fr</t>
-        </is>
-      </c>
-      <c r="H289" s="2" t="inlineStr">
-        <is>
-          <t>sylvain.rollot@ch-chalon71.fr</t>
-        </is>
-      </c>
+          <t>lea.carbone@ch-metropole-savoie.fr</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12342,22 +12330,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Savoie</t>
+          <t>Haute-Savoie</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Centre hospitalier Métropole Savoie (CHAMBERY)</t>
+          <t>Centre Hospitalier Annecy Genevois - site ANNECY (EPAGNY METZ TESSY)</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1996-establishment5735</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2012-establishment5750</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -12367,15 +12355,19 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Dr Vincent DESCOTES-GENON</t>
+          <t>Dr Emmanuel DESJOYAUX</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>vincent.descotes-genon@ch-metropole-savoie.fr</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr"/>
+          <t>edesjoyaux@ch-annecygenevois.fr</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>amechoud@ch-annecygenevois.fr</t>
+        </is>
+      </c>
       <c r="I290" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12385,40 +12377,44 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Savoie</t>
+          <t>Haute-Savoie</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Centre hospitalier Métropole Savoie (AIX-LES-BAINS)</t>
+          <t>Centre Hospitalier Annecy Genevois - site ANNECY (EPAGNY METZ TESSY)</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1996-establishment5736</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2012-establishment5750</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Médecine polyvalente à orientation gastro-entérologie et cardiologie</t>
+          <t>Cardiologie - USIC - Unité de soins intensifs cardiologiques</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Dr Léa CARBONE</t>
+          <t>Dr Emmanuel DESJOYAUX</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>lea.carbone@ch-metropole-savoie.fr</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr"/>
+          <t>edesjoyaux@ch-annecygenevois.fr</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>amechoud@ch-annecygenevois.fr</t>
+        </is>
+      </c>
       <c r="I291" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12438,12 +12434,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Annecy Genevois - site ANNECY (EPAGNY METZ TESSY)</t>
+          <t>Centre Hospitalier Alpes Léman Établissement Support du GHT Léman Mont-Blanc (Contamine sur Arve)</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2012-establishment5750</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2013-establishment5751</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -12453,17 +12449,13 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Dr Emmanuel DESJOYAUX</t>
-        </is>
-      </c>
-      <c r="G292" s="2" t="inlineStr">
-        <is>
-          <t>edesjoyaux@ch-annecygenevois.fr</t>
-        </is>
-      </c>
+          <t>Dr Vuthik PANH</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr"/>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>amechoud@ch-annecygenevois.fr</t>
+          <t>nmenuet@ch-alpes-leman.fr</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -12485,34 +12477,26 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Annecy Genevois - site ANNECY (EPAGNY METZ TESSY)</t>
+          <t>HOPITAUX DU LEMAN Site Georges PIANTA à THONON (Thonon-les-Bains)</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2012-establishment5750</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2017-establishment5755</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Cardiologie - USIC - Unité de soins intensifs cardiologiques</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Dr Emmanuel DESJOYAUX</t>
-        </is>
-      </c>
-      <c r="G293" s="2" t="inlineStr">
-        <is>
-          <t>edesjoyaux@ch-annecygenevois.fr</t>
-        </is>
-      </c>
-      <c r="H293" s="2" t="inlineStr">
-        <is>
-          <t>amechoud@ch-annecygenevois.fr</t>
-        </is>
-      </c>
+          <t>Dr Audrey NGEUTCHA TANTCHOU</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12532,30 +12516,26 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Alpes Léman Établissement Support du GHT Léman Mont-Blanc (Contamine sur Arve)</t>
+          <t>HOPITAUX DU LEMAN Site Georges PIANTA à THONON (Thonon-les-Bains)</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2013-establishment5751</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2017-establishment5755</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Explorations fonctionnelles cardiologiques</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Dr Vuthik PANH</t>
+          <t>Mme Myriam MOUCHET</t>
         </is>
       </c>
       <c r="G294" t="inlineStr"/>
-      <c r="H294" s="2" t="inlineStr">
-        <is>
-          <t>nmenuet@ch-alpes-leman.fr</t>
-        </is>
-      </c>
+      <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12665,27 +12645,27 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>HOPITAUX DU LEMAN Site Georges PIANTA à THONON (Thonon-les-Bains)</t>
+          <t>Hopital Gabriel Déplante (RUMILLY)</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2017-establishment5755</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2015-establishment7659</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>CARDIO-GERIATRIE</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Dr Audrey NGEUTCHA TANTCHOU</t>
+          <t>Dr Mathieu CHACORNAC</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>secretariat-cardiologie@ch-hopitauxduleman.fr</t>
+          <t>mchacornac@ch-annecygenevois.fr</t>
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
@@ -12698,40 +12678,40 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Haute-Savoie</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>HOPITAUX DU LEMAN Site Georges PIANTA à THONON (Thonon-les-Bains)</t>
+          <t>AP-HP Hôpital Universitaire Pitié Salpêtrière (Paris)</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2017-establishment5755</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2048-establishment5783</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Explorations fonctionnelles cardiologiques</t>
+          <t>Cardiogénétique et myogénétique moléculaire et cellulaire</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Mme Myriam MOUCHET</t>
-        </is>
-      </c>
-      <c r="G298" s="2" t="inlineStr">
-        <is>
-          <t>m-mouchet@ch-hopitauxduleman.fr</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr"/>
+          <t>Dr MAGALIE LODIN PASQUIER</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
       <c r="I298" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12741,40 +12721,40 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Haute-Savoie</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Hopital Gabriel Déplante (RUMILLY)</t>
+          <t>AP-HP Hôpital Universitaire Pitié Salpêtrière (Paris)</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2015-establishment7659</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2048-establishment5783</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>CARDIO-GERIATRIE</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Dr Mathieu CHACORNAC</t>
-        </is>
-      </c>
-      <c r="G299" s="2" t="inlineStr">
-        <is>
-          <t>mchacornac@ch-annecygenevois.fr</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr"/>
+          <t>Dr MICHEL ZEITOUNI</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
       <c r="I299" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12804,12 +12784,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Cardiogénétique et myogénétique moléculaire et cellulaire</t>
+          <t>Cardiologie - Hospitalisation</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Dr MAGALIE LODIN PASQUIER</t>
+          <t>Dr MARIA ELISABETA GHEORGHIU</t>
         </is>
       </c>
       <c r="G300" t="inlineStr"/>
@@ -12847,12 +12827,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Imagerie Cardiovasculaire et Thoracique (ICT)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Dr MICHEL ZEITOUNI</t>
+          <t>Dr PAUL-GYDEON RITVO</t>
         </is>
       </c>
       <c r="G301" t="inlineStr"/>
@@ -12890,12 +12870,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Cardiologie - Hospitalisation</t>
+          <t>Lipidologie et Prévention Cardiovasculaire</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Dr MARIA ELISABETA GHEORGHIU</t>
+          <t>Dr ANTONIO GALLO</t>
         </is>
       </c>
       <c r="G302" t="inlineStr"/>
@@ -12933,12 +12913,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Imagerie Cardiovasculaire et Thoracique (ICT)</t>
+          <t>Pharmacologie oncologique et cardiovasculaire et Oncocardiologie</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Dr PAUL-GYDEON RITVO</t>
+          <t>Pr JOE ELIE SALEM</t>
         </is>
       </c>
       <c r="G303" t="inlineStr"/>
@@ -12976,12 +12956,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Lipidologie et Prévention Cardiovasculaire</t>
+          <t>Radiologie cardiovasculaire et interventionnelle</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Dr ANTONIO GALLO</t>
+          <t>TRISTAN PITTIN</t>
         </is>
       </c>
       <c r="G304" t="inlineStr"/>
@@ -13019,12 +12999,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Pharmacologie oncologique et cardiovasculaire et Oncocardiologie</t>
+          <t>Unité de Cardiologie Ambulatoire Sans et Avec Rendez-vous</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Pr JOE ELIE SALEM</t>
+          <t>Dr CLEMENT DAVRIL</t>
         </is>
       </c>
       <c r="G305" t="inlineStr"/>
@@ -13062,12 +13042,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Radiologie cardiovasculaire et interventionnelle</t>
+          <t>Unité Soins Intensifs Cardiologie (USIC)</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>TRISTAN PITTIN</t>
+          <t>Pr JOHANNE SILVAIN</t>
         </is>
       </c>
       <c r="G306" t="inlineStr"/>
@@ -13095,33 +13075,33 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Universitaire Pitié Salpêtrière (Paris)</t>
+          <t>AP-HP Hôpital Cochin - Port-Royal (Paris)</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2048-establishment5783</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2051-establishment5786</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Unité de Cardiologie Ambulatoire Sans et Avec Rendez-vous</t>
+          <t>Anesthésie en chirurgie digestive, endocrinienne, endoscopie digestive, radiologie et cardiologie interventionnelles</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Dr CLEMENT DAVRIL</t>
+          <t>Dr ILYES MEKKI</t>
         </is>
       </c>
       <c r="G307" t="inlineStr"/>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>choella.akbaraly@aphp.fr</t>
+          <t>marie-cecile.mocellin@aphp.fr</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>Non spécifié / Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -13138,28 +13118,28 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Universitaire Pitié Salpêtrière (Paris)</t>
+          <t>AP-HP Hôpital Cochin - Port-Royal (Paris)</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2048-establishment5783</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2051-establishment5786</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Unité Soins Intensifs Cardiologie (USIC)</t>
+          <t>cardiologie</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Pr JOHANNE SILVAIN</t>
+          <t>Dr ANISSA ZIDOUNE</t>
         </is>
       </c>
       <c r="G308" t="inlineStr"/>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>choella.akbaraly@aphp.fr</t>
+          <t>marie-cecile.mocellin@aphp.fr</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -13191,12 +13171,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Anesthésie en chirurgie digestive, endocrinienne, endoscopie digestive, radiologie et cardiologie interventionnelles</t>
+          <t>explorations invasives cardiologiques</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Dr ILYES MEKKI</t>
+          <t>Dr FABIEN PICARD</t>
         </is>
       </c>
       <c r="G309" t="inlineStr"/>
@@ -13207,7 +13187,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non spécifié / Non</t>
         </is>
       </c>
     </row>
@@ -13234,12 +13214,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>cardiologie</t>
+          <t>Imagerie cardiothoracique et oncologique</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Dr ANISSA ZIDOUNE</t>
+          <t>Pr MARIE PIERRE REVEL DUBOIS</t>
         </is>
       </c>
       <c r="G310" t="inlineStr"/>
@@ -13267,28 +13247,28 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Cochin - Port-Royal (Paris)</t>
+          <t>AP-HP Groupe hospitalier Lariboisière - Fernand-Widal (Paris)</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2051-establishment5786</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2043-establishment5778</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>explorations invasives cardiologiques</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Dr FABIEN PICARD</t>
+          <t>MARIE CHRISTINE DARRICAU</t>
         </is>
       </c>
       <c r="G311" t="inlineStr"/>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>marie-cecile.mocellin@aphp.fr</t>
+          <t>nolwenn.jacob@aphp.fr</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -13310,28 +13290,28 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Cochin - Port-Royal (Paris)</t>
+          <t>AP-HP Groupe hospitalier Lariboisière - Fernand-Widal (Paris)</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2051-establishment5786</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2043-establishment5778</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Imagerie cardiothoracique et oncologique</t>
+          <t>Explorations Fonctionnelles Cardio-vasculaires et Respiratoires</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Pr MARIE PIERRE REVEL DUBOIS</t>
+          <t>Dr PIERRE LOZERON</t>
         </is>
       </c>
       <c r="G312" t="inlineStr"/>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>marie-cecile.mocellin@aphp.fr</t>
+          <t>nolwenn.jacob@aphp.fr</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -13363,12 +13343,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Unité de Soins Intensifs en Cardiologie</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>MARIE CHRISTINE DARRICAU</t>
+          <t>AURORE LEMAY</t>
         </is>
       </c>
       <c r="G313" t="inlineStr"/>
@@ -13396,28 +13376,28 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>AP-HP Groupe hospitalier Lariboisière - Fernand-Widal (Paris)</t>
+          <t>AP-HP Hôpital Bichat - Claude-Bernard (Paris)</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2043-establishment5778</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2038-establishment5775</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Explorations Fonctionnelles Cardio-vasculaires et Respiratoires</t>
+          <t>Hospitalisation de cardiologie</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Dr PIERRE LOZERON</t>
+          <t>Dr JULIA ATTIA</t>
         </is>
       </c>
       <c r="G314" t="inlineStr"/>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>nolwenn.jacob@aphp.fr</t>
+          <t>marie.hiance@aphp.fr</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -13439,28 +13419,28 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>AP-HP Groupe hospitalier Lariboisière - Fernand-Widal (Paris)</t>
+          <t>AP-HP Hôpital Bichat - Claude-Bernard (Paris)</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2043-establishment5778</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2038-establishment5775</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Unité de Soins Intensifs en Cardiologie</t>
+          <t>Imagerie cardiovasculaire</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>AURORE LEMAY</t>
+          <t>Dr Alexandre FITOUSSI</t>
         </is>
       </c>
       <c r="G315" t="inlineStr"/>
       <c r="H315" s="2" t="inlineStr">
         <is>
-          <t>nolwenn.jacob@aphp.fr</t>
+          <t>marie.hiance@aphp.fr</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -13492,12 +13472,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Hospitalisation de cardiologie</t>
+          <t>Réanimation chirurgicale cardiologique</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Dr JULIA ATTIA</t>
+          <t>Pr DAN LONGROIS</t>
         </is>
       </c>
       <c r="G316" t="inlineStr"/>
@@ -13535,12 +13515,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Imagerie cardiovasculaire</t>
+          <t>Soins intensifs de cardiologie</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Dr Alexandre FITOUSSI</t>
+          <t>Pr GREGORY DUCROCQ</t>
         </is>
       </c>
       <c r="G317" t="inlineStr"/>
@@ -13568,28 +13548,28 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Bichat - Claude-Bernard (Paris)</t>
+          <t>AP-HP Hôpital européen Georges-Pompidou (Paris)</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2038-establishment5775</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2056-establishment5791</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Réanimation chirurgicale cardiologique</t>
+          <t>Biochimie cardiovasculaire</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Pr DAN LONGROIS</t>
+          <t>MURIELLE PIETROBONI</t>
         </is>
       </c>
       <c r="G318" t="inlineStr"/>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>marie.hiance@aphp.fr</t>
+          <t>Sophie.maraval@egp.aphp.fr</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -13611,28 +13591,28 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Bichat - Claude-Bernard (Paris)</t>
+          <t>AP-HP Hôpital européen Georges-Pompidou (Paris)</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2038-establishment5775</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2056-establishment5791</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Soins intensifs de cardiologie</t>
+          <t>Cardio-oncologie</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Pr GREGORY DUCROCQ</t>
+          <t>Dr SEBASTIAN STOICA</t>
         </is>
       </c>
       <c r="G319" t="inlineStr"/>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>marie.hiance@aphp.fr</t>
+          <t>Sophie.maraval@egp.aphp.fr</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -13664,12 +13644,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Biochimie cardiovasculaire</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>MURIELLE PIETROBONI</t>
+          <t>Dr CATHERINE SZYMANSKI</t>
         </is>
       </c>
       <c r="G320" t="inlineStr"/>
@@ -13707,14 +13687,10 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Cardio-oncologie</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>Dr SEBASTIAN STOICA</t>
-        </is>
-      </c>
+          <t>Consultation de cardiologie</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr"/>
       <c r="H321" s="2" t="inlineStr">
         <is>
@@ -13750,12 +13726,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Plateau Technique non invasif (Explorations non invasives cardio-vasculaires)</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Dr CATHERINE SZYMANSKI</t>
+          <t>Dr DORRA M'BAREK RABOUDI</t>
         </is>
       </c>
       <c r="G322" t="inlineStr"/>
@@ -13783,24 +13759,28 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital européen Georges-Pompidou (Paris)</t>
+          <t>AP-HP Groupe Hospitalier Saint-Louis, Lariboisière, Fernand-Widal Site Saint Louis (Paris)</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2056-establishment5791</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2044-establishment5779</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Consultation de cardiologie</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr"/>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Dr BENJAMIN SIBILIA</t>
+        </is>
+      </c>
       <c r="G323" t="inlineStr"/>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>Sophie.maraval@egp.aphp.fr</t>
+          <t>nolwenn.jacob@aphp.fr</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -13822,30 +13802,26 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital européen Georges-Pompidou (Paris)</t>
+          <t>HOPITAL PARIS SAINT-JOSEPH (GHPSJ - Maternité Notre-Dame de Bon Secours) (PARIS)</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2056-establishment5791</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3228-establishment6803</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Plateau Technique non invasif (Explorations non invasives cardio-vasculaires)</t>
+          <t>CARDIOLOGIE</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Dr DORRA M'BAREK RABOUDI</t>
+          <t>Dr Romain CADOR</t>
         </is>
       </c>
       <c r="G324" t="inlineStr"/>
-      <c r="H324" s="2" t="inlineStr">
-        <is>
-          <t>Sophie.maraval@egp.aphp.fr</t>
-        </is>
-      </c>
+      <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -13865,12 +13841,12 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>AP-HP Groupe Hospitalier Saint-Louis, Lariboisière, Fernand-Widal Site Saint Louis (Paris)</t>
+          <t>Hôpital Hôpital Saint Antoine (Paris)</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2044-establishment5779</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2034-establishment5772</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -13880,13 +13856,13 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Dr BENJAMIN SIBILIA</t>
+          <t>Dr CLEMENT DARRICAUD</t>
         </is>
       </c>
       <c r="G325" t="inlineStr"/>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>nolwenn.jacob@aphp.fr</t>
+          <t>choella.akbaraly@aphp.fr</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -13908,26 +13884,26 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>HOPITAL PARIS SAINT-JOSEPH (GHPSJ - Maternité Notre-Dame de Bon Secours) (PARIS)</t>
+          <t>Hôpital Hôpital Saint Antoine (Paris)</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3228-establishment6803</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2034-establishment5772</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>Dr Romain CADOR</t>
-        </is>
-      </c>
+          <t>Soins intensifs de cardiologie</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr"/>
-      <c r="H326" t="inlineStr"/>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
       <c r="I326" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -13947,28 +13923,28 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Hôpital Hôpital Saint Antoine (Paris)</t>
+          <t>AP-HP Hôpital Necker - Enfants Malades (Paris)</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2034-establishment5772</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2053-establishment5788</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie pédiatrique</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Dr CLEMENT DARRICAUD</t>
+          <t>JULES ADER</t>
         </is>
       </c>
       <c r="G327" t="inlineStr"/>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>choella.akbaraly@aphp.fr</t>
+          <t>marie.Ayoub@aphp.fr</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -13990,24 +13966,28 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Hôpital Hôpital Saint Antoine (Paris)</t>
+          <t>AP-HP Hôpital Necker - Enfants Malades (Paris)</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2034-establishment5772</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2053-establishment5788</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Soins intensifs de cardiologie</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr"/>
+          <t>Hôpital de jour de cardiologie pédiatrique</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Pr DAMIEN BONNET</t>
+        </is>
+      </c>
       <c r="G328" t="inlineStr"/>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>choella.akbaraly@aphp.fr</t>
+          <t>marie.Ayoub@aphp.fr</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -14039,12 +14019,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Cardiologie pédiatrique</t>
+          <t>Unité Fonctionnelle de Cardiologie Adulte</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>JULES ADER</t>
+          <t>Pr Eloi MARIJON</t>
         </is>
       </c>
       <c r="G329" t="inlineStr"/>
@@ -14072,28 +14052,28 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Necker - Enfants Malades (Paris)</t>
+          <t>AP-HP Hôpital Tenon (Paris)</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2053-establishment5788</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2055-establishment5790</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Hôpital de jour de cardiologie pédiatrique</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Pr DAMIEN BONNET</t>
+          <t>Pr ARON ARIEL COHEN</t>
         </is>
       </c>
       <c r="G330" t="inlineStr"/>
       <c r="H330" s="2" t="inlineStr">
         <is>
-          <t>marie.Ayoub@aphp.fr</t>
+          <t>choella.akbaraly@aphp.fr</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -14115,28 +14095,28 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Necker - Enfants Malades (Paris)</t>
+          <t>AP-HP Hôpital universitaire Robert-Debré (Paris)</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2053-establishment5788</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2039-establishment5776</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Unité Fonctionnelle de Cardiologie Adulte</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Pr Eloi MARIJON</t>
+          <t>Dr BASTIEN MOYSSET</t>
         </is>
       </c>
       <c r="G331" t="inlineStr"/>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>marie.Ayoub@aphp.fr</t>
+          <t>nolwenn.jacob@aphp.fr</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -14158,30 +14138,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Tenon (Paris)</t>
+          <t>HOPITAL HOPITAL LEOPOLD BELLAN (PARIS)</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2055-establishment5790</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3238-establishment7346</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>Pr ARON ARIEL COHEN</t>
-        </is>
-      </c>
+          <t>UNITE DE READAPTATION CARDIO-VASCULAIRE</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr"/>
-      <c r="H332" s="2" t="inlineStr">
-        <is>
-          <t>choella.akbaraly@aphp.fr</t>
-        </is>
-      </c>
+      <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14201,30 +14173,26 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital universitaire Robert-Debré (Paris)</t>
+          <t>Hôpital Hôtel Dieu (AP-HP) (Paris)</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2039-establishment5776</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2041-establishment5777</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>HTA cardiologie</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Dr BASTIEN MOYSSET</t>
+          <t>ELEONORE SOTTO</t>
         </is>
       </c>
       <c r="G333" t="inlineStr"/>
-      <c r="H333" s="2" t="inlineStr">
-        <is>
-          <t>nolwenn.jacob@aphp.fr</t>
-        </is>
-      </c>
+      <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14234,27 +14202,27 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Seine-Maritime</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>HOPITAL HOPITAL LEOPOLD BELLAN (PARIS)</t>
+          <t>Hôpital Charles-Nicolle (Rouen)</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3238-establishment7346</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2057-establishment1353</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>UNITE DE READAPTATION CARDIO-VASCULAIRE</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F334" t="inlineStr"/>
@@ -14269,34 +14237,30 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Seine-Maritime</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Hôpital Hôtel Dieu (AP-HP) (Paris)</t>
+          <t>Hôpital Charles-Nicolle (Rouen)</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2041-establishment5777</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2057-establishment1353</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>HTA cardiologie</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>ELEONORE SOTTO</t>
-        </is>
-      </c>
+          <t>Service de Chirurgie Thoracique et cardio-vasculaire</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr">
@@ -14318,12 +14282,12 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Hôpital Charles-Nicolle (Rouen)</t>
+          <t>Centre Hospitalier Intercommunal Elbeuf-Louviers/Val de Reuil (ELBEUF)</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2057-establishment1353</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2098-establishment5829</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -14331,8 +14295,16 @@
           <t>Cardiologie</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Dr Fabian TOURNEVACHE</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>fabian.tournevache@chi-elbeuf-louviers.fr</t>
+        </is>
+      </c>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr">
         <is>
@@ -14353,22 +14325,34 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Hôpital Charles-Nicolle (Rouen)</t>
+          <t>Groupe Hospitalier du Havre Hôpital Jacques Monod (MONTIVILLIERS)</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2057-establishment1353</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2059-establishment3306</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Service de Chirurgie Thoracique et cardio-vasculaire</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr"/>
-      <c r="G337" t="inlineStr"/>
-      <c r="H337" t="inlineStr"/>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Dr Emmanuel LECLUSE</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>emmanuel.lecluse@ch-havre.fr</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>melanie.couturier@ch-havre.fr</t>
+        </is>
+      </c>
       <c r="I337" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14388,30 +14372,34 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Intercommunal Elbeuf-Louviers/Val de Reuil (ELBEUF)</t>
+          <t>Groupe Hospitalier du Havre Hôpital Jacques Monod (MONTIVILLIERS)</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2098-establishment5829</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2059-establishment3306</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>SSR cardio-respiratoire (HC et HDJ)</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Dr Fabian TOURNEVACHE</t>
+          <t>Dr Emmanuel LECLUSE</t>
         </is>
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>fabian.tournevache@chi-elbeuf-louviers.fr</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr"/>
+          <t>emmanuel.lecluse@ch-havre.fr</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>melanie.couturier@ch-havre.fr</t>
+        </is>
+      </c>
       <c r="I338" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14431,32 +14419,32 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Groupe Hospitalier du Havre Hôpital Jacques Monod (MONTIVILLIERS)</t>
+          <t>CENTRE HOSPITALIER DE DIEPPE : Site Pasteur (Dieppe)</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2059-establishment3306</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2071-establishment5802</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>CARDIOLOGIE ET UNITE DE SOINS INTENSIFS CARDIOLOGIQUES</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Dr Emmanuel LECLUSE</t>
+          <t>Dr Carole HUCHE</t>
         </is>
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>emmanuel.lecluse@ch-havre.fr</t>
+          <t>chuche@ch-dieppe.fr</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
-          <t>melanie.couturier@ch-havre.fr</t>
+          <t>rdubuisson@ch-dieppe.fr</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -14478,34 +14466,30 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Groupe Hospitalier du Havre Hôpital Jacques Monod (MONTIVILLIERS)</t>
+          <t>Centre Hospitalier Intercommunal (FECAMP)</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2059-establishment3306</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2089-establishment5820</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>SSR cardio-respiratoire (HC et HDJ)</t>
+          <t>Médecine à orientation cardiologique</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Dr Emmanuel LECLUSE</t>
+          <t>Dr Philippe CALOT</t>
         </is>
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>emmanuel.lecluse@ch-havre.fr</t>
-        </is>
-      </c>
-      <c r="H340" s="2" t="inlineStr">
-        <is>
-          <t>melanie.couturier@ch-havre.fr</t>
-        </is>
-      </c>
+          <t>philippe.calot@ch-fecamp.fr</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14515,44 +14499,40 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Seine-Maritime</t>
+          <t>Seine-et-Marne</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER DE DIEPPE : Site Pasteur (Dieppe)</t>
+          <t>Grand Hôpital de l'Est Francilien (JOSSIGNY)</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2071-establishment5802</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5865</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE ET UNITE DE SOINS INTENSIFS CARDIOLOGIQUES</t>
+          <t>Cardiologie - USIC - HDJ - HDS - Explorations fonctionnelles cardiologiques - MLV</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Dr Carole HUCHE</t>
+          <t>Dr Simon ELHADAD</t>
         </is>
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>chuche@ch-dieppe.fr</t>
-        </is>
-      </c>
-      <c r="H341" s="2" t="inlineStr">
-        <is>
-          <t>rdubuisson@ch-dieppe.fr</t>
-        </is>
-      </c>
+          <t>mgerber@ghef.fr</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14562,39 +14542,35 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Seine-Maritime</t>
+          <t>Seine-et-Marne</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Intercommunal (FECAMP)</t>
+          <t>Grand Hôpital de l'Est Francilien (JOSSIGNY)</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2089-establishment5820</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5865</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Médecine à orientation cardiologique</t>
+          <t>Unité de cardiologie du sport - MLV</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Dr Philippe CALOT</t>
-        </is>
-      </c>
-      <c r="G342" s="2" t="inlineStr">
-        <is>
-          <t>philippe.calot@ch-fecamp.fr</t>
-        </is>
-      </c>
+          <t>Dr Simon ELHADAD</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr"/>
       <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr">
         <is>
@@ -14615,27 +14591,27 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Grand Hôpital de l'Est Francilien (JOSSIGNY)</t>
+          <t>Hôpital de Melun-Sénart - Groupe hospitalier Sud Ile-de-France (Melun)</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5865</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2117-establishment10636</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Cardiologie - USIC - HDJ - HDS - Explorations fonctionnelles cardiologiques - MLV</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Dr Simon ELHADAD</t>
+          <t>Dr Cyrus MOINI</t>
         </is>
       </c>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>mgerber@ghef.fr</t>
+          <t>cyrus.moini@ghsif.fr</t>
         </is>
       </c>
       <c r="H343" t="inlineStr"/>
@@ -14658,22 +14634,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Grand Hôpital de l'Est Francilien (JOSSIGNY)</t>
+          <t>Grand Hôpital de l'Est Francilien (MEAUX)</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5865</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5849</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Unité de cardiologie du sport - MLV</t>
+          <t>Cardiologie - USIC - Explorations fonctionnelles cardiologiques - MX</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Dr Simon ELHADAD</t>
+          <t>Dr Sergio PERNA</t>
         </is>
       </c>
       <c r="G344" t="inlineStr"/>
@@ -14697,29 +14673,25 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Hôpital de Melun-Sénart - Groupe hospitalier Sud Ile-de-France (Melun)</t>
+          <t>Grand Hôpital de l'Est Francilien (COULOMMIERS)</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2117-establishment10636</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5872</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie - Explorations fonctionnelles cardiologiques - CLM</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Dr Cyrus MOINI</t>
-        </is>
-      </c>
-      <c r="G345" s="2" t="inlineStr">
-        <is>
-          <t>cyrus.moini@ghsif.fr</t>
-        </is>
-      </c>
+          <t>Dr Simon ELHADAD</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr"/>
       <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr">
         <is>
@@ -14740,25 +14712,29 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Grand Hôpital de l'Est Francilien (MEAUX)</t>
+          <t>Centre hospitalier Léon Binet (Provins)</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5849</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2140-establishment5869</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Cardiologie - USIC - Explorations fonctionnelles cardiologiques - MX</t>
+          <t>Cardiologie et maladies vasculaires</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Dr Sergio PERNA</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr"/>
+          <t>Dr Farid TAOURI</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>ehaddad@ch-provins.fr</t>
+        </is>
+      </c>
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr">
         <is>
@@ -14779,24 +14755,20 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Grand Hôpital de l'Est Francilien (COULOMMIERS)</t>
+          <t>Site hospitalier de Fontainebleau (FONTAINEBLEAU)</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5872</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2132-establishment5861</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Cardiologie - Explorations fonctionnelles cardiologiques - CLM</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>Dr Simon ELHADAD</t>
-        </is>
-      </c>
+          <t>Médecine A-B (neurologie - cardiologie)</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr"/>
       <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr">
@@ -14818,27 +14790,27 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Centre hospitalier Léon Binet (Provins)</t>
+          <t>Site de Montereau-Fault-Yonne (MONTEREAU FAUT YONNE)</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2140-establishment5869</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2132-establishment5884</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Cardiologie et maladies vasculaires</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Dr Farid TAOURI</t>
+          <t>Dr Adama SANGARE</t>
         </is>
       </c>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>ehaddad@ch-provins.fr</t>
+          <t>adama.sangare@ch-montereau.fr</t>
         </is>
       </c>
       <c r="H348" t="inlineStr"/>
@@ -14851,32 +14823,44 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Seine-et-Marne</t>
+          <t>Yvelines</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Site hospitalier de Fontainebleau (FONTAINEBLEAU)</t>
+          <t>Centre hospitalier intercommunal de Poissy-Saint-Germain-en-Laye &gt; Site hospitalier de Poissy (POISSY)</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2132-establishment5861</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2163-establishment2557</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Médecine A-B (neurologie - cardiologie)</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr"/>
-      <c r="G349" t="inlineStr"/>
-      <c r="H349" t="inlineStr"/>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Dr David BERVILLE</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>david.berville@ght-yvelinesnord.fr</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>agathe.benoist@ght-yvelinesnord.fr</t>
+        </is>
+      </c>
       <c r="I349" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14886,22 +14870,22 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Seine-et-Marne</t>
+          <t>Yvelines</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Site de Montereau-Fault-Yonne (MONTEREAU FAUT YONNE)</t>
+          <t>Hôpital André Mignot Centre Hospitalier de Versailles (Le Chesnay)</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2132-establishment5884</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2165-establishment5893</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -14911,12 +14895,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Dr Adama SANGARE</t>
+          <t>Dr Geraldine GIBAULT GENTY</t>
         </is>
       </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>adama.sangare@ch-montereau.fr</t>
+          <t>ggibaultgenty@ght78sud.fr</t>
         </is>
       </c>
       <c r="H350" t="inlineStr"/>
@@ -14939,12 +14923,12 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Centre hospitalier intercommunal de Poissy-Saint-Germain-en-Laye &gt; Site hospitalier de Poissy (POISSY)</t>
+          <t>Centre hospitalier François Quesnay (Mantes-la-Jolie)</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2163-establishment2557</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2166-establishment5894</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -14986,27 +14970,27 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Hôpital André Mignot Centre Hospitalier de Versailles (Le Chesnay)</t>
+          <t>Centre hospitalier (RAMBOUILLET)</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2165-establishment5893</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2179-establishment5908</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie-Pneumologie-USIC</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Dr Geraldine GIBAULT GENTY</t>
+          <t>Dr Christophe CHAVELAS</t>
         </is>
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>ggibaultgenty@ght78sud.fr</t>
+          <t>cchavelas@ght78sud.fr</t>
         </is>
       </c>
       <c r="H352" t="inlineStr"/>
@@ -15029,34 +15013,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Centre hospitalier François Quesnay (Mantes-la-Jolie)</t>
+          <t>Etablissement SSR et Institut de Néphrologie de Maisons-Laffitte Groupe MGEN (Maisons-Laffitte)</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2166-establishment5894</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3220-establishment8546</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>Dr David BERVILLE</t>
-        </is>
-      </c>
-      <c r="G353" s="2" t="inlineStr">
-        <is>
-          <t>david.berville@ght-yvelinesnord.fr</t>
-        </is>
-      </c>
-      <c r="H353" s="2" t="inlineStr">
-        <is>
-          <t>agathe.benoist@ght-yvelinesnord.fr</t>
-        </is>
-      </c>
+          <t>Service de SSR Cardiologie-Néphrologie-Polyvalents</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15076,27 +15048,27 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Centre hospitalier (RAMBOUILLET)</t>
+          <t>Centre hospitalier intercommunal de Poissy-Saint-Germain-en-Laye &gt; Site hospitalier de Saint-Germain-en-Laye (SAINT-GERMAIN-EN-LAYE)</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2179-establishment5908</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2163-establishment5891</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Cardiologie-Pneumologie-USIC</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Dr Christophe CHAVELAS</t>
+          <t>Dr David BERVILLE</t>
         </is>
       </c>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>cchavelas@ght78sud.fr</t>
+          <t>david.berville@ght-yvelinesnord.fr</t>
         </is>
       </c>
       <c r="H354" t="inlineStr"/>
@@ -15109,32 +15081,36 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Yvelines</t>
+          <t>Deux-Sèvres</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Etablissement SSR et Institut de Néphrologie de Maisons-Laffitte Groupe MGEN (Maisons-Laffitte)</t>
+          <t>Centre hospitalier (Niort)</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3220-establishment8546</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2190-establishment5917</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Service de SSR Cardiologie-Néphrologie-Polyvalents</t>
+          <t>Cardiologie et Explorations Cardiovasculaires</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr"/>
-      <c r="H355" t="inlineStr"/>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>karine.morin@ch-niort.fr</t>
+        </is>
+      </c>
       <c r="I355" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15144,22 +15120,22 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Yvelines</t>
+          <t>Somme</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Centre hospitalier intercommunal de Poissy-Saint-Germain-en-Laye &gt; Site hospitalier de Saint-Germain-en-Laye (SAINT-GERMAIN-EN-LAYE)</t>
+          <t>CHU Amiens Picardie - Site Sud (Amiens)</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2163-establishment5891</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2224-establishment1360</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -15167,16 +15143,8 @@
           <t>Cardiologie</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>Dr David BERVILLE</t>
-        </is>
-      </c>
-      <c r="G356" s="2" t="inlineStr">
-        <is>
-          <t>david.berville@ght-yvelinesnord.fr</t>
-        </is>
-      </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr"/>
       <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr">
         <is>
@@ -15187,36 +15155,32 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Deux-Sèvres</t>
+          <t>Somme</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Niort)</t>
+          <t>CHU Amiens Picardie - Site Sud (Amiens)</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2190-establishment5917</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2224-establishment1360</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Cardiologie et Explorations Cardiovasculaires</t>
+          <t>Cardiologie et Pneumo-Allergologie Pédiatriques</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr"/>
-      <c r="H357" s="2" t="inlineStr">
-        <is>
-          <t>karine.morin@ch-niort.fr</t>
-        </is>
-      </c>
+      <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15246,7 +15210,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie, Rythmologie et Stimulation Cardiaque</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
@@ -15281,10 +15245,14 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Cardiologie et Pneumo-Allergologie Pédiatriques</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr"/>
+          <t>Réanimation Médico-Chirurgicale Cardio Thoracique Vasculaire et Respiratoire</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Pr Hervé DUPONT</t>
+        </is>
+      </c>
       <c r="G359" t="inlineStr"/>
       <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr">
@@ -15316,7 +15284,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Cardiologie, Rythmologie et Stimulation Cardiaque</t>
+          <t>Unité de Soins Intensifs de Cardiologie (USIC)</t>
         </is>
       </c>
       <c r="F360" t="inlineStr"/>
@@ -15341,25 +15309,29 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>CHU Amiens Picardie - Site Sud (Amiens)</t>
+          <t>Centre hospitalier (Abbeville)</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2224-establishment1360</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2230-establishment5957</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Réanimation Médico-Chirurgicale Cardio Thoracique Vasculaire et Respiratoire</t>
+          <t>Médecine cardiologique - USIC</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Pr Hervé DUPONT</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr"/>
+          <t>Dr Vincent MOUQUET</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>hautbout.karine@ch-abbeville.fr</t>
+        </is>
+      </c>
       <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr">
         <is>
@@ -15380,21 +15352,29 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>CHU Amiens Picardie - Site Sud (Amiens)</t>
+          <t>Centre hospitalier (Abbeville)</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2224-establishment1360</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2230-establishment5957</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Unité de Soins Intensifs de Cardiologie (USIC)</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr"/>
-      <c r="G362" t="inlineStr"/>
+          <t>Soins de suite et de réadaptation cardio-respiratoires</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Dr Olivier LELEU</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>hautbout.karine@ch-abbeville.fr</t>
+        </is>
+      </c>
       <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr">
         <is>
@@ -15415,27 +15395,27 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Abbeville)</t>
+          <t>Centre hospitalier (Corbie)</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2230-establishment5957</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2258-establishment5983</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Médecine cardiologique - USIC</t>
+          <t>SSR - Réadaptation cardio-vasculaire</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Dr Vincent MOUQUET</t>
+          <t>Dr Florent KRIM</t>
         </is>
       </c>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>hautbout.karine@ch-abbeville.fr</t>
+          <t>cardiovasculaire@ch-corbie.fr</t>
         </is>
       </c>
       <c r="H363" t="inlineStr"/>
@@ -15448,39 +15428,31 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Somme</t>
+          <t>Tarn</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Abbeville)</t>
+          <t>HOPITAL DU PAYS d'AUTAN - Site de Castres (Castres)</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2230-establishment5957</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2261-establishment5986</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Soins de suite et de réadaptation cardio-respiratoires</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>Dr Olivier LELEU</t>
-        </is>
-      </c>
-      <c r="G364" s="2" t="inlineStr">
-        <is>
-          <t>hautbout.karine@ch-abbeville.fr</t>
-        </is>
-      </c>
+          <t>CARDIOLOGIE</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr">
         <is>
@@ -15491,39 +15463,31 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Somme</t>
+          <t>Tarn</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Corbie)</t>
+          <t>HOPITAL DU PAYS d'AUTAN - Site de Castres (Castres)</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2258-establishment5983</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2261-establishment5986</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>SSR - Réadaptation cardio-vasculaire</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>Dr Florent KRIM</t>
-        </is>
-      </c>
-      <c r="G365" s="2" t="inlineStr">
-        <is>
-          <t>cardiovasculaire@ch-corbie.fr</t>
-        </is>
-      </c>
+          <t>CARDIOLOGIE et USIC</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr"/>
       <c r="I365" t="inlineStr">
         <is>
@@ -15544,22 +15508,26 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>HOPITAL DU PAYS d'AUTAN - Site de Castres (Castres)</t>
+          <t>Centre hospitalier (Albi)</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2261-establishment5986</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2260-establishment5985</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F366" t="inlineStr"/>
       <c r="G366" t="inlineStr"/>
-      <c r="H366" t="inlineStr"/>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>jeremy.luceno@ch-albi.fr</t>
+        </is>
+      </c>
       <c r="I366" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15569,32 +15537,44 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Tarn</t>
+          <t>Tarn-et-Garonne</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>HOPITAL DU PAYS d'AUTAN - Site de Castres (Castres)</t>
+          <t>Centre Hospitalier Général (MONTAUBAN)</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2261-establishment5986</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2269-establishment5994</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE et USIC</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr"/>
-      <c r="G367" t="inlineStr"/>
-      <c r="H367" t="inlineStr"/>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Dr Nouredinne EL HAJJAJI</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>n.elhajjaji@ch-montauban.fr</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>secretariat-dsqgr@ch-montauban.fr</t>
+        </is>
+      </c>
       <c r="I367" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15604,34 +15584,42 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Tarn</t>
+          <t>Tarn-et-Garonne</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Albi)</t>
+          <t>Centre Hospitalier Général (MONTAUBAN)</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2260-establishment5985</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2269-establishment5994</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr"/>
+          <t>Soins Intensifs Neuro-Cardio-Vasculaires</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Dr Nouredinne EL HAJJAJI</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>n.elhajjaji@ch-montauban.fr</t>
+        </is>
+      </c>
       <c r="H368" s="2" t="inlineStr">
         <is>
-          <t>jeremy.luceno@ch-albi.fr</t>
+          <t>secretariat-dsqgr@ch-montauban.fr</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -15643,42 +15631,42 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Tarn-et-Garonne</t>
+          <t>Var</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Général (MONTAUBAN)</t>
+          <t>C.H.I.T.S. Hôpital Sainte Musse (Toulon)</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2269-establishment5994</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2284-establishment2219</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie A</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Dr Nouredinne EL HAJJAJI</t>
+          <t>Dr Jean-Michel TARTIERE</t>
         </is>
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>n.elhajjaji@ch-montauban.fr</t>
+          <t>jean-michel.tartiere@ch-toulon.fr</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
         <is>
-          <t>secretariat-dsqgr@ch-montauban.fr</t>
+          <t>Corentin.Balluais@ch-toulon.fr</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -15690,42 +15678,42 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Tarn-et-Garonne</t>
+          <t>Var</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Général (MONTAUBAN)</t>
+          <t>C.H.I.T.S. Hôpital Sainte Musse (Toulon)</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2269-establishment5994</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2284-establishment2219</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Soins Intensifs Neuro-Cardio-Vasculaires</t>
+          <t>Unité de Soins intensifs cardiologiques (USIC)</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Dr Nouredinne EL HAJJAJI</t>
+          <t>Dr Farid CHALLAL</t>
         </is>
       </c>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>n.elhajjaji@ch-montauban.fr</t>
+          <t>farid.challal@ch-toulon.fr</t>
         </is>
       </c>
       <c r="H370" s="2" t="inlineStr">
         <is>
-          <t>secretariat-dsqgr@ch-montauban.fr</t>
+          <t>Corentin.Balluais@ch-toulon.fr</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -15747,34 +15735,30 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>C.H.I.T.S. Hôpital Sainte Musse (Toulon)</t>
+          <t>Centre Hospitalier Intercommunal (FREJUS)</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2284-establishment2219</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2302-establishment6026</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Cardiologie A</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Dr Jean-Michel TARTIERE</t>
+          <t>Dr Hélène ZAKARIAN</t>
         </is>
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>jean-michel.tartiere@ch-toulon.fr</t>
-        </is>
-      </c>
-      <c r="H371" s="2" t="inlineStr">
-        <is>
-          <t>Corentin.Balluais@ch-toulon.fr</t>
-        </is>
-      </c>
+          <t>zakarian-h@chi-fsr.fr</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr"/>
       <c r="I371" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15794,34 +15778,30 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>C.H.I.T.S. Hôpital Sainte Musse (Toulon)</t>
+          <t>Hôpital National d'Instruction des armées SAINTE ANNE (TOULON)</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2284-establishment2219</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8042</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Unité de Soins intensifs cardiologiques (USIC)</t>
+          <t>CARDIOLOGIE ET MALADIES VASCULAIRES HIA Sainte-Anne</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Dr Farid CHALLAL</t>
+          <t>Pr Gilles CELLARIER</t>
         </is>
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>farid.challal@ch-toulon.fr</t>
-        </is>
-      </c>
-      <c r="H372" s="2" t="inlineStr">
-        <is>
-          <t>Corentin.Balluais@ch-toulon.fr</t>
-        </is>
-      </c>
+          <t>cardiologie@hia-sainte-anne.ssa.msante.fr</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15841,12 +15821,12 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Intercommunal (FREJUS)</t>
+          <t>Centre Hospitalier de la Dracénie (Draguignan)</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2302-establishment6026</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2283-establishment6008</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -15854,16 +15834,8 @@
           <t>Cardiologie</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>Dr Hélène ZAKARIAN</t>
-        </is>
-      </c>
-      <c r="G373" s="2" t="inlineStr">
-        <is>
-          <t>zakarian-h@chi-fsr.fr</t>
-        </is>
-      </c>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr">
         <is>
@@ -15884,27 +15856,27 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Hôpital National d'Instruction des armées SAINTE ANNE (TOULON)</t>
+          <t>HCL Hôpital Renée Sabran (Giens)</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8042</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2294-establishment6018</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE ET MALADIES VASCULAIRES HIA Sainte-Anne</t>
+          <t>Consultations Cardiologie</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Pr Gilles CELLARIER</t>
+          <t>Mme Daniele RAUFAST</t>
         </is>
       </c>
       <c r="G374" s="2" t="inlineStr">
         <is>
-          <t>cardiologie@hia-sainte-anne.ssa.msante.fr</t>
+          <t>daniele.raufast@chu-lyon.fr</t>
         </is>
       </c>
       <c r="H374" t="inlineStr"/>
@@ -15917,22 +15889,22 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Var</t>
+          <t>Vaucluse</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de la Dracénie (Draguignan)</t>
+          <t>Centre Hospitalier Henri Duffaut (Avignon)</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2283-establishment6008</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2347-establishment6067</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -15942,7 +15914,11 @@
       </c>
       <c r="F375" t="inlineStr"/>
       <c r="G375" t="inlineStr"/>
-      <c r="H375" t="inlineStr"/>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>baratier.aurelie@ch-avignon.fr</t>
+        </is>
+      </c>
       <c r="I375" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15952,40 +15928,44 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Var</t>
+          <t>Vaucluse</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>HCL Hôpital Renée Sabran (Giens)</t>
+          <t>Centre hospitalier intercommunal de Cavaillon - Lauris (Cavaillon)</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2294-establishment6018</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2329-establishment6052</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Consultations Cardiologie</t>
+          <t>Service de médecine A - Cardiologie</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Mme Daniele RAUFAST</t>
+          <t>Dr Patrick GIRAUD</t>
         </is>
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>daniele.raufast@chu-lyon.fr</t>
-        </is>
-      </c>
-      <c r="H376" t="inlineStr"/>
+          <t>p.giraud@ch-cavaillon.fr</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>anne.desroche@ch-cavaillon.fr</t>
+        </is>
+      </c>
       <c r="I376" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15995,22 +15975,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Vaucluse</t>
+          <t>Vendée</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Henri Duffaut (Avignon)</t>
+          <t>Centre Hospitalier Départemental Vendée, site de La Roche-sur-Yon (La Roche-sur-Yon)</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2347-establishment6067</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2349-establishment6069</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -16020,11 +16000,7 @@
       </c>
       <c r="F377" t="inlineStr"/>
       <c r="G377" t="inlineStr"/>
-      <c r="H377" s="2" t="inlineStr">
-        <is>
-          <t>baratier.aurelie@ch-avignon.fr</t>
-        </is>
-      </c>
+      <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16034,44 +16010,36 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Vaucluse</t>
+          <t>Vendée</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Centre hospitalier intercommunal de Cavaillon - Lauris (Cavaillon)</t>
+          <t>Centre Hospitalier Côte de Lumière (LES SABLES D'OLONNE)</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2329-establishment6052</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2352-establishment6071</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Service de médecine A - Cardiologie</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Dr Patrick GIRAUD</t>
-        </is>
-      </c>
-      <c r="G378" s="2" t="inlineStr">
-        <is>
-          <t>p.giraud@ch-cavaillon.fr</t>
-        </is>
-      </c>
-      <c r="H378" s="2" t="inlineStr">
-        <is>
-          <t>anne.desroche@ch-cavaillon.fr</t>
-        </is>
-      </c>
+          <t>Dr Claire BOIVINEAU</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16091,20 +16059,24 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Départemental Vendée, site de La Roche-sur-Yon (La Roche-sur-Yon)</t>
+          <t>Centre Hospitalier Côte de Lumière (LES SABLES D'OLONNE)</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2349-establishment6069</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2352-establishment6071</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr"/>
+          <t>Unité de Soins Intensifs de Cardiologie (USIC)</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Dr Patrice PERNOLLET</t>
+        </is>
+      </c>
       <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr">
@@ -16126,12 +16098,12 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Côte de Lumière (LES SABLES D'OLONNE)</t>
+          <t>Centre Hospitalier Loire Vendée Océan - site de Challans (CHALLANS)</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2352-establishment6071</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2365-establishment6082</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -16139,11 +16111,7 @@
           <t>Cardiologie</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>Dr Claire BOIVINEAU</t>
-        </is>
-      </c>
+      <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr">
@@ -16165,26 +16133,26 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Côte de Lumière (LES SABLES D'OLONNE)</t>
+          <t>Centre hospitalier (FONTENAY LE COMTE)</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2352-establishment6071</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2356-establishment6075</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Unité de Soins Intensifs de Cardiologie (USIC)</t>
-        </is>
-      </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>Dr Patrice PERNOLLET</t>
-        </is>
-      </c>
+          <t>Cardiologie et neuro-vasculaire</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr"/>
       <c r="G381" t="inlineStr"/>
-      <c r="H381" t="inlineStr"/>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>corentin.ringot@ght85.fr</t>
+        </is>
+      </c>
       <c r="I381" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16194,32 +16162,44 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Vendée</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Loire Vendée Océan - site de Challans (CHALLANS)</t>
+          <t>Site hospitalier de Poitiers La Miletrie (Poitiers)</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2365-establishment6082</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment1364</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F382" t="inlineStr"/>
-      <c r="G382" t="inlineStr"/>
-      <c r="H382" t="inlineStr"/>
+          <t>Chirurgie cardio-thoracique</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Pr Pierre CORBI</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>pierre.corbi@chu-poitiers.fr</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>heloise.baux@chu-poitiers.fr</t>
+        </is>
+      </c>
       <c r="I382" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16229,34 +16209,42 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Vendée</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Centre hospitalier (FONTENAY LE COMTE)</t>
+          <t>Site hospitalier de Poitiers La Miletrie (Poitiers)</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2356-establishment6075</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment1364</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Cardiologie et neuro-vasculaire</t>
-        </is>
-      </c>
-      <c r="F383" t="inlineStr"/>
-      <c r="G383" t="inlineStr"/>
+          <t>Service médico-chirurgical de Cardiologie</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Pr Luc-Philippe CHRISTIAENS</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>luc-philippe.christiaens@chu-poitiers.fr</t>
+        </is>
+      </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>corentin.ringot@ght85.fr</t>
+          <t>heloise.baux@chu-poitiers.fr</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -16278,34 +16266,30 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Site hospitalier de Poitiers La Miletrie (Poitiers)</t>
+          <t>Site hospitalier de Châtellerault (Chatellerault)</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment1364</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment6093</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Chirurgie cardio-thoracique</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Pr Pierre CORBI</t>
+          <t>Dr Damien COISNE</t>
         </is>
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>pierre.corbi@chu-poitiers.fr</t>
-        </is>
-      </c>
-      <c r="H384" s="2" t="inlineStr">
-        <is>
-          <t>heloise.baux@chu-poitiers.fr</t>
-        </is>
-      </c>
+          <t>cardiologie@ghnv.fr</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr"/>
       <c r="I384" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16325,34 +16309,30 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Site hospitalier de Poitiers La Miletrie (Poitiers)</t>
+          <t>Site hospitalier de Montmorillon (Montmorillon)</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment1364</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment6098</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Service médico-chirurgical de Cardiologie</t>
+          <t>Médecine générale - Cardiologie - Rhumatologie - Angiologie - Diabétologie/endocrinologie - Douleur</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Pr Luc-Philippe CHRISTIAENS</t>
+          <t>Dr Jean-Claude LORENZO</t>
         </is>
       </c>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>luc-philippe.christiaens@chu-poitiers.fr</t>
-        </is>
-      </c>
-      <c r="H385" s="2" t="inlineStr">
-        <is>
-          <t>heloise.baux@chu-poitiers.fr</t>
-        </is>
-      </c>
+          <t>jean-claude.lorenzo@ch-montmorillon.fr</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16362,22 +16342,22 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Haute-Vienne</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Site hospitalier de Châtellerault (Chatellerault)</t>
+          <t>CHU Dupuytren 1 (Limoges)</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment6093</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2386-establishment1372</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -16387,14 +16367,10 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Dr Damien COISNE</t>
-        </is>
-      </c>
-      <c r="G386" s="2" t="inlineStr">
-        <is>
-          <t>cardiologie@ghnv.fr</t>
-        </is>
-      </c>
+          <t>Pr Victor ABOYANS</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr">
         <is>
@@ -16405,40 +16381,36 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Vosges</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Site hospitalier de Montmorillon (Montmorillon)</t>
+          <t>Centre hospitalier Nouvel Hôpital d'Epinal - plateau de la justice (Epinal)</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment6098</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2413-establishment6126</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Médecine générale - Cardiologie - Rhumatologie - Angiologie - Diabétologie/endocrinologie - Douleur</t>
-        </is>
-      </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>Dr Jean-Claude LORENZO</t>
-        </is>
-      </c>
-      <c r="G387" s="2" t="inlineStr">
-        <is>
-          <t>jean-claude.lorenzo@ch-montmorillon.fr</t>
-        </is>
-      </c>
-      <c r="H387" t="inlineStr"/>
+          <t>Cardiologie USIC Plateau Technique</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>sec.direction@ch-ed.fr</t>
+        </is>
+      </c>
       <c r="I387" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16448,36 +16420,36 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Haute-Vienne</t>
+          <t>Vosges</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>CHU Dupuytren 1 (Limoges)</t>
+          <t>Centre hospitalier Nouvel Hôpital d'Epinal - plateau de la justice (Epinal)</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2386-establishment1372</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2413-establishment6126</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>Pr Victor ABOYANS</t>
-        </is>
-      </c>
+          <t>Unité de Soins Intensifs de Cardiologie</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr"/>
-      <c r="H388" t="inlineStr"/>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>sec.direction@ch-ed.fr</t>
+        </is>
+      </c>
       <c r="I388" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16497,24 +16469,24 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Centre hospitalier Nouvel Hôpital d'Epinal - plateau de la justice (Epinal)</t>
+          <t>Centre hospitalier (Remiremont)</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2413-establishment6126</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2425-establishment6138</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Cardiologie USIC Plateau Technique</t>
+          <t>Médecine orientation Cardiologie</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr"/>
       <c r="H389" s="2" t="inlineStr">
         <is>
-          <t>sec.direction@ch-ed.fr</t>
+          <t>helene.marion@ch-remiremont.fr</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -16536,24 +16508,32 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Centre hospitalier Nouvel Hôpital d'Epinal - plateau de la justice (Epinal)</t>
+          <t>Site Hospitalier de Neufchâteau Siège Social (Neufchâteau)</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2413-establishment6126</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2435-establishment6148</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Unité de Soins Intensifs de Cardiologie</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr"/>
-      <c r="G390" t="inlineStr"/>
+          <t>CARDIOLOGIE ET SOINS INTENSIFS CARDIAQUES</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Dr Jean-Louis MEREGNANI</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>jl.meregnani@ch-ouestvosgien.fr</t>
+        </is>
+      </c>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>sec.direction@ch-ed.fr</t>
+          <t>e.andrique@ch-ouestvosgien.fr</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -16565,36 +16545,32 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Vosges</t>
+          <t>Yonne</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Remiremont)</t>
+          <t>Centre hospitalier Centre hospitalier d'Auxerre (Auxerre)</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2425-establishment6138</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2462-establishment6170</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Médecine orientation Cardiologie</t>
+          <t>Cardiologie et unité de soins intensifs cardiologiques</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr"/>
-      <c r="H391" s="2" t="inlineStr">
-        <is>
-          <t>helene.marion@ch-remiremont.fr</t>
-        </is>
-      </c>
+      <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16604,42 +16580,42 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Vosges</t>
+          <t>Yonne</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Site Hospitalier de Neufchâteau Siège Social (Neufchâteau)</t>
+          <t>Hopital Gaston Ramon (Sens)</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2435-establishment6148</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2465-establishment6172</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE ET SOINS INTENSIFS CARDIAQUES</t>
+          <t>Médecine cardiologie et soins intensifs</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Dr Jean-Louis MEREGNANI</t>
+          <t>Dr Didier PACAUD</t>
         </is>
       </c>
       <c r="G392" s="2" t="inlineStr">
         <is>
-          <t>jl.meregnani@ch-ouestvosgien.fr</t>
+          <t>dpacaud@ch-sens.fr</t>
         </is>
       </c>
       <c r="H392" s="2" t="inlineStr">
         <is>
-          <t>e.andrique@ch-ouestvosgien.fr</t>
+          <t>drh@ch-sens.fr</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -16661,21 +16637,29 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Centre hospitalier Centre hospitalier d'Auxerre (Auxerre)</t>
+          <t>CENTRE HOSPITALIER (JOIGNY)</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2462-establishment6170</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2477-establishment6183</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Cardiologie et unité de soins intensifs cardiologiques</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr"/>
-      <c r="G393" t="inlineStr"/>
+          <t>Plateau Technique de Cardiologie</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Dr Yan MORVAN</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>morvan@ch-joigny.fr</t>
+        </is>
+      </c>
       <c r="H393" t="inlineStr"/>
       <c r="I393" t="inlineStr">
         <is>
@@ -16696,34 +16680,30 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Hopital Gaston Ramon (Sens)</t>
+          <t>CENTRE HOSPITALIER (JOIGNY)</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2465-establishment6172</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2477-establishment6183</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Médecine cardiologie et soins intensifs</t>
+          <t>SMR des affections cardio-vasculaires</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Dr Didier PACAUD</t>
+          <t>Dr Yan MORVAN</t>
         </is>
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>dpacaud@ch-sens.fr</t>
-        </is>
-      </c>
-      <c r="H394" s="2" t="inlineStr">
-        <is>
-          <t>drh@ch-sens.fr</t>
-        </is>
-      </c>
+          <t>morvan@ch-joigny.fr</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr"/>
       <c r="I394" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16743,29 +16723,25 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER (JOIGNY)</t>
+          <t>CENTRE HOSPITALIER (AVALLON)</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2477-establishment6183</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2826-establishment6392</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Plateau Technique de Cardiologie</t>
+          <t>médecine 2 à orientation pneumologique et cardiologique</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Dr Yan MORVAN</t>
-        </is>
-      </c>
-      <c r="G395" s="2" t="inlineStr">
-        <is>
-          <t>morvan@ch-joigny.fr</t>
-        </is>
-      </c>
+          <t>Dr Brahim BOUKHELOUA</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr">
         <is>
@@ -16776,37 +16752,37 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Yonne</t>
+          <t>Territoire de Belfort</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER (JOIGNY)</t>
+          <t>Hôpital Nord Franche-Comté (TREVENANS)</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2477-establishment6183</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2497-establishment6201</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>SMR des affections cardio-vasculaires</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Dr Yan MORVAN</t>
+          <t>Dr Yoann LEFRANCOIS</t>
         </is>
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>morvan@ch-joigny.fr</t>
+          <t>yoann.lefrancois@hnfc.fr</t>
         </is>
       </c>
       <c r="H396" t="inlineStr"/>
@@ -16819,36 +16795,44 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Yonne</t>
+          <t>Essonne</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER (AVALLON)</t>
+          <t>Centre Hospitalier Sud Francilien (Corbeil-Essonnes)</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2826-establishment6392</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2501-establishment10188</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>médecine 2 à orientation pneumologique et cardiologique</t>
+          <t>CARDIOLOGIE</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Dr Brahim BOUKHELOUA</t>
-        </is>
-      </c>
-      <c r="G397" t="inlineStr"/>
-      <c r="H397" t="inlineStr"/>
+          <t>Dr Brahim MEFTOUT</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>brahim.meftout@chsf.fr</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>antoine.vallauri@chsf.fr</t>
+        </is>
+      </c>
       <c r="I397" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16858,40 +16842,44 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Territoire de Belfort</t>
+          <t>Essonne</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Hôpital Nord Franche-Comté (TREVENANS)</t>
+          <t>Centre Hospitalier Sud Francilien (Corbeil-Essonnes)</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2497-establishment6201</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2501-establishment10188</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>SMR READAPTATION CARDIO VASCULAIRE</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Dr Yoann LEFRANCOIS</t>
+          <t>Dr François KOUKOUI</t>
         </is>
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>yoann.lefrancois@hnfc.fr</t>
-        </is>
-      </c>
-      <c r="H398" t="inlineStr"/>
+          <t>francois.koukoui@ch-sud-francilien.fr</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>antoine.vallauri@chsf.fr</t>
+        </is>
+      </c>
       <c r="I398" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16911,34 +16899,26 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Sud Francilien (Corbeil-Essonnes)</t>
+          <t>Hôpital Paris-Saclay (ORSAY)</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2501-establishment10188</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2505-establishment7767</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
+          <t>Cardiologie et Unité de Soins Intensifs de Cardiologie (USIC)</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Dr Brahim MEFTOUT</t>
-        </is>
-      </c>
-      <c r="G399" s="2" t="inlineStr">
-        <is>
-          <t>brahim.meftout@chsf.fr</t>
-        </is>
-      </c>
-      <c r="H399" s="2" t="inlineStr">
-        <is>
-          <t>antoine.vallauri@chsf.fr</t>
-        </is>
-      </c>
+          <t>Dr Maruan BARRI</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr"/>
+      <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16958,34 +16938,26 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Sud Francilien (Corbeil-Essonnes)</t>
+          <t>CENTRE HOSPITALIER DE BLIGNY (BRIIS SOUS FORGES)</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2501-establishment10188</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3248-establishment7081</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>SMR READAPTATION CARDIO VASCULAIRE</t>
+          <t>READAPTATION CARDIAQUE ET SOINS DE SUITE CARDIOLOGIQUES</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Dr François KOUKOUI</t>
-        </is>
-      </c>
-      <c r="G400" s="2" t="inlineStr">
-        <is>
-          <t>francois.koukoui@ch-sud-francilien.fr</t>
-        </is>
-      </c>
-      <c r="H400" s="2" t="inlineStr">
-        <is>
-          <t>antoine.vallauri@chsf.fr</t>
-        </is>
-      </c>
+          <t>Dr Titi FARROKHI</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr"/>
+      <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16995,32 +16967,32 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Essonne</t>
+          <t>Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Hôpital Paris-Saclay (ORSAY)</t>
+          <t>Hôpital Ambroise-Paré AP-HP (Boulogne-Billancourt)</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2505-establishment7767</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2524-establishment6228</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Cardiologie et Unité de Soins Intensifs de Cardiologie (USIC)</t>
+          <t>Cardiologie et maladies vasculaires</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Dr Maruan BARRI</t>
+          <t>Dr MARIE HAUGUEL-MOREAU</t>
         </is>
       </c>
       <c r="G401" t="inlineStr"/>
@@ -17034,32 +17006,32 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Essonne</t>
+          <t>Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER DE BLIGNY (BRIIS SOUS FORGES)</t>
+          <t>Hôpital Antoine Béclère AP-HP (Clamart)</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3248-establishment7081</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2531-establishment6235</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>READAPTATION CARDIAQUE ET SOINS DE SUITE CARDIOLOGIQUES</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Dr Titi FARROKHI</t>
+          <t>Dr CLAUDIUS STATESCU</t>
         </is>
       </c>
       <c r="G402" t="inlineStr"/>
@@ -17083,26 +17055,30 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Hôpital Ambroise-Paré AP-HP (Boulogne-Billancourt)</t>
+          <t>AP-HP Hôpital Beaujon (Clichy)</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2524-establishment6228</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2526-establishment6230</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Cardiologie et maladies vasculaires</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Dr MARIE HAUGUEL-MOREAU</t>
+          <t>Dr AGNES CACHIER</t>
         </is>
       </c>
       <c r="G403" t="inlineStr"/>
-      <c r="H403" t="inlineStr"/>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>marie.hiance@aphp.fr</t>
+        </is>
+      </c>
       <c r="I403" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17122,24 +17098,20 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Hôpital Antoine Béclère AP-HP (Clamart)</t>
+          <t>Hôpital National d'Instruction des Armées PERCY (CLAMART)</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2531-establishment6235</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8044</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>Dr CLAUDIUS STATESCU</t>
-        </is>
-      </c>
+          <t>CARDIOLOGIE/MEDECINE AERONAUTIQUE 92</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
       <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr">
@@ -17161,30 +17133,22 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Beaujon (Clichy)</t>
+          <t>Hôpital National d'Instruction des Armées PERCY (CLAMART)</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2526-establishment6230</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8044</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>Dr AGNES CACHIER</t>
-        </is>
-      </c>
+          <t>CHIRURGIE THORACIQUE ET CARDIO-VASCULAIRE 92</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
       <c r="G405" t="inlineStr"/>
-      <c r="H405" s="2" t="inlineStr">
-        <is>
-          <t>marie.hiance@aphp.fr</t>
-        </is>
-      </c>
+      <c r="H405" t="inlineStr"/>
       <c r="I405" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17204,21 +17168,29 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Hôpital National d'Instruction des Armées PERCY (CLAMART)</t>
+          <t>Centre d'accueil et de soins hospitaliers CASH (Nanterre)</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8044</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2522-establishment6226</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE/MEDECINE AERONAUTIQUE 92</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr"/>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Dr Mohand GOUDJIL</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>mohand.goudjil@ch-nanterre.fr</t>
+        </is>
+      </c>
       <c r="H406" t="inlineStr"/>
       <c r="I406" t="inlineStr">
         <is>
@@ -17239,21 +17211,29 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Hôpital National d'Instruction des Armées PERCY (CLAMART)</t>
+          <t>Centre d'accueil et de soins hospitaliers CASH (Nanterre)</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8044</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2522-establishment6226</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>CHIRURGIE THORACIQUE ET CARDIO-VASCULAIRE 92</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr"/>
+          <t>Unité de Soins Intensifs de Cardiologie</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Dr Mohand GOUDJIL</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>mohand.goudjil@ch-nanterre.fr</t>
+        </is>
+      </c>
       <c r="H407" t="inlineStr"/>
       <c r="I407" t="inlineStr">
         <is>
@@ -17274,30 +17254,34 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Centre d'accueil et de soins hospitaliers CASH (Nanterre)</t>
+          <t>Centre Hospitalier Centre Hospitalier Stell (Rueil-Malmaison)</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2522-establishment6226</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2547-establishment6249</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Hôpital de jour de Soins de suite et de réadaptation cardio-vasculaires</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Dr Mohand GOUDJIL</t>
+          <t>Dr Fatima BOUKHSIBI</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>mohand.goudjil@ch-nanterre.fr</t>
-        </is>
-      </c>
-      <c r="H408" t="inlineStr"/>
+          <t>fatima.boukhsibi@ch-rueil.fr</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>drh@ch-rueil.fr</t>
+        </is>
+      </c>
       <c r="I408" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17317,30 +17301,34 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Centre d'accueil et de soins hospitaliers CASH (Nanterre)</t>
+          <t>Centre Hospitalier Centre Hospitalier Stell (Rueil-Malmaison)</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2522-establishment6226</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2547-establishment6249</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Unité de Soins Intensifs de Cardiologie</t>
+          <t>Soins de Suite et de Réadaptation Cardiovasculaire</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Dr Mohand GOUDJIL</t>
+          <t>Dr Fatima BOUKHSIBI</t>
         </is>
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>mohand.goudjil@ch-nanterre.fr</t>
-        </is>
-      </c>
-      <c r="H409" t="inlineStr"/>
+          <t>fatima.boukhsibi@ch-rueil.fr</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>drh@ch-rueil.fr</t>
+        </is>
+      </c>
       <c r="I409" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17360,32 +17348,32 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Centre Hospitalier Stell (Rueil-Malmaison)</t>
+          <t>Site Hospitalier de Neuilly-sur-Seine (Siège Social) (Neuilly-sur-Seine)</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2547-establishment6249</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2537-establishment6240</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Hôpital de jour de Soins de suite et de réadaptation cardio-vasculaires</t>
+          <t>Spécialités médicales (Cardiologie)</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Dr Fatima BOUKHSIBI</t>
+          <t>Dr Camille BOTELLA</t>
         </is>
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>fatima.boukhsibi@ch-rueil.fr</t>
+          <t>cbotella@ch-rivesdeseine.fr</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
-          <t>drh@ch-rueil.fr</t>
+          <t>direction@ch-rivesdeseine.fr</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -17397,42 +17385,42 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Hauts-de-Seine</t>
+          <t>Seine-Saint-Denis</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Centre Hospitalier Stell (Rueil-Malmaison)</t>
+          <t>Centre hospitalier Intercommunal (Aulnay-sous-Bois)</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2547-establishment6249</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2573-establishment6274</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Soins de Suite et de Réadaptation Cardiovasculaire</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Dr Fatima BOUKHSIBI</t>
+          <t>Dr François WALYLO</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>fatima.boukhsibi@ch-rueil.fr</t>
+          <t>francois.walylo@ch-aulnay.fr</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
         <is>
-          <t>drh@ch-rueil.fr</t>
+          <t>maxime.lemee@ght-gpne.fr</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -17444,44 +17432,36 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Hauts-de-Seine</t>
+          <t>Seine-Saint-Denis</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Site Hospitalier de Neuilly-sur-Seine (Siège Social) (Neuilly-sur-Seine)</t>
+          <t>Hôpital Avicenne - AP-HP.Hôpitaux Universitaires Paris Seine-Saint-Denis (Bobigny)</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2537-establishment6240</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2552-establishment6254</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Spécialités médicales (Cardiologie)</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Dr Camille BOTELLA</t>
-        </is>
-      </c>
-      <c r="G412" s="2" t="inlineStr">
-        <is>
-          <t>cbotella@ch-rivesdeseine.fr</t>
-        </is>
-      </c>
-      <c r="H412" s="2" t="inlineStr">
-        <is>
-          <t>direction@ch-rivesdeseine.fr</t>
-        </is>
-      </c>
+          <t>NATHALIE AZOPPARDI</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr"/>
       <c r="I412" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17501,12 +17481,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Centre hospitalier Intercommunal (Aulnay-sous-Bois)</t>
+          <t>Centre hospitalier intercommunal André Grégoire (Montreuil-sous-Bois)</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2573-establishment6274</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2568-establishment6255</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -17516,19 +17496,15 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Dr François WALYLO</t>
+          <t>Dr Albert BOCCARA</t>
         </is>
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>francois.walylo@ch-aulnay.fr</t>
-        </is>
-      </c>
-      <c r="H413" s="2" t="inlineStr">
-        <is>
-          <t>maxime.lemee@ght-gpne.fr</t>
-        </is>
-      </c>
+          <t>albert.boccara@ght-gpne.fr</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr"/>
       <c r="I413" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17548,12 +17524,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Hôpital Avicenne - AP-HP.Hôpitaux Universitaires Paris Seine-Saint-Denis (Bobigny)</t>
+          <t>Groupement Hospitalier de Territoire Grand Paris Nord Est (Montfermeil)</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2552-establishment6254</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2568-establishment6269</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -17563,11 +17539,19 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>NATHALIE AZOPPARDI</t>
-        </is>
-      </c>
-      <c r="G414" t="inlineStr"/>
-      <c r="H414" t="inlineStr"/>
+          <t>M. Olivier NALLET</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>olivier.nallet@ght-gpne.fr</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>maxime.lemee@ght-gpne.fr</t>
+        </is>
+      </c>
       <c r="I414" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17577,22 +17561,22 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Seine-Saint-Denis</t>
+          <t>Val-de-Marne</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Centre hospitalier intercommunal André Grégoire (Montreuil-sous-Bois)</t>
+          <t>Hôpital Bicêtre AP-HP (Le Kremlin-Bicêtre)</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2568-establishment6255</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2589-establishment6290</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -17602,14 +17586,10 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Dr Albert BOCCARA</t>
-        </is>
-      </c>
-      <c r="G415" s="2" t="inlineStr">
-        <is>
-          <t>albert.boccara@ght-gpne.fr</t>
-        </is>
-      </c>
+          <t>Dr SAFA JEBALI</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr">
         <is>
@@ -17620,44 +17600,36 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Seine-Saint-Denis</t>
+          <t>Val-de-Marne</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Groupement Hospitalier de Territoire Grand Paris Nord Est (Montfermeil)</t>
+          <t>Hôpital Bicêtre AP-HP (Le Kremlin-Bicêtre)</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2568-establishment6269</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2589-establishment6290</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Explorations fonctionnelles cardio-vasculaires</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>M. Olivier NALLET</t>
-        </is>
-      </c>
-      <c r="G416" s="2" t="inlineStr">
-        <is>
-          <t>olivier.nallet@ght-gpne.fr</t>
-        </is>
-      </c>
-      <c r="H416" s="2" t="inlineStr">
-        <is>
-          <t>maxime.lemee@ght-gpne.fr</t>
-        </is>
-      </c>
+          <t>Dr OLIVIER CHOURAQUI</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr"/>
       <c r="I416" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17677,12 +17649,12 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Hôpital Bicêtre AP-HP (Le Kremlin-Bicêtre)</t>
+          <t>AP-HP Hôpital Henri Mondor (Créteil)</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2589-establishment6290</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2577-establishment6278</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -17692,11 +17664,15 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Dr SAFA JEBALI</t>
+          <t>Dr ALBAN COPIE</t>
         </is>
       </c>
       <c r="G417" t="inlineStr"/>
-      <c r="H417" t="inlineStr"/>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>adeline.rouby@aphp.fr</t>
+        </is>
+      </c>
       <c r="I417" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17716,29 +17692,33 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Hôpital Bicêtre AP-HP (Le Kremlin-Bicêtre)</t>
+          <t>AP-HP Hôpital Henri Mondor (Créteil)</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2589-establishment6290</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2577-establishment6278</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Explorations fonctionnelles cardio-vasculaires</t>
+          <t>Cardiologie interventionnelle</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Dr OLIVIER CHOURAQUI</t>
+          <t>Pr EMMANUEL TEIGER</t>
         </is>
       </c>
       <c r="G418" t="inlineStr"/>
-      <c r="H418" t="inlineStr"/>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>adeline.rouby@aphp.fr</t>
+        </is>
+      </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>Non spécifié / Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -17765,12 +17745,12 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Chirurgie cardio-vasculaire</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Dr ALBAN COPIE</t>
+          <t>MORGANE ARNOUX</t>
         </is>
       </c>
       <c r="G419" t="inlineStr"/>
@@ -17808,12 +17788,12 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Cardiologie interventionnelle</t>
+          <t>Exploration fonctionnelle cardiovasculaire non invasive et de cardiologie ambulatoire</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Pr EMMANUEL TEIGER</t>
+          <t>Pr GENEVIEVE DERUMEAUX</t>
         </is>
       </c>
       <c r="G420" t="inlineStr"/>
@@ -17824,7 +17804,7 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non spécifié / Non</t>
         </is>
       </c>
     </row>
@@ -17841,30 +17821,22 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Henri Mondor (Créteil)</t>
+          <t>Hôpital Paul-Brousse AP-HP (Villejuif)</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2577-establishment6278</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2596-establishment6296</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Chirurgie cardio-vasculaire</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>MORGANE ARNOUX</t>
-        </is>
-      </c>
+          <t>CARDIOLOGIE</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr"/>
-      <c r="H421" s="2" t="inlineStr">
-        <is>
-          <t>adeline.rouby@aphp.fr</t>
-        </is>
-      </c>
+      <c r="H421" t="inlineStr"/>
       <c r="I421" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17884,28 +17856,28 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Henri Mondor (Créteil)</t>
+          <t>AP-HP Hôpital Charles Foix (Ivry-sur-Seine)</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2577-establishment6278</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2584-establishment6285</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Exploration fonctionnelle cardiovasculaire non invasive et de cardiologie ambulatoire</t>
+          <t>court séjour gériatrique à orientation cardiologie et neuro-psycho</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Pr GENEVIEVE DERUMEAUX</t>
+          <t>Dr SONIA ADRAR</t>
         </is>
       </c>
       <c r="G422" t="inlineStr"/>
       <c r="H422" s="2" t="inlineStr">
         <is>
-          <t>adeline.rouby@aphp.fr</t>
+          <t>choella.akbaraly@aphp.fr</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -17927,22 +17899,30 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Hôpital Paul-Brousse AP-HP (Villejuif)</t>
+          <t>AP-HP Hôpital Charles Foix (Ivry-sur-Seine)</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2596-establishment6296</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2584-establishment6285</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr"/>
+          <t>Soins de suite et de réadapation à orientation cardiologie et neuro-psycho-gériatrique</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Dr CARMELO LAFUENTE LAFUENTE</t>
+        </is>
+      </c>
       <c r="G423" t="inlineStr"/>
-      <c r="H423" t="inlineStr"/>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
       <c r="I423" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17962,28 +17942,32 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Charles Foix (Ivry-sur-Seine)</t>
+          <t>Centre Hospitalier Intercommunal de Villeneuve-Saint-Georges Lucie &amp; Raymond Aubrac (Villeneuve-Saint-Georges)</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2584-establishment6285</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2583-establishment6284</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>court séjour gériatrique à orientation cardiologie et neuro-psycho</t>
+          <t>Cardiologie et urgences cardio-vasculaires</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Dr SONIA ADRAR</t>
-        </is>
-      </c>
-      <c r="G424" t="inlineStr"/>
+          <t>Dr Emmanuel SALENGRO</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>emmanuel.salengro@chiv.fr</t>
+        </is>
+      </c>
       <c r="H424" s="2" t="inlineStr">
         <is>
-          <t>choella.akbaraly@aphp.fr</t>
+          <t>elena.ketterer@chiv.fr</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -17995,40 +17979,40 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Val-de-Marne</t>
+          <t>Val-d'Oise</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Charles Foix (Ivry-sur-Seine)</t>
+          <t>Hôpital NOVO - Site de Pontoise (CERGY PONTOISE)</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2584-establishment6285</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2605-establishment6305</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Soins de suite et de réadapation à orientation cardiologie et neuro-psycho-gériatrique</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Dr CARMELO LAFUENTE LAFUENTE</t>
-        </is>
-      </c>
-      <c r="G425" t="inlineStr"/>
-      <c r="H425" s="2" t="inlineStr">
-        <is>
-          <t>choella.akbaraly@aphp.fr</t>
-        </is>
-      </c>
+          <t>Dr Véronique DECALF</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>veronique.decalf@ght-novo.fr</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr"/>
       <c r="I425" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18038,44 +18022,40 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Val-de-Marne</t>
+          <t>Val-d'Oise</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Intercommunal de Villeneuve-Saint-Georges Lucie &amp; Raymond Aubrac (Villeneuve-Saint-Georges)</t>
+          <t>Centre Hospitalier de Gonesse (Gonesse)</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2583-establishment6284</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2610-establishment6309</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Cardiologie et urgences cardio-vasculaires</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Dr Emmanuel SALENGRO</t>
+          <t>Dr Nabil POULOS</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>emmanuel.salengro@chiv.fr</t>
-        </is>
-      </c>
-      <c r="H426" s="2" t="inlineStr">
-        <is>
-          <t>elena.ketterer@chiv.fr</t>
-        </is>
-      </c>
+          <t>nabil.poulos@ch-gonesse.fr</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr"/>
       <c r="I426" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18095,33 +18075,29 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Hôpital NOVO - Site de Pontoise (CERGY PONTOISE)</t>
+          <t>Groupement hospitalier Eaubonne - Montmorency - Hôpital Simone Veil (EAUBONNE)</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2605-establishment6305</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2600-establishment6300</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>Dr Véronique DECALF</t>
-        </is>
-      </c>
-      <c r="G427" s="2" t="inlineStr">
-        <is>
-          <t>veronique.decalf@ght-novo.fr</t>
-        </is>
-      </c>
-      <c r="H427" t="inlineStr"/>
+          <t>Cardiologie - Cardiologie interventionnelle - USIC</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>sec.drh@ch-simoneveil.fr</t>
+        </is>
+      </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>Non spécifié / Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -18138,30 +18114,34 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de Gonesse (Gonesse)</t>
+          <t>Centre hospitalier Victor Dupouy (Argenteuil)</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2610-establishment6309</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2598-establishment6298</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>CARDIOLOGIE</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Dr Nabil POULOS</t>
+          <t>Dr François DUCLOS</t>
         </is>
       </c>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>nabil.poulos@ch-gonesse.fr</t>
-        </is>
-      </c>
-      <c r="H428" t="inlineStr"/>
+          <t>francois.duclos@ch-argenteuil.fr</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>bianca.dasilvabarreto@ch-argenteuil.fr</t>
+        </is>
+      </c>
       <c r="I428" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18181,71 +18161,75 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Groupement hospitalier Eaubonne - Montmorency - Hôpital Simone Veil (EAUBONNE)</t>
+          <t>Hôpital Le Parc (Taverny)</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2600-establishment6300</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2599-establishment6299</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Cardiologie - Cardiologie interventionnelle - USIC</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr"/>
-      <c r="G429" t="inlineStr"/>
-      <c r="H429" s="2" t="inlineStr">
-        <is>
-          <t>sec.drh@ch-simoneveil.fr</t>
-        </is>
-      </c>
+          <t>CARDIOLOGIE</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Dr Ioana MORARU</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>i.moraru@hopital-parc-taverny.fr</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr"/>
       <c r="I429" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non spécifié / Non</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>971</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Val-d'Oise</t>
+          <t>Guadeloupe</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Centre hospitalier Victor Dupouy (Argenteuil)</t>
+          <t>Centre Hospitalier Universitaire de la Guadeloupe (Pointe-à-Pitre)</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2598-establishment6298</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2624-establishment6323</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Dr François DUCLOS</t>
+          <t>Pr Annie LANNUZEL</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>francois.duclos@ch-argenteuil.fr</t>
+          <t>annie.lannuzel@chu-guadeloupe.fr</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
-          <t>bianca.dasilvabarreto@ch-argenteuil.fr</t>
+          <t>christiana.cologer@chu-guadeloupe.fr</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -18257,40 +18241,36 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>971</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Val-d'Oise</t>
+          <t>Guadeloupe</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Hôpital Le Parc (Taverny)</t>
+          <t>Centre Hospitalier Universitaire de la Guadeloupe (Pointe-à-Pitre)</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2599-establishment6299</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2624-establishment6323</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>Dr Ioana MORARU</t>
-        </is>
-      </c>
-      <c r="G431" s="2" t="inlineStr">
-        <is>
-          <t>i.moraru@hopital-parc-taverny.fr</t>
-        </is>
-      </c>
-      <c r="H431" t="inlineStr"/>
+          <t>Chirurgie thoracique et cardio-vasculaire</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>christiana.cologer@chu-guadeloupe.fr</t>
+        </is>
+      </c>
       <c r="I431" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18300,44 +18280,40 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>972</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Guadeloupe</t>
+          <t>Martinique</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Universitaire de la Guadeloupe (Pointe-à-Pitre)</t>
+          <t>Hôpital Pierre Zobda-Quitman (Fort-de-France)</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2624-establishment6323</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2640-establishment1385</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Département de Cardiologie - Soins Intensifs 7B</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Pr Annie LANNUZEL</t>
+          <t>Pr Jocelyn INAMO</t>
         </is>
       </c>
       <c r="G432" s="2" t="inlineStr">
         <is>
-          <t>annie.lannuzel@chu-guadeloupe.fr</t>
-        </is>
-      </c>
-      <c r="H432" s="2" t="inlineStr">
-        <is>
-          <t>christiana.cologer@chu-guadeloupe.fr</t>
-        </is>
-      </c>
+          <t>jocelyn.inamo@chu-martinique.fr</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr"/>
       <c r="I432" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18347,36 +18323,40 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>972</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Guadeloupe</t>
+          <t>Martinique</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Universitaire de la Guadeloupe (Pointe-à-Pitre)</t>
+          <t>Hôpital Pierre Zobda-Quitman (Fort-de-France)</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2624-establishment6323</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2640-establishment1385</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Chirurgie thoracique et cardio-vasculaire</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr"/>
-      <c r="G433" t="inlineStr"/>
-      <c r="H433" s="2" t="inlineStr">
-        <is>
-          <t>christiana.cologer@chu-guadeloupe.fr</t>
-        </is>
-      </c>
+          <t>Département de Cardiologie 7D</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Pr Jocelyn INAMO</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>jocelyn.inamo@chu-martinique.fr</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr"/>
       <c r="I433" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18386,37 +18366,37 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>973</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Martinique</t>
+          <t>Guyane</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Hôpital Pierre Zobda-Quitman (Fort-de-France)</t>
+          <t>Centre Hospitalier de Cayenne Andrée Rosemon (Cayenne)</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2640-establishment1385</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2645-establishment6342</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Département de Cardiologie - Soins Intensifs 7B</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Pr Jocelyn INAMO</t>
+          <t>Dr Yves-Kénol FRANCK</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr">
         <is>
-          <t>jocelyn.inamo@chu-martinique.fr</t>
+          <t>yves-kenol.franck@ch-cayenne.fr</t>
         </is>
       </c>
       <c r="H434" t="inlineStr"/>
@@ -18429,40 +18409,44 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>973</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Martinique</t>
+          <t>Guyane</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Hôpital Pierre Zobda-Quitman (Fort-de-France)</t>
+          <t>Centre Hospitalier de l'Ouest Guyanais Franck Joly (Saint-Laurent-du-Maroni)</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2640-establishment1385</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2646-establishment6343</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Département de Cardiologie 7D</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Pr Jocelyn INAMO</t>
+          <t>Dr Grace-À-Dieu YABETA</t>
         </is>
       </c>
       <c r="G435" s="2" t="inlineStr">
         <is>
-          <t>jocelyn.inamo@chu-martinique.fr</t>
-        </is>
-      </c>
-      <c r="H435" t="inlineStr"/>
+          <t>g.yabeta@ch-ouestguyane.fr</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>s.lavenaire@ch-ouestguyane.fr</t>
+        </is>
+      </c>
       <c r="I435" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18472,39 +18456,31 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Guyane</t>
+          <t>La Réunion</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de Cayenne Andrée Rosemon (Cayenne)</t>
+          <t>Centre Hospitalier Universitaire Sud Réunion (Saint-Pierre)</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2645-establishment6342</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2651-establishment6347</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>Dr Yves-Kénol FRANCK</t>
-        </is>
-      </c>
-      <c r="G436" s="2" t="inlineStr">
-        <is>
-          <t>yves-kenol.franck@ch-cayenne.fr</t>
-        </is>
-      </c>
+          <t>Cardiologie (Sud)</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr"/>
       <c r="I436" t="inlineStr">
         <is>
@@ -18515,44 +18491,40 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Guyane</t>
+          <t>La Réunion</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de l'Ouest Guyanais Franck Joly (Saint-Laurent-du-Maroni)</t>
+          <t>Centre hospitalier Felix Guyon (Saint-Denis)</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2646-establishment6343</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2651-establishment6344</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie (Nord)</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Dr Grace-À-Dieu YABETA</t>
+          <t>Dr Christian KICHENIN</t>
         </is>
       </c>
       <c r="G437" s="2" t="inlineStr">
         <is>
-          <t>g.yabeta@ch-ouestguyane.fr</t>
-        </is>
-      </c>
-      <c r="H437" s="2" t="inlineStr">
-        <is>
-          <t>s.lavenaire@ch-ouestguyane.fr</t>
-        </is>
-      </c>
+          <t>cardiologie@chd-fguyon.fr</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr"/>
       <c r="I437" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18572,21 +18544,29 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Universitaire Sud Réunion (Saint-Pierre)</t>
+          <t>Centre hospitalier Felix Guyon (Saint-Denis)</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2651-establishment6347</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2651-establishment6344</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Cardiologie (Sud)</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr"/>
+          <t>Chir. Thoracique et Cardiovasculaire</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>M. Jean-François DELAMBRE</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>jf-delambre@chd-fguyon.fr</t>
+        </is>
+      </c>
       <c r="H438" t="inlineStr"/>
       <c r="I438" t="inlineStr">
         <is>
@@ -18607,30 +18587,34 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Centre hospitalier Felix Guyon (Saint-Denis)</t>
+          <t>Centre hospitalier Ouest Réunion (Saint-Paul)</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2651-establishment6344</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2656-establishment6352</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Cardiologie (Nord)</t>
+          <t>Médecine à orientation Cardiologie et Neurologie</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Dr Christian KICHENIN</t>
+          <t>Dr Fanny LE MEE</t>
         </is>
       </c>
       <c r="G439" s="2" t="inlineStr">
         <is>
-          <t>cardiologie@chd-fguyon.fr</t>
-        </is>
-      </c>
-      <c r="H439" t="inlineStr"/>
+          <t>secretariat.cardiologie@chor.re</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>Ol.MANICON@pso.re</t>
+        </is>
+      </c>
       <c r="I439" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18640,131 +18624,41 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>987</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>La Réunion</t>
+          <t>Polynésie Française</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Centre hospitalier Felix Guyon (Saint-Denis)</t>
+          <t>Centre Hospitalier de Polynésie française (Papeete)</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2651-establishment6344</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2771-establishment7816</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Chir. Thoracique et Cardiovasculaire</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>M. Jean-François DELAMBRE</t>
+          <t>M. Christophe LEGOANVIC</t>
         </is>
       </c>
       <c r="G440" s="2" t="inlineStr">
         <is>
-          <t>jf-delambre@chd-fguyon.fr</t>
+          <t>christophe.legoanvic@cht.pf</t>
         </is>
       </c>
       <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr">
-        <is>
-          <t>Non spécifié / Non</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>La Réunion</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>Centre hospitalier Ouest Réunion (Saint-Paul)</t>
-        </is>
-      </c>
-      <c r="D441" s="2" t="inlineStr">
-        <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2656-establishment6352</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>Médecine à orientation Cardiologie et Neurologie</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>Dr Fanny LE MEE</t>
-        </is>
-      </c>
-      <c r="G441" s="2" t="inlineStr">
-        <is>
-          <t>secretariat.cardiologie@chor.re</t>
-        </is>
-      </c>
-      <c r="H441" s="2" t="inlineStr">
-        <is>
-          <t>Ol.MANICON@pso.re</t>
-        </is>
-      </c>
-      <c r="I441" t="inlineStr">
-        <is>
-          <t>Non spécifié / Non</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>Polynésie Française</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>Centre Hospitalier de Polynésie française (Papeete)</t>
-        </is>
-      </c>
-      <c r="D442" s="2" t="inlineStr">
-        <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2771-establishment7816</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>M. Christophe LEGOANVIC</t>
-        </is>
-      </c>
-      <c r="G442" s="2" t="inlineStr">
-        <is>
-          <t>christophe.legoanvic@cht.pf</t>
-        </is>
-      </c>
-      <c r="H442" t="inlineStr"/>
-      <c r="I442" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -18815,824 +18709,815 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G356" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D361" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G369" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D373" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G373" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G376" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G378" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G386" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G387" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G395" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G396" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D397" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D398" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G398" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D399" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G399" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D400" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G400" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D401" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D402" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D403" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G408" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G409" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G410" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D411" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G411" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D412" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G412" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D413" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G413" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D414" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D415" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G415" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D416" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G416" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D417" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D418" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D419" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D420" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D421" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D422" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D423" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D424" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D425" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D426" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G426" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D427" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G427" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D428" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D429" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D430" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G430" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D431" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G431" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D432" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G432" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D433" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D434" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G434" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D435" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G435" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D436" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G436" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D437" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G437" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D438" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D439" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G439" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D440" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G440" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D441" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G441" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D442" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G442" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H326" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G346" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G349" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H349" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H355" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D361" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G361" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G362" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H366" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G367" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H367" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G368" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G369" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D373" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H375" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G376" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H376" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H381" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G382" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H382" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G383" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H387" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H388" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G390" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G393" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G396" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D397" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G397" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D398" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G398" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D399" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D400" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D401" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D402" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D403" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G406" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G407" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G408" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H408" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G409" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G410" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D411" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G411" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D412" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D413" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G413" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D414" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G414" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H414" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D415" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D416" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D417" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H417" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D418" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H418" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D419" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D420" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D421" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D422" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D423" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D424" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G424" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D425" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G425" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D426" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G426" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D427" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H427" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D428" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H428" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D429" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G429" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D430" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G430" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D431" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H431" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D432" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G432" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D433" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G433" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D434" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G434" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D435" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G435" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H435" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D436" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D437" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G437" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D438" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G438" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D439" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G439" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D440" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G440" r:id="rId852"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fhf_cardiologie.xlsx
+++ b/fhf_cardiologie.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I440"/>
+  <dimension ref="A1:I442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8906,11 +8906,7 @@
           <t>louis-francois.garnier@ch-ploermel.fr</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr">
-        <is>
-          <t>maryse.caoudal@ch-bretagne-atlantique.fr</t>
-        </is>
-      </c>
+      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -9989,7 +9985,7 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>fbried@chsa.fr</t>
+          <t>isouplet@chsa.fr</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -10598,40 +10594,44 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Puy-de-Dôme</t>
+          <t>Pas-de-Calais</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>CHRU Clermont- Ferrand Gabriel-Montpied (Clermont-Ferrand)</t>
+          <t>Centre Hospitalier d'Arras (Arras)</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1688-establishment2931</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1656-establishment5419</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Cardiologie médicale et médecine vasculaire</t>
+          <t>Cardiologie / USIC / Explorations fonctionnelles cardio.</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>M. Romain ESCHALIER</t>
+          <t>Dr Francesco FAVATA</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>reschalier@chu-clermontferrand.fr</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr"/>
+          <t>Francesco.FAVATA@gh-artoisternois.fr</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>secretariat.direction@gh-artoisternois.fr</t>
+        </is>
+      </c>
       <c r="I246" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -10641,40 +10641,44 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Puy-de-Dôme</t>
+          <t>Pas-de-Calais</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>CHRU Clermont- Ferrand Gabriel-Montpied (Clermont-Ferrand)</t>
+          <t>Centre Hospitalier d'Arras (Arras)</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1688-establishment2931</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1656-establishment5419</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Chirurgie Cardio-Vasculaire</t>
+          <t>SSR Cardio - Pneumo (Éole)</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Pr Lionel CAMILLERI</t>
+          <t>Dr Philippe PAUQUET</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>lcamilleri@chu-clermontferrand.fr</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr"/>
+          <t>Philippe.PAUQUET@gh-artoisternois.fr</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>secretariat.direction@gh-artoisternois.fr</t>
+        </is>
+      </c>
       <c r="I247" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -10694,27 +10698,27 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Centre hospitalier Guy Thomas (Riom)</t>
+          <t>CHRU Clermont- Ferrand Gabriel-Montpied (Clermont-Ferrand)</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1694-establishment5455</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1688-establishment2931</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Médecine à orientation cardiologique</t>
+          <t>Cardiologie médicale et médecine vasculaire</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Dr Pascale HAUMONT</t>
+          <t>M. Romain ESCHALIER</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>p.haumont@ch-riom.fr</t>
+          <t>reschalier@chu-clermontferrand.fr</t>
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
@@ -10727,31 +10731,39 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Pyrénées-Atlantiques</t>
+          <t>Puy-de-Dôme</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Pau)</t>
+          <t>CHRU Clermont- Ferrand Gabriel-Montpied (Clermont-Ferrand)</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1731-establishment5490</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1688-establishment2931</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
+          <t>Chirurgie Cardio-Vasculaire</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Pr Lionel CAMILLERI</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>lcamilleri@chu-clermontferrand.fr</t>
+        </is>
+      </c>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
@@ -10762,40 +10774,40 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Pyrénées-Atlantiques</t>
+          <t>Puy-de-Dôme</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Centre hospitalier de la Côte Basque - Saint-Léon (Bayonne)</t>
+          <t>Centre hospitalier Guy Thomas (Riom)</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1733-establishment5492</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1694-establishment5455</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Cardiologie Consultations</t>
+          <t>Médecine à orientation cardiologique</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Dr Jean-Baptiste BERNEAU</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr">
-        <is>
-          <t>jdaeschler@ch-cotebasque.fr</t>
-        </is>
-      </c>
+          <t>Dr Pascale HAUMONT</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>p.haumont@ch-riom.fr</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -10815,17 +10827,17 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Orthez)</t>
+          <t>Centre hospitalier (Pau)</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1738-establishment5497</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1731-establishment5490</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>MEDECINE POLYVALENTE à orientations Cardiologie, Médecine, Pneumologie et Gastroentérologie</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -10840,36 +10852,40 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Hautes-Pyrénées</t>
+          <t>Pyrénées-Atlantiques</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de Bigorre site de la Gespe (MCO) (Tarbes)</t>
+          <t>Centre hospitalier de la Côte Basque - Saint-Léon (Bayonne)</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1746-establishment5505</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1733-establishment5492</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie Consultations</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Mme Christine LEONARD</t>
+          <t>Dr Jean-Baptiste BERNEAU</t>
         </is>
       </c>
       <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>jdaeschler@ch-cotebasque.fr</t>
+        </is>
+      </c>
       <c r="I252" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -10879,34 +10895,30 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Hautes-Pyrénées</t>
+          <t>Pyrénées-Atlantiques</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de Bigorre site de la Gespe (MCO) (Tarbes)</t>
+          <t>Centre hospitalier (Orthez)</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1746-establishment5505</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1738-establishment5497</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Réanimation spécialisée en cardiologie</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>M. Michel SERRANO</t>
-        </is>
-      </c>
+          <t>MEDECINE POLYVALENTE à orientations Cardiologie, Médecine, Pneumologie et Gastroentérologie</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
@@ -10928,22 +10940,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER (Lourdes)</t>
+          <t>Centre Hospitalier de Bigorre site de la Gespe (MCO) (Tarbes)</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1746-establishment5506</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1746-establishment5505</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Cardiologie et maladies vasculaires</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>M. Christian DEMASLES</t>
+          <t>Mme Christine LEONARD</t>
         </is>
       </c>
       <c r="G254" t="inlineStr"/>
@@ -10957,30 +10969,34 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Pyrénées-Orientales</t>
+          <t>Hautes-Pyrénées</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de Perpignan (Perpignan)</t>
+          <t>Centre Hospitalier de Bigorre site de la Gespe (MCO) (Tarbes)</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1761-establishment5519</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1746-establishment5505</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr"/>
+          <t>Réanimation spécialisée en cardiologie</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>M. Michel SERRANO</t>
+        </is>
+      </c>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
@@ -10992,44 +11008,36 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Bas-Rhin</t>
+          <t>Hautes-Pyrénées</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Haguenau)</t>
+          <t>CENTRE HOSPITALIER (Lourdes)</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1806-establishment5561</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1746-establishment5506</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Service de Cardiologie</t>
+          <t>Cardiologie et maladies vasculaires</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Dr Philippe COUPPIE</t>
-        </is>
-      </c>
-      <c r="G256" s="2" t="inlineStr">
-        <is>
-          <t>sec.cardiologie@ch-haguenau.fr</t>
-        </is>
-      </c>
-      <c r="H256" s="2" t="inlineStr">
-        <is>
-          <t>Valentine.SCHALLER@ch-haguenau.fr</t>
-        </is>
-      </c>
+          <t>M. Christian DEMASLES</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -11039,44 +11047,32 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Bas-Rhin</t>
+          <t>Pyrénées-Orientales</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER SELESTAT (SELESTAT)</t>
+          <t>Centre Hospitalier de Perpignan (Perpignan)</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1811-establishment5566</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1761-establishment5519</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Consultations externes de cardiologie et explorations cardiovasculaires</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>Dr Mounzer MANSOUR</t>
-        </is>
-      </c>
-      <c r="G257" s="2" t="inlineStr">
-        <is>
-          <t>Mounzer.MANSOUR@ghso.fr</t>
-        </is>
-      </c>
-      <c r="H257" s="2" t="inlineStr">
-        <is>
-          <t>agnes.schreiner@ghso.fr</t>
-        </is>
-      </c>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -11096,32 +11092,32 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Wissembourg)</t>
+          <t>Centre hospitalier (Haguenau)</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1786-establishment5544</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1806-establishment5561</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Plateau technique de cardiologie</t>
+          <t>Service de Cardiologie</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Dr Rodolphe THEOLADE</t>
+          <t>Dr Philippe COUPPIE</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>rtheolade@ch-wissembourg.fr</t>
+          <t>sec.cardiologie@ch-haguenau.fr</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>dam@ch-haguenau.fr</t>
+          <t>Valentine.SCHALLER@ch-haguenau.fr</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -11143,32 +11139,32 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Wissembourg)</t>
+          <t>CENTRE HOSPITALIER SELESTAT (SELESTAT)</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1786-establishment5544</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1811-establishment5566</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>SSR Cardiologique</t>
+          <t>Consultations externes de cardiologie et explorations cardiovasculaires</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Dr Rodolphe THEOLADE</t>
+          <t>Dr Mounzer MANSOUR</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>rtheolade@ch-wissembourg.fr</t>
+          <t>Mounzer.MANSOUR@ghso.fr</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>dam@ch-haguenau.fr</t>
+          <t>agnes.schreiner@ghso.fr</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -11190,24 +11186,32 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Hôpital Civil (Strasbourg)</t>
+          <t>Centre hospitalier (Wissembourg)</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1777-establishment1331</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1786-establishment5544</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Cardiologie - NHC</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
+          <t>Plateau technique de cardiologie</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Dr Rodolphe THEOLADE</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>rtheolade@ch-wissembourg.fr</t>
+        </is>
+      </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>armelle.drexler@chru-strasbourg.fr</t>
+          <t>dam@ch-haguenau.fr</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -11229,24 +11233,32 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Hôpital Civil (Strasbourg)</t>
+          <t>Centre hospitalier (Wissembourg)</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1777-establishment1331</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1786-establishment5544</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Chirurgie cardio vasculaire - transplantation et assistance cardiaque - NHC</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
+          <t>SSR Cardiologique</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Dr Rodolphe THEOLADE</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>rtheolade@ch-wissembourg.fr</t>
+        </is>
+      </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>armelle.drexler@chru-strasbourg.fr</t>
+          <t>dam@ch-haguenau.fr</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -11258,38 +11270,34 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Haut-Rhin</t>
+          <t>Bas-Rhin</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Hôpital Louis Pasteur (Colmar)</t>
+          <t>Hôpital Civil (Strasbourg)</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1817-establishment5572</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1777-establishment1331</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Cardiologie (Médecine C)</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>Dr Laszlo LEVAI</t>
-        </is>
-      </c>
+          <t>Cardiologie - NHC</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr"/>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>affairesmedicales.dirg@ch-colmar.fr</t>
+          <t>armelle.drexler@chru-strasbourg.fr</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -11301,34 +11309,34 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Haut-Rhin</t>
+          <t>Bas-Rhin</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Hôpital Louis Pasteur (Colmar)</t>
+          <t>Hôpital Civil (Strasbourg)</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1817-establishment5572</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1777-establishment1331</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Explorations fonctionnelles cardio-vasculaires</t>
+          <t>Chirurgie cardio vasculaire - transplantation et assistance cardiaque - NHC</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr"/>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>affairesmedicales.dirg@ch-colmar.fr</t>
+          <t>armelle.drexler@chru-strasbourg.fr</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -11350,22 +11358,30 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Hôpital Emile Muller (Mulhouse)</t>
+          <t>Hôpital Louis Pasteur (Colmar)</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1818-establishment9947</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1817-establishment5572</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Radiologie cardio-interventionnelle</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr"/>
+          <t>Cardiologie (Médecine C)</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Dr Laszlo LEVAI</t>
+        </is>
+      </c>
       <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr"/>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>affairesmedicales.dirg@ch-colmar.fr</t>
+        </is>
+      </c>
       <c r="I264" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -11385,22 +11401,26 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Hôpital Hasenrain (Mulhouse)</t>
+          <t>Hôpital Louis Pasteur (Colmar)</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1818-establishment5573</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1817-establishment5572</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Explorations fonctionnelles cardio-vasculaires</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>affairesmedicales.dirg@ch-colmar.fr</t>
+        </is>
+      </c>
       <c r="I265" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -11410,27 +11430,27 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Rhône</t>
+          <t>Haut-Rhin</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Hôpital de la Croix-Rousse - HCL (Lyon)</t>
+          <t>Hôpital Emile Muller (Mulhouse)</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1860-establishment5607</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1818-establishment9947</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Consultation de Cardiologie Pédiatrique</t>
+          <t>Radiologie cardio-interventionnelle</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -11445,27 +11465,27 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Rhône</t>
+          <t>Haut-Rhin</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Hôpital de la Croix-Rousse - HCL (Lyon)</t>
+          <t>Hôpital Hasenrain (Mulhouse)</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1860-establishment5607</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1818-establishment5573</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Service de Cardiologie</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -11490,37 +11510,25 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Hôpital de Villefranche-sur-Saône - HNO (Villefranche-sur-Saône Cedex)</t>
+          <t>Hôpital de la Croix-Rousse - HCL (Lyon)</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1887-establishment5630</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1860-establishment5607</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE, CARDIOLOGIE INTERVENTIONNELLE ET UNITE DE SOINS INTENSIFS DE CARDIOLOGIE</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>Dr Olivier LE VAVASSEUR</t>
-        </is>
-      </c>
-      <c r="G268" s="2" t="inlineStr">
-        <is>
-          <t>secretariat.cardio@hno.fr</t>
-        </is>
-      </c>
-      <c r="H268" s="2" t="inlineStr">
-        <is>
-          <t>direction-generale@hno.fr</t>
-        </is>
-      </c>
+          <t>Consultation de Cardiologie Pédiatrique</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non spécifié / Non</t>
         </is>
       </c>
     </row>
@@ -11537,17 +11545,17 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Hôpital Femme Mère-Enfant -HCL (BRON)</t>
+          <t>Hôpital de la Croix-Rousse - HCL (Lyon)</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1867-establishment6722</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1860-establishment5607</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Consultation de Cardiologie Pédiatrique</t>
+          <t>Service de Cardiologie</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -11572,25 +11580,37 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Hôpital Louis Pradel - HCL (Bron)</t>
+          <t>Hôpital de Villefranche-sur-Saône - HNO (Villefranche-sur-Saône Cedex)</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1867-establishment5613</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1887-establishment5630</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Plateau ambulatoire cardiologique</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
+          <t>CARDIOLOGIE, CARDIOLOGIE INTERVENTIONNELLE ET UNITE DE SOINS INTENSIFS DE CARDIOLOGIE</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Dr Olivier LE VAVASSEUR</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>secretariat.cardio@hno.fr</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>direction-generale@hno.fr</t>
+        </is>
+      </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Non spécifié / Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -11607,17 +11627,17 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Hôpital Louis Pradel - HCL (Bron)</t>
+          <t>Hôpital Femme Mère-Enfant -HCL (BRON)</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1867-establishment5613</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1867-establishment6722</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Plateau Urgences Cardiologiques</t>
+          <t>Consultation de Cardiologie Pédiatrique</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -11652,7 +11672,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Service d'Hémodynamique et de Cardiologie Interventionnelle</t>
+          <t>Plateau ambulatoire cardiologique</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -11660,7 +11680,7 @@
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non spécifié / Non</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11707,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Service d'Imagerie cardio-vasculaire et thoracique</t>
+          <t>Plateau Urgences Cardiologiques</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -11722,7 +11742,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Service de Cardiologie : filière coronaires et valves</t>
+          <t>Service d'Hémodynamique et de Cardiologie Interventionnelle</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -11730,7 +11750,7 @@
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Non spécifié / Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11777,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Service de Cardiologie congénitale adultes et enfants</t>
+          <t>Service d'Imagerie cardio-vasculaire et thoracique</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -11792,7 +11812,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Service de Cardiologie E (cardiologie générale)</t>
+          <t>Service de Cardiologie : filière coronaires et valves</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -11827,7 +11847,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Service de Chirurgie Cardio-Vasculaire A</t>
+          <t>Service de Cardiologie congénitale adultes et enfants</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -11862,7 +11882,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Service de Chirurgie Cardio-Vasculaire B</t>
+          <t>Service de Cardiologie E (cardiologie générale)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -11897,7 +11917,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Service de Chirurgie Cardio-Vasculaire C</t>
+          <t>Service de Chirurgie Cardio-Vasculaire A</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -11922,17 +11942,17 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Hôpital Saint Joseph Saint Luc (Lyon)</t>
+          <t>Hôpital Louis Pradel - HCL (Bron)</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3208-establishment7212</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1867-establishment5613</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Service de Chirurgie Cardio-Vasculaire B</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -11957,29 +11977,21 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Hopital spécialisé des Armées DESGENETTES (LYON 3)</t>
+          <t>Hôpital Louis Pradel - HCL (Bron)</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8038</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1867-establishment5613</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE ET PATHOLOGIE VASCULAIRE 69</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>Dr Delphine MIOULET</t>
-        </is>
-      </c>
-      <c r="G281" s="2" t="inlineStr">
-        <is>
-          <t>cardiologie@hiadcssa.org</t>
-        </is>
-      </c>
+          <t>Service de Chirurgie Cardio-Vasculaire C</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
@@ -12000,29 +12012,21 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Hôpital Lyon Sud HCL (Pierre-Bénite)</t>
+          <t>Hôpital Saint Joseph Saint Luc (Lyon)</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1878-establishment5623</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3208-establishment7212</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Consultations de cardiologie - Explorations fonctionnelles cardiologiques</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>Pr Pierre LANTELME</t>
-        </is>
-      </c>
-      <c r="G282" s="2" t="inlineStr">
-        <is>
-          <t>pierre.lantelme@chu-lyon.fr</t>
-        </is>
-      </c>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
@@ -12033,37 +12037,37 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Haute-Saône</t>
+          <t>Rhône</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>GROUPE HOSPITALIER DE LA HAUTE-SAONE site de Vesoul (VESOUL)</t>
+          <t>Hopital spécialisé des Armées DESGENETTES (LYON 3)</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1902-establishment8474</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8038</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>CARDIOLOGIE ET PATHOLOGIE VASCULAIRE 69</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Dr Lisbeth CART</t>
+          <t>Dr Delphine MIOULET</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>l.cart@gh70.fr</t>
+          <t>cardiologie@hiadcssa.org</t>
         </is>
       </c>
       <c r="H283" t="inlineStr"/>
@@ -12076,31 +12080,39 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Saône-et-Loire</t>
+          <t>Rhône</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Centre hospitalier (MACON)</t>
+          <t>Hôpital Lyon Sud HCL (Pierre-Bénite)</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1908-establishment5650</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1878-establishment5623</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
+          <t>Consultations de cardiologie - Explorations fonctionnelles cardiologiques</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Pr Pierre LANTELME</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>pierre.lantelme@chu-lyon.fr</t>
+        </is>
+      </c>
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
@@ -12111,37 +12123,37 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Saône-et-Loire</t>
+          <t>Haute-Saône</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Hôpital Fondation Hôtel-Dieu du Creusot (LE CREUSOT)</t>
+          <t>GROUPE HOSPITALIER DE LA HAUTE-SAONE site de Vesoul (VESOUL)</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3155-establishment7870</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1902-establishment8474</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Consultations Cardiologie</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Dr Ghassan YANNI</t>
+          <t>Dr Lisbeth CART</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>ghyanni@hoteldieu-creusot.fr</t>
+          <t>l.cart@gh70.fr</t>
         </is>
       </c>
       <c r="H285" t="inlineStr"/>
@@ -12164,29 +12176,21 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Centre hospitalier EHPAD (AUTUN)</t>
+          <t>Centre hospitalier (MACON)</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1935-establishment5674</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1908-establishment5650</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Consultations Cardiologie</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>Dr Patrick BUTTARD</t>
-        </is>
-      </c>
-      <c r="G286" s="2" t="inlineStr">
-        <is>
-          <t>P.BUTTARD@ch-autun.fr</t>
-        </is>
-      </c>
+          <t>CARDIOLOGIE</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
@@ -12207,34 +12211,30 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Centre hospitalier (CHALON-SUR-SAONE)</t>
+          <t>Hôpital Fondation Hôtel-Dieu du Creusot (LE CREUSOT)</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1927-establishment5666</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3155-establishment7870</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Consultations Cardiologie</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Dr Patrick BUTTARD</t>
+          <t>Dr Ghassan YANNI</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>patrick.buttard@ch-chalon71.fr</t>
-        </is>
-      </c>
-      <c r="H287" s="2" t="inlineStr">
-        <is>
-          <t>sylvain.rollot@ch-chalon71.fr</t>
-        </is>
-      </c>
+          <t>ghyanni@hoteldieu-creusot.fr</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12244,37 +12244,37 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Savoie</t>
+          <t>Saône-et-Loire</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Centre hospitalier Métropole Savoie (CHAMBERY)</t>
+          <t>Centre hospitalier EHPAD (AUTUN)</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1996-establishment5735</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1935-establishment5674</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Consultations Cardiologie</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Dr Vincent DESCOTES-GENON</t>
+          <t>Dr Patrick BUTTARD</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>vincent.descotes-genon@ch-metropole-savoie.fr</t>
+          <t>P.BUTTARD@ch-autun.fr</t>
         </is>
       </c>
       <c r="H288" t="inlineStr"/>
@@ -12287,40 +12287,44 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Savoie</t>
+          <t>Saône-et-Loire</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Centre hospitalier Métropole Savoie (AIX-LES-BAINS)</t>
+          <t>Centre hospitalier (CHALON-SUR-SAONE)</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1996-establishment5736</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1927-establishment5666</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Médecine polyvalente à orientation gastro-entérologie et cardiologie</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Dr Léa CARBONE</t>
+          <t>Dr Patrick BUTTARD</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>lea.carbone@ch-metropole-savoie.fr</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr"/>
+          <t>patrick.buttard@ch-chalon71.fr</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>sylvain.rollot@ch-chalon71.fr</t>
+        </is>
+      </c>
       <c r="I289" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12330,22 +12334,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Haute-Savoie</t>
+          <t>Savoie</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Annecy Genevois - site ANNECY (EPAGNY METZ TESSY)</t>
+          <t>Centre hospitalier Métropole Savoie (CHAMBERY)</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2012-establishment5750</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1996-establishment5735</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -12355,19 +12359,15 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Dr Emmanuel DESJOYAUX</t>
+          <t>Dr Vincent DESCOTES-GENON</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>edesjoyaux@ch-annecygenevois.fr</t>
-        </is>
-      </c>
-      <c r="H290" s="2" t="inlineStr">
-        <is>
-          <t>amechoud@ch-annecygenevois.fr</t>
-        </is>
-      </c>
+          <t>vincent.descotes-genon@ch-metropole-savoie.fr</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12377,44 +12377,40 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Haute-Savoie</t>
+          <t>Savoie</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Annecy Genevois - site ANNECY (EPAGNY METZ TESSY)</t>
+          <t>Centre hospitalier Métropole Savoie (AIX-LES-BAINS)</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2012-establishment5750</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure1996-establishment5736</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Cardiologie - USIC - Unité de soins intensifs cardiologiques</t>
+          <t>Médecine polyvalente à orientation gastro-entérologie et cardiologie</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Dr Emmanuel DESJOYAUX</t>
+          <t>Dr Léa CARBONE</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>edesjoyaux@ch-annecygenevois.fr</t>
-        </is>
-      </c>
-      <c r="H291" s="2" t="inlineStr">
-        <is>
-          <t>amechoud@ch-annecygenevois.fr</t>
-        </is>
-      </c>
+          <t>lea.carbone@ch-metropole-savoie.fr</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12434,12 +12430,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Alpes Léman Établissement Support du GHT Léman Mont-Blanc (Contamine sur Arve)</t>
+          <t>Centre Hospitalier Annecy Genevois - site ANNECY (EPAGNY METZ TESSY)</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2013-establishment5751</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2012-establishment5750</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -12449,13 +12445,17 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Dr Vuthik PANH</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr"/>
+          <t>Dr Emmanuel DESJOYAUX</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>edesjoyaux@ch-annecygenevois.fr</t>
+        </is>
+      </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>nmenuet@ch-alpes-leman.fr</t>
+          <t>amechoud@ch-annecygenevois.fr</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -12477,26 +12477,34 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>HOPITAUX DU LEMAN Site Georges PIANTA à THONON (Thonon-les-Bains)</t>
+          <t>Centre Hospitalier Annecy Genevois - site ANNECY (EPAGNY METZ TESSY)</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2017-establishment5755</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2012-establishment5750</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie - USIC - Unité de soins intensifs cardiologiques</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Dr Audrey NGEUTCHA TANTCHOU</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="inlineStr"/>
+          <t>Dr Emmanuel DESJOYAUX</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>edesjoyaux@ch-annecygenevois.fr</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>amechoud@ch-annecygenevois.fr</t>
+        </is>
+      </c>
       <c r="I293" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12516,26 +12524,30 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>HOPITAUX DU LEMAN Site Georges PIANTA à THONON (Thonon-les-Bains)</t>
+          <t>Centre Hospitalier Alpes Léman Établissement Support du GHT Léman Mont-Blanc (Contamine sur Arve)</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2017-establishment5755</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2013-establishment5751</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Explorations fonctionnelles cardiologiques</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Mme Myriam MOUCHET</t>
+          <t>Dr Vuthik PANH</t>
         </is>
       </c>
       <c r="G294" t="inlineStr"/>
-      <c r="H294" t="inlineStr"/>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>nmenuet@ch-alpes-leman.fr</t>
+        </is>
+      </c>
       <c r="I294" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12555,29 +12567,25 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Annecy Genevois site de St Julien en Genevois (Saint-Julien-en-Genevois)</t>
+          <t>HOPITAUX DU LEMAN Site Georges PIANTA à THONON (Thonon-les-Bains)</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2012-establishment5754</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2017-establishment5755</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Cardiologie clinique et explorations fonctionnelles - site de St Julien</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Dr Rachid BENDERBOUS</t>
-        </is>
-      </c>
-      <c r="G295" s="2" t="inlineStr">
-        <is>
-          <t>rbenderbous@ch-annecygenevois.fr</t>
-        </is>
-      </c>
+          <t>Dr Audrey NGEUTCHA TANTCHOU</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
@@ -12598,34 +12606,26 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Intercommunal Hôpitaux du Pays du Mont-Blanc site de SALLANCHES (SALLANCHES)</t>
+          <t>HOPITAUX DU LEMAN Site Georges PIANTA à THONON (Thonon-les-Bains)</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2028-establishment5766</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2017-establishment5755</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>MEDECINE CARDIOLOGIQUE ET GASTROENTEROLOGIE</t>
+          <t>Explorations fonctionnelles cardiologiques</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Dr Patrick BROIN</t>
-        </is>
-      </c>
-      <c r="G296" s="2" t="inlineStr">
-        <is>
-          <t>Meds_Sec@ch-sallanches-chamonix.fr</t>
-        </is>
-      </c>
-      <c r="H296" s="2" t="inlineStr">
-        <is>
-          <t>e.lemiere@ch-sallanches-chamonix.fr</t>
-        </is>
-      </c>
+          <t>Mme Myriam MOUCHET</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12645,27 +12645,27 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Hopital Gabriel Déplante (RUMILLY)</t>
+          <t>Centre Hospitalier Annecy Genevois site de St Julien en Genevois (Saint-Julien-en-Genevois)</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2015-establishment7659</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2012-establishment5754</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>CARDIO-GERIATRIE</t>
+          <t>Cardiologie clinique et explorations fonctionnelles - site de St Julien</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Dr Mathieu CHACORNAC</t>
+          <t>Dr Rachid BENDERBOUS</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>mchacornac@ch-annecygenevois.fr</t>
+          <t>rbenderbous@ch-annecygenevois.fr</t>
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
@@ -12678,38 +12678,42 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Haute-Savoie</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Universitaire Pitié Salpêtrière (Paris)</t>
+          <t>Centre Hospitalier Intercommunal Hôpitaux du Pays du Mont-Blanc site de SALLANCHES (SALLANCHES)</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2048-establishment5783</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2028-establishment5766</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Cardiogénétique et myogénétique moléculaire et cellulaire</t>
+          <t>MEDECINE CARDIOLOGIQUE ET GASTROENTEROLOGIE</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Dr MAGALIE LODIN PASQUIER</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr"/>
+          <t>Dr Patrick BROIN</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>Meds_Sec@ch-sallanches-chamonix.fr</t>
+        </is>
+      </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>choella.akbaraly@aphp.fr</t>
+          <t>e.lemiere@ch-sallanches-chamonix.fr</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -12721,40 +12725,40 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Haute-Savoie</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Universitaire Pitié Salpêtrière (Paris)</t>
+          <t>Hopital Gabriel Déplante (RUMILLY)</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2048-establishment5783</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2015-establishment7659</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>CARDIO-GERIATRIE</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Dr MICHEL ZEITOUNI</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr"/>
-      <c r="H299" s="2" t="inlineStr">
-        <is>
-          <t>choella.akbaraly@aphp.fr</t>
-        </is>
-      </c>
+          <t>Dr Mathieu CHACORNAC</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>mchacornac@ch-annecygenevois.fr</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -12784,12 +12788,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Cardiologie - Hospitalisation</t>
+          <t>Cardiogénétique et myogénétique moléculaire et cellulaire</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Dr MARIA ELISABETA GHEORGHIU</t>
+          <t>Dr MAGALIE LODIN PASQUIER</t>
         </is>
       </c>
       <c r="G300" t="inlineStr"/>
@@ -12827,12 +12831,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Imagerie Cardiovasculaire et Thoracique (ICT)</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Dr PAUL-GYDEON RITVO</t>
+          <t>Dr MICHEL ZEITOUNI</t>
         </is>
       </c>
       <c r="G301" t="inlineStr"/>
@@ -12870,12 +12874,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Lipidologie et Prévention Cardiovasculaire</t>
+          <t>Cardiologie - Hospitalisation</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Dr ANTONIO GALLO</t>
+          <t>Dr MARIA ELISABETA GHEORGHIU</t>
         </is>
       </c>
       <c r="G302" t="inlineStr"/>
@@ -12913,12 +12917,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Pharmacologie oncologique et cardiovasculaire et Oncocardiologie</t>
+          <t>Imagerie Cardiovasculaire et Thoracique (ICT)</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Pr JOE ELIE SALEM</t>
+          <t>Dr PAUL-GYDEON RITVO</t>
         </is>
       </c>
       <c r="G303" t="inlineStr"/>
@@ -12956,12 +12960,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Radiologie cardiovasculaire et interventionnelle</t>
+          <t>Lipidologie et Prévention Cardiovasculaire</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>TRISTAN PITTIN</t>
+          <t>Dr ANTONIO GALLO</t>
         </is>
       </c>
       <c r="G304" t="inlineStr"/>
@@ -12999,12 +13003,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Unité de Cardiologie Ambulatoire Sans et Avec Rendez-vous</t>
+          <t>Pharmacologie oncologique et cardiovasculaire et Oncocardiologie</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Dr CLEMENT DAVRIL</t>
+          <t>Pr JOE ELIE SALEM</t>
         </is>
       </c>
       <c r="G305" t="inlineStr"/>
@@ -13042,12 +13046,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Unité Soins Intensifs Cardiologie (USIC)</t>
+          <t>Radiologie cardiovasculaire et interventionnelle</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Pr JOHANNE SILVAIN</t>
+          <t>TRISTAN PITTIN</t>
         </is>
       </c>
       <c r="G306" t="inlineStr"/>
@@ -13075,33 +13079,33 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Cochin - Port-Royal (Paris)</t>
+          <t>AP-HP Hôpital Universitaire Pitié Salpêtrière (Paris)</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2051-establishment5786</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2048-establishment5783</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Anesthésie en chirurgie digestive, endocrinienne, endoscopie digestive, radiologie et cardiologie interventionnelles</t>
+          <t>Unité de Cardiologie Ambulatoire Sans et Avec Rendez-vous</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Dr ILYES MEKKI</t>
+          <t>Dr CLEMENT DAVRIL</t>
         </is>
       </c>
       <c r="G307" t="inlineStr"/>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>marie-cecile.mocellin@aphp.fr</t>
+          <t>choella.akbaraly@aphp.fr</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non spécifié / Non</t>
         </is>
       </c>
     </row>
@@ -13118,28 +13122,28 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Cochin - Port-Royal (Paris)</t>
+          <t>AP-HP Hôpital Universitaire Pitié Salpêtrière (Paris)</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2051-establishment5786</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2048-establishment5783</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>cardiologie</t>
+          <t>Unité Soins Intensifs Cardiologie (USIC)</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Dr ANISSA ZIDOUNE</t>
+          <t>Pr JOHANNE SILVAIN</t>
         </is>
       </c>
       <c r="G308" t="inlineStr"/>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>marie-cecile.mocellin@aphp.fr</t>
+          <t>choella.akbaraly@aphp.fr</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -13171,12 +13175,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>explorations invasives cardiologiques</t>
+          <t>Anesthésie en chirurgie digestive, endocrinienne, endoscopie digestive, radiologie et cardiologie interventionnelles</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Dr FABIEN PICARD</t>
+          <t>Dr ILYES MEKKI</t>
         </is>
       </c>
       <c r="G309" t="inlineStr"/>
@@ -13187,7 +13191,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Non spécifié / Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -13214,12 +13218,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Imagerie cardiothoracique et oncologique</t>
+          <t>cardiologie</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Pr MARIE PIERRE REVEL DUBOIS</t>
+          <t>Dr ANISSA ZIDOUNE</t>
         </is>
       </c>
       <c r="G310" t="inlineStr"/>
@@ -13247,28 +13251,28 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>AP-HP Groupe hospitalier Lariboisière - Fernand-Widal (Paris)</t>
+          <t>AP-HP Hôpital Cochin - Port-Royal (Paris)</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2043-establishment5778</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2051-establishment5786</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>explorations invasives cardiologiques</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>MARIE CHRISTINE DARRICAU</t>
+          <t>Dr FABIEN PICARD</t>
         </is>
       </c>
       <c r="G311" t="inlineStr"/>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>nolwenn.jacob@aphp.fr</t>
+          <t>marie-cecile.mocellin@aphp.fr</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -13290,28 +13294,28 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>AP-HP Groupe hospitalier Lariboisière - Fernand-Widal (Paris)</t>
+          <t>AP-HP Hôpital Cochin - Port-Royal (Paris)</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2043-establishment5778</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2051-establishment5786</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Explorations Fonctionnelles Cardio-vasculaires et Respiratoires</t>
+          <t>Imagerie cardiothoracique et oncologique</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Dr PIERRE LOZERON</t>
+          <t>Pr MARIE PIERRE REVEL DUBOIS</t>
         </is>
       </c>
       <c r="G312" t="inlineStr"/>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>nolwenn.jacob@aphp.fr</t>
+          <t>marie-cecile.mocellin@aphp.fr</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -13343,12 +13347,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Unité de Soins Intensifs en Cardiologie</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>AURORE LEMAY</t>
+          <t>MARIE CHRISTINE DARRICAU</t>
         </is>
       </c>
       <c r="G313" t="inlineStr"/>
@@ -13376,28 +13380,28 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Bichat - Claude-Bernard (Paris)</t>
+          <t>AP-HP Groupe hospitalier Lariboisière - Fernand-Widal (Paris)</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2038-establishment5775</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2043-establishment5778</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Hospitalisation de cardiologie</t>
+          <t>Explorations Fonctionnelles Cardio-vasculaires et Respiratoires</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Dr JULIA ATTIA</t>
+          <t>Dr PIERRE LOZERON</t>
         </is>
       </c>
       <c r="G314" t="inlineStr"/>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>marie.hiance@aphp.fr</t>
+          <t>nolwenn.jacob@aphp.fr</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -13419,28 +13423,28 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Bichat - Claude-Bernard (Paris)</t>
+          <t>AP-HP Groupe hospitalier Lariboisière - Fernand-Widal (Paris)</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2038-establishment5775</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2043-establishment5778</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Imagerie cardiovasculaire</t>
+          <t>Unité de Soins Intensifs en Cardiologie</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Dr Alexandre FITOUSSI</t>
+          <t>AURORE LEMAY</t>
         </is>
       </c>
       <c r="G315" t="inlineStr"/>
       <c r="H315" s="2" t="inlineStr">
         <is>
-          <t>marie.hiance@aphp.fr</t>
+          <t>nolwenn.jacob@aphp.fr</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -13472,12 +13476,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Réanimation chirurgicale cardiologique</t>
+          <t>Hospitalisation de cardiologie</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Pr DAN LONGROIS</t>
+          <t>Dr JULIA ATTIA</t>
         </is>
       </c>
       <c r="G316" t="inlineStr"/>
@@ -13515,12 +13519,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Soins intensifs de cardiologie</t>
+          <t>Imagerie cardiovasculaire</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Pr GREGORY DUCROCQ</t>
+          <t>Dr Alexandre FITOUSSI</t>
         </is>
       </c>
       <c r="G317" t="inlineStr"/>
@@ -13548,28 +13552,28 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital européen Georges-Pompidou (Paris)</t>
+          <t>AP-HP Hôpital Bichat - Claude-Bernard (Paris)</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2056-establishment5791</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2038-establishment5775</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Biochimie cardiovasculaire</t>
+          <t>Réanimation chirurgicale cardiologique</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>MURIELLE PIETROBONI</t>
+          <t>Pr DAN LONGROIS</t>
         </is>
       </c>
       <c r="G318" t="inlineStr"/>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>Sophie.maraval@egp.aphp.fr</t>
+          <t>marie.hiance@aphp.fr</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -13591,28 +13595,28 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital européen Georges-Pompidou (Paris)</t>
+          <t>AP-HP Hôpital Bichat - Claude-Bernard (Paris)</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2056-establishment5791</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2038-establishment5775</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Cardio-oncologie</t>
+          <t>Soins intensifs de cardiologie</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Dr SEBASTIAN STOICA</t>
+          <t>Pr GREGORY DUCROCQ</t>
         </is>
       </c>
       <c r="G319" t="inlineStr"/>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>Sophie.maraval@egp.aphp.fr</t>
+          <t>marie.hiance@aphp.fr</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -13644,12 +13648,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Biochimie cardiovasculaire</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Dr CATHERINE SZYMANSKI</t>
+          <t>MURIELLE PIETROBONI</t>
         </is>
       </c>
       <c r="G320" t="inlineStr"/>
@@ -13687,10 +13691,14 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Consultation de cardiologie</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr"/>
+          <t>Cardio-oncologie</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Dr SEBASTIAN STOICA</t>
+        </is>
+      </c>
       <c r="G321" t="inlineStr"/>
       <c r="H321" s="2" t="inlineStr">
         <is>
@@ -13726,12 +13734,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Plateau Technique non invasif (Explorations non invasives cardio-vasculaires)</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Dr DORRA M'BAREK RABOUDI</t>
+          <t>Dr CATHERINE SZYMANSKI</t>
         </is>
       </c>
       <c r="G322" t="inlineStr"/>
@@ -13759,28 +13767,24 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>AP-HP Groupe Hospitalier Saint-Louis, Lariboisière, Fernand-Widal Site Saint Louis (Paris)</t>
+          <t>AP-HP Hôpital européen Georges-Pompidou (Paris)</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2044-establishment5779</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2056-establishment5791</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>Dr BENJAMIN SIBILIA</t>
-        </is>
-      </c>
+          <t>Consultation de cardiologie</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr"/>
       <c r="G323" t="inlineStr"/>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>nolwenn.jacob@aphp.fr</t>
+          <t>Sophie.maraval@egp.aphp.fr</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -13802,26 +13806,30 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>HOPITAL PARIS SAINT-JOSEPH (GHPSJ - Maternité Notre-Dame de Bon Secours) (PARIS)</t>
+          <t>AP-HP Hôpital européen Georges-Pompidou (Paris)</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3228-establishment6803</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2056-establishment5791</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
+          <t>Plateau Technique non invasif (Explorations non invasives cardio-vasculaires)</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Dr Romain CADOR</t>
+          <t>Dr DORRA M'BAREK RABOUDI</t>
         </is>
       </c>
       <c r="G324" t="inlineStr"/>
-      <c r="H324" t="inlineStr"/>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>Sophie.maraval@egp.aphp.fr</t>
+        </is>
+      </c>
       <c r="I324" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -13841,12 +13849,12 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Hôpital Hôpital Saint Antoine (Paris)</t>
+          <t>AP-HP Groupe Hospitalier Saint-Louis, Lariboisière, Fernand-Widal Site Saint Louis (Paris)</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2034-establishment5772</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2044-establishment5779</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -13856,13 +13864,13 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Dr CLEMENT DARRICAUD</t>
+          <t>Dr BENJAMIN SIBILIA</t>
         </is>
       </c>
       <c r="G325" t="inlineStr"/>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>choella.akbaraly@aphp.fr</t>
+          <t>nolwenn.jacob@aphp.fr</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -13884,26 +13892,26 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Hôpital Hôpital Saint Antoine (Paris)</t>
+          <t>HOPITAL PARIS SAINT-JOSEPH (GHPSJ - Maternité Notre-Dame de Bon Secours) (PARIS)</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2034-establishment5772</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3228-establishment6803</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Soins intensifs de cardiologie</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr"/>
+          <t>CARDIOLOGIE</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Dr Romain CADOR</t>
+        </is>
+      </c>
       <c r="G326" t="inlineStr"/>
-      <c r="H326" s="2" t="inlineStr">
-        <is>
-          <t>choella.akbaraly@aphp.fr</t>
-        </is>
-      </c>
+      <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -13923,28 +13931,28 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Necker - Enfants Malades (Paris)</t>
+          <t>Hôpital Hôpital Saint Antoine (Paris)</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2053-establishment5788</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2034-establishment5772</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Cardiologie pédiatrique</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>JULES ADER</t>
+          <t>Dr CLEMENT DARRICAUD</t>
         </is>
       </c>
       <c r="G327" t="inlineStr"/>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>marie.Ayoub@aphp.fr</t>
+          <t>choella.akbaraly@aphp.fr</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -13966,28 +13974,24 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Necker - Enfants Malades (Paris)</t>
+          <t>Hôpital Hôpital Saint Antoine (Paris)</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2053-establishment5788</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2034-establishment5772</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Hôpital de jour de cardiologie pédiatrique</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>Pr DAMIEN BONNET</t>
-        </is>
-      </c>
+          <t>Soins intensifs de cardiologie</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr"/>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>marie.Ayoub@aphp.fr</t>
+          <t>choella.akbaraly@aphp.fr</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -14019,12 +14023,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Unité Fonctionnelle de Cardiologie Adulte</t>
+          <t>Cardiologie pédiatrique</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Pr Eloi MARIJON</t>
+          <t>JULES ADER</t>
         </is>
       </c>
       <c r="G329" t="inlineStr"/>
@@ -14052,28 +14056,28 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Tenon (Paris)</t>
+          <t>AP-HP Hôpital Necker - Enfants Malades (Paris)</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2055-establishment5790</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2053-establishment5788</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Hôpital de jour de cardiologie pédiatrique</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Pr ARON ARIEL COHEN</t>
+          <t>Pr DAMIEN BONNET</t>
         </is>
       </c>
       <c r="G330" t="inlineStr"/>
       <c r="H330" s="2" t="inlineStr">
         <is>
-          <t>choella.akbaraly@aphp.fr</t>
+          <t>marie.Ayoub@aphp.fr</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -14095,28 +14099,28 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital universitaire Robert-Debré (Paris)</t>
+          <t>AP-HP Hôpital Necker - Enfants Malades (Paris)</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2039-establishment5776</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2053-establishment5788</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Unité Fonctionnelle de Cardiologie Adulte</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Dr BASTIEN MOYSSET</t>
+          <t>Pr Eloi MARIJON</t>
         </is>
       </c>
       <c r="G331" t="inlineStr"/>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>nolwenn.jacob@aphp.fr</t>
+          <t>marie.Ayoub@aphp.fr</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -14138,22 +14142,30 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>HOPITAL HOPITAL LEOPOLD BELLAN (PARIS)</t>
+          <t>AP-HP Hôpital Tenon (Paris)</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3238-establishment7346</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2055-establishment5790</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>UNITE DE READAPTATION CARDIO-VASCULAIRE</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr"/>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Pr ARON ARIEL COHEN</t>
+        </is>
+      </c>
       <c r="G332" t="inlineStr"/>
-      <c r="H332" t="inlineStr"/>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
       <c r="I332" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14173,26 +14185,30 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Hôpital Hôtel Dieu (AP-HP) (Paris)</t>
+          <t>AP-HP Hôpital universitaire Robert-Debré (Paris)</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2041-establishment5777</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2039-establishment5776</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>HTA cardiologie</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>ELEONORE SOTTO</t>
+          <t>Dr BASTIEN MOYSSET</t>
         </is>
       </c>
       <c r="G333" t="inlineStr"/>
-      <c r="H333" t="inlineStr"/>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>nolwenn.jacob@aphp.fr</t>
+        </is>
+      </c>
       <c r="I333" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14202,27 +14218,27 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Seine-Maritime</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Hôpital Charles-Nicolle (Rouen)</t>
+          <t>HOPITAL HOPITAL LEOPOLD BELLAN (PARIS)</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2057-establishment1353</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3238-establishment7346</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>UNITE DE READAPTATION CARDIO-VASCULAIRE</t>
         </is>
       </c>
       <c r="F334" t="inlineStr"/>
@@ -14237,30 +14253,34 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Seine-Maritime</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Hôpital Charles-Nicolle (Rouen)</t>
+          <t>Hôpital Hôtel Dieu (AP-HP) (Paris)</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2057-establishment1353</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2041-establishment5777</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Service de Chirurgie Thoracique et cardio-vasculaire</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr"/>
+          <t>HTA cardiologie</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>ELEONORE SOTTO</t>
+        </is>
+      </c>
       <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr">
@@ -14282,12 +14302,12 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Intercommunal Elbeuf-Louviers/Val de Reuil (ELBEUF)</t>
+          <t>Hôpital Charles-Nicolle (Rouen)</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2098-establishment5829</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2057-establishment1353</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -14295,16 +14315,8 @@
           <t>Cardiologie</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>Dr Fabian TOURNEVACHE</t>
-        </is>
-      </c>
-      <c r="G336" s="2" t="inlineStr">
-        <is>
-          <t>fabian.tournevache@chi-elbeuf-louviers.fr</t>
-        </is>
-      </c>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr">
         <is>
@@ -14325,34 +14337,22 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Groupe Hospitalier du Havre Hôpital Jacques Monod (MONTIVILLIERS)</t>
+          <t>Hôpital Charles-Nicolle (Rouen)</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2059-establishment3306</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2057-establishment1353</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>Dr Emmanuel LECLUSE</t>
-        </is>
-      </c>
-      <c r="G337" s="2" t="inlineStr">
-        <is>
-          <t>emmanuel.lecluse@ch-havre.fr</t>
-        </is>
-      </c>
-      <c r="H337" s="2" t="inlineStr">
-        <is>
-          <t>melanie.couturier@ch-havre.fr</t>
-        </is>
-      </c>
+          <t>Service de Chirurgie Thoracique et cardio-vasculaire</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14372,34 +14372,30 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Groupe Hospitalier du Havre Hôpital Jacques Monod (MONTIVILLIERS)</t>
+          <t>Centre Hospitalier Intercommunal Elbeuf-Louviers/Val de Reuil (ELBEUF)</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2059-establishment3306</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2098-establishment5829</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>SSR cardio-respiratoire (HC et HDJ)</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Dr Emmanuel LECLUSE</t>
+          <t>Dr Fabian TOURNEVACHE</t>
         </is>
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>emmanuel.lecluse@ch-havre.fr</t>
-        </is>
-      </c>
-      <c r="H338" s="2" t="inlineStr">
-        <is>
-          <t>melanie.couturier@ch-havre.fr</t>
-        </is>
-      </c>
+          <t>fabian.tournevache@chi-elbeuf-louviers.fr</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14419,32 +14415,32 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER DE DIEPPE : Site Pasteur (Dieppe)</t>
+          <t>Groupe Hospitalier du Havre Hôpital Jacques Monod (MONTIVILLIERS)</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2071-establishment5802</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2059-establishment3306</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE ET UNITE DE SOINS INTENSIFS CARDIOLOGIQUES</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Dr Carole HUCHE</t>
+          <t>Dr Emmanuel LECLUSE</t>
         </is>
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>chuche@ch-dieppe.fr</t>
+          <t>emmanuel.lecluse@ch-havre.fr</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
-          <t>rdubuisson@ch-dieppe.fr</t>
+          <t>melanie.couturier@ch-havre.fr</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -14466,30 +14462,34 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Intercommunal (FECAMP)</t>
+          <t>Groupe Hospitalier du Havre Hôpital Jacques Monod (MONTIVILLIERS)</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2089-establishment5820</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2059-establishment3306</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Médecine à orientation cardiologique</t>
+          <t>SSR cardio-respiratoire (HC et HDJ)</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Dr Philippe CALOT</t>
+          <t>Dr Emmanuel LECLUSE</t>
         </is>
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>philippe.calot@ch-fecamp.fr</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr"/>
+          <t>emmanuel.lecluse@ch-havre.fr</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>melanie.couturier@ch-havre.fr</t>
+        </is>
+      </c>
       <c r="I340" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14499,40 +14499,44 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Seine-et-Marne</t>
+          <t>Seine-Maritime</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Grand Hôpital de l'Est Francilien (JOSSIGNY)</t>
+          <t>CENTRE HOSPITALIER DE DIEPPE : Site Pasteur (Dieppe)</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5865</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2071-establishment5802</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Cardiologie - USIC - HDJ - HDS - Explorations fonctionnelles cardiologiques - MLV</t>
+          <t>CARDIOLOGIE ET UNITE DE SOINS INTENSIFS CARDIOLOGIQUES</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Dr Simon ELHADAD</t>
+          <t>Dr Carole HUCHE</t>
         </is>
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>mgerber@ghef.fr</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr"/>
+          <t>chuche@ch-dieppe.fr</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>rdubuisson@ch-dieppe.fr</t>
+        </is>
+      </c>
       <c r="I341" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14542,35 +14546,39 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Seine-et-Marne</t>
+          <t>Seine-Maritime</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Grand Hôpital de l'Est Francilien (JOSSIGNY)</t>
+          <t>Centre Hospitalier Intercommunal (FECAMP)</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5865</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2089-establishment5820</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Unité de cardiologie du sport - MLV</t>
+          <t>Médecine à orientation cardiologique</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Dr Simon ELHADAD</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr"/>
+          <t>Dr Philippe CALOT</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>philippe.calot@ch-fecamp.fr</t>
+        </is>
+      </c>
       <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr">
         <is>
@@ -14591,27 +14599,27 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Hôpital de Melun-Sénart - Groupe hospitalier Sud Ile-de-France (Melun)</t>
+          <t>Grand Hôpital de l'Est Francilien (JOSSIGNY)</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2117-establishment10636</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5865</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie - USIC - HDJ - HDS - Explorations fonctionnelles cardiologiques - MLV</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Dr Cyrus MOINI</t>
+          <t>Dr Simon ELHADAD</t>
         </is>
       </c>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>cyrus.moini@ghsif.fr</t>
+          <t>mgerber@ghef.fr</t>
         </is>
       </c>
       <c r="H343" t="inlineStr"/>
@@ -14634,22 +14642,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Grand Hôpital de l'Est Francilien (MEAUX)</t>
+          <t>Grand Hôpital de l'Est Francilien (JOSSIGNY)</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5849</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5865</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Cardiologie - USIC - Explorations fonctionnelles cardiologiques - MX</t>
+          <t>Unité de cardiologie du sport - MLV</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Dr Sergio PERNA</t>
+          <t>Dr Simon ELHADAD</t>
         </is>
       </c>
       <c r="G344" t="inlineStr"/>
@@ -14673,25 +14681,29 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Grand Hôpital de l'Est Francilien (COULOMMIERS)</t>
+          <t>Hôpital de Melun-Sénart - Groupe hospitalier Sud Ile-de-France (Melun)</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5872</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2117-establishment10636</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Cardiologie - Explorations fonctionnelles cardiologiques - CLM</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Dr Simon ELHADAD</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr"/>
+          <t>Dr Cyrus MOINI</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>cyrus.moini@ghsif.fr</t>
+        </is>
+      </c>
       <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr">
         <is>
@@ -14712,29 +14724,25 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Centre hospitalier Léon Binet (Provins)</t>
+          <t>Grand Hôpital de l'Est Francilien (MEAUX)</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2140-establishment5869</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5849</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Cardiologie et maladies vasculaires</t>
+          <t>Cardiologie - USIC - Explorations fonctionnelles cardiologiques - MX</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Dr Farid TAOURI</t>
-        </is>
-      </c>
-      <c r="G346" s="2" t="inlineStr">
-        <is>
-          <t>ehaddad@ch-provins.fr</t>
-        </is>
-      </c>
+          <t>Dr Sergio PERNA</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr"/>
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr">
         <is>
@@ -14755,20 +14763,24 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Site hospitalier de Fontainebleau (FONTAINEBLEAU)</t>
+          <t>Grand Hôpital de l'Est Francilien (COULOMMIERS)</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2132-establishment5861</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2119-establishment5872</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Médecine A-B (neurologie - cardiologie)</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr"/>
+          <t>Cardiologie - Explorations fonctionnelles cardiologiques - CLM</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Dr Simon ELHADAD</t>
+        </is>
+      </c>
       <c r="G347" t="inlineStr"/>
       <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr">
@@ -14790,27 +14802,27 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Site de Montereau-Fault-Yonne (MONTEREAU FAUT YONNE)</t>
+          <t>Centre hospitalier Léon Binet (Provins)</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2132-establishment5884</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2140-establishment5869</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie et maladies vasculaires</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Dr Adama SANGARE</t>
+          <t>Dr Farid TAOURI</t>
         </is>
       </c>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>adama.sangare@ch-montereau.fr</t>
+          <t>ehaddad@ch-provins.fr</t>
         </is>
       </c>
       <c r="H348" t="inlineStr"/>
@@ -14823,44 +14835,32 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Yvelines</t>
+          <t>Seine-et-Marne</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Centre hospitalier intercommunal de Poissy-Saint-Germain-en-Laye &gt; Site hospitalier de Poissy (POISSY)</t>
+          <t>Site hospitalier de Fontainebleau (FONTAINEBLEAU)</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2163-establishment2557</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2132-establishment5861</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>Dr David BERVILLE</t>
-        </is>
-      </c>
-      <c r="G349" s="2" t="inlineStr">
-        <is>
-          <t>david.berville@ght-yvelinesnord.fr</t>
-        </is>
-      </c>
-      <c r="H349" s="2" t="inlineStr">
-        <is>
-          <t>agathe.benoist@ght-yvelinesnord.fr</t>
-        </is>
-      </c>
+          <t>Médecine A-B (neurologie - cardiologie)</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr"/>
+      <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -14870,22 +14870,22 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Yvelines</t>
+          <t>Seine-et-Marne</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Hôpital André Mignot Centre Hospitalier de Versailles (Le Chesnay)</t>
+          <t>Site de Montereau-Fault-Yonne (MONTEREAU FAUT YONNE)</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2165-establishment5893</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2132-establishment5884</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Dr Geraldine GIBAULT GENTY</t>
+          <t>Dr Adama SANGARE</t>
         </is>
       </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>ggibaultgenty@ght78sud.fr</t>
+          <t>adama.sangare@ch-montereau.fr</t>
         </is>
       </c>
       <c r="H350" t="inlineStr"/>
@@ -14923,12 +14923,12 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Centre hospitalier François Quesnay (Mantes-la-Jolie)</t>
+          <t>Centre hospitalier intercommunal de Poissy-Saint-Germain-en-Laye &gt; Site hospitalier de Poissy (POISSY)</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2166-establishment5894</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2163-establishment2557</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -14970,27 +14970,27 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Centre hospitalier (RAMBOUILLET)</t>
+          <t>Hôpital André Mignot Centre Hospitalier de Versailles (Le Chesnay)</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2179-establishment5908</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2165-establishment5893</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Cardiologie-Pneumologie-USIC</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Dr Christophe CHAVELAS</t>
+          <t>Dr Geraldine GIBAULT GENTY</t>
         </is>
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>cchavelas@ght78sud.fr</t>
+          <t>ggibaultgenty@ght78sud.fr</t>
         </is>
       </c>
       <c r="H352" t="inlineStr"/>
@@ -15013,22 +15013,34 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Etablissement SSR et Institut de Néphrologie de Maisons-Laffitte Groupe MGEN (Maisons-Laffitte)</t>
+          <t>Centre hospitalier François Quesnay (Mantes-la-Jolie)</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3220-establishment8546</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2166-establishment5894</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Service de SSR Cardiologie-Néphrologie-Polyvalents</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr"/>
-      <c r="G353" t="inlineStr"/>
-      <c r="H353" t="inlineStr"/>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Dr David BERVILLE</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>david.berville@ght-yvelinesnord.fr</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>agathe.benoist@ght-yvelinesnord.fr</t>
+        </is>
+      </c>
       <c r="I353" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15048,27 +15060,27 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Centre hospitalier intercommunal de Poissy-Saint-Germain-en-Laye &gt; Site hospitalier de Saint-Germain-en-Laye (SAINT-GERMAIN-EN-LAYE)</t>
+          <t>Centre hospitalier (RAMBOUILLET)</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2163-establishment5891</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2179-establishment5908</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie-Pneumologie-USIC</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Dr David BERVILLE</t>
+          <t>Dr Christophe CHAVELAS</t>
         </is>
       </c>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>david.berville@ght-yvelinesnord.fr</t>
+          <t>cchavelas@ght78sud.fr</t>
         </is>
       </c>
       <c r="H354" t="inlineStr"/>
@@ -15081,36 +15093,32 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Deux-Sèvres</t>
+          <t>Yvelines</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Niort)</t>
+          <t>Etablissement SSR et Institut de Néphrologie de Maisons-Laffitte Groupe MGEN (Maisons-Laffitte)</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2190-establishment5917</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3220-establishment8546</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Cardiologie et Explorations Cardiovasculaires</t>
+          <t>Service de SSR Cardiologie-Néphrologie-Polyvalents</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr"/>
-      <c r="H355" s="2" t="inlineStr">
-        <is>
-          <t>karine.morin@ch-niort.fr</t>
-        </is>
-      </c>
+      <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15120,22 +15128,22 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Somme</t>
+          <t>Yvelines</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>CHU Amiens Picardie - Site Sud (Amiens)</t>
+          <t>Centre hospitalier intercommunal de Poissy-Saint-Germain-en-Laye &gt; Site hospitalier de Saint-Germain-en-Laye (SAINT-GERMAIN-EN-LAYE)</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2224-establishment1360</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2163-establishment5891</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -15143,8 +15151,16 @@
           <t>Cardiologie</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr"/>
-      <c r="G356" t="inlineStr"/>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Dr David BERVILLE</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>david.berville@ght-yvelinesnord.fr</t>
+        </is>
+      </c>
       <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr">
         <is>
@@ -15155,32 +15171,36 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Somme</t>
+          <t>Deux-Sèvres</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>CHU Amiens Picardie - Site Sud (Amiens)</t>
+          <t>Centre hospitalier (Niort)</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2224-establishment1360</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2190-establishment5917</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Cardiologie et Pneumo-Allergologie Pédiatriques</t>
+          <t>Cardiologie et Explorations Cardiovasculaires</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr"/>
-      <c r="H357" t="inlineStr"/>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>karine.morin@ch-niort.fr</t>
+        </is>
+      </c>
       <c r="I357" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15210,7 +15230,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Cardiologie, Rythmologie et Stimulation Cardiaque</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
@@ -15245,14 +15265,10 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Réanimation Médico-Chirurgicale Cardio Thoracique Vasculaire et Respiratoire</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>Pr Hervé DUPONT</t>
-        </is>
-      </c>
+          <t>Cardiologie et Pneumo-Allergologie Pédiatriques</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
       <c r="G359" t="inlineStr"/>
       <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr">
@@ -15284,7 +15300,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Unité de Soins Intensifs de Cardiologie (USIC)</t>
+          <t>Cardiologie, Rythmologie et Stimulation Cardiaque</t>
         </is>
       </c>
       <c r="F360" t="inlineStr"/>
@@ -15309,29 +15325,25 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Abbeville)</t>
+          <t>CHU Amiens Picardie - Site Sud (Amiens)</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2230-establishment5957</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2224-establishment1360</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Médecine cardiologique - USIC</t>
+          <t>Réanimation Médico-Chirurgicale Cardio Thoracique Vasculaire et Respiratoire</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Dr Vincent MOUQUET</t>
-        </is>
-      </c>
-      <c r="G361" s="2" t="inlineStr">
-        <is>
-          <t>hautbout.karine@ch-abbeville.fr</t>
-        </is>
-      </c>
+          <t>Pr Hervé DUPONT</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr">
         <is>
@@ -15352,29 +15364,21 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Abbeville)</t>
+          <t>CHU Amiens Picardie - Site Sud (Amiens)</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2230-establishment5957</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2224-establishment1360</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Soins de suite et de réadaptation cardio-respiratoires</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>Dr Olivier LELEU</t>
-        </is>
-      </c>
-      <c r="G362" s="2" t="inlineStr">
-        <is>
-          <t>hautbout.karine@ch-abbeville.fr</t>
-        </is>
-      </c>
+          <t>Unité de Soins Intensifs de Cardiologie (USIC)</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr">
         <is>
@@ -15395,27 +15399,27 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Corbie)</t>
+          <t>Centre hospitalier (Abbeville)</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2258-establishment5983</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2230-establishment5957</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>SSR - Réadaptation cardio-vasculaire</t>
+          <t>Médecine cardiologique - USIC</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Dr Florent KRIM</t>
+          <t>Dr Vincent MOUQUET</t>
         </is>
       </c>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>cardiovasculaire@ch-corbie.fr</t>
+          <t>hautbout.karine@ch-abbeville.fr</t>
         </is>
       </c>
       <c r="H363" t="inlineStr"/>
@@ -15428,31 +15432,39 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Tarn</t>
+          <t>Somme</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>HOPITAL DU PAYS d'AUTAN - Site de Castres (Castres)</t>
+          <t>Centre hospitalier (Abbeville)</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2261-establishment5986</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2230-establishment5957</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr"/>
-      <c r="G364" t="inlineStr"/>
+          <t>Soins de suite et de réadaptation cardio-respiratoires</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Dr Olivier LELEU</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>hautbout.karine@ch-abbeville.fr</t>
+        </is>
+      </c>
       <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr">
         <is>
@@ -15463,31 +15475,39 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Tarn</t>
+          <t>Somme</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>HOPITAL DU PAYS d'AUTAN - Site de Castres (Castres)</t>
+          <t>Centre hospitalier (Corbie)</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2261-establishment5986</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2258-establishment5983</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE et USIC</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr"/>
-      <c r="G365" t="inlineStr"/>
+          <t>SSR - Réadaptation cardio-vasculaire</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Dr Florent KRIM</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>cardiovasculaire@ch-corbie.fr</t>
+        </is>
+      </c>
       <c r="H365" t="inlineStr"/>
       <c r="I365" t="inlineStr">
         <is>
@@ -15508,26 +15528,22 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Albi)</t>
+          <t>HOPITAL DU PAYS d'AUTAN - Site de Castres (Castres)</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2260-establishment5985</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2261-establishment5986</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>CARDIOLOGIE</t>
         </is>
       </c>
       <c r="F366" t="inlineStr"/>
       <c r="G366" t="inlineStr"/>
-      <c r="H366" s="2" t="inlineStr">
-        <is>
-          <t>jeremy.luceno@ch-albi.fr</t>
-        </is>
-      </c>
+      <c r="H366" t="inlineStr"/>
       <c r="I366" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15537,44 +15553,32 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Tarn-et-Garonne</t>
+          <t>Tarn</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Général (MONTAUBAN)</t>
+          <t>HOPITAL DU PAYS d'AUTAN - Site de Castres (Castres)</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2269-establishment5994</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2261-establishment5986</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>Dr Nouredinne EL HAJJAJI</t>
-        </is>
-      </c>
-      <c r="G367" s="2" t="inlineStr">
-        <is>
-          <t>n.elhajjaji@ch-montauban.fr</t>
-        </is>
-      </c>
-      <c r="H367" s="2" t="inlineStr">
-        <is>
-          <t>secretariat-dsqgr@ch-montauban.fr</t>
-        </is>
-      </c>
+          <t>CARDIOLOGIE et USIC</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr"/>
       <c r="I367" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15584,42 +15588,34 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Tarn-et-Garonne</t>
+          <t>Tarn</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Général (MONTAUBAN)</t>
+          <t>Centre hospitalier (Albi)</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2269-establishment5994</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2260-establishment5985</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Soins Intensifs Neuro-Cardio-Vasculaires</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>Dr Nouredinne EL HAJJAJI</t>
-        </is>
-      </c>
-      <c r="G368" s="2" t="inlineStr">
-        <is>
-          <t>n.elhajjaji@ch-montauban.fr</t>
-        </is>
-      </c>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr"/>
       <c r="H368" s="2" t="inlineStr">
         <is>
-          <t>secretariat-dsqgr@ch-montauban.fr</t>
+          <t>jeremy.luceno@ch-albi.fr</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -15631,42 +15627,42 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Var</t>
+          <t>Tarn-et-Garonne</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>C.H.I.T.S. Hôpital Sainte Musse (Toulon)</t>
+          <t>Centre Hospitalier Général (MONTAUBAN)</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2284-establishment2219</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2269-establishment5994</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Cardiologie A</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Dr Jean-Michel TARTIERE</t>
+          <t>Dr Nouredinne EL HAJJAJI</t>
         </is>
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>jean-michel.tartiere@ch-toulon.fr</t>
+          <t>n.elhajjaji@ch-montauban.fr</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
         <is>
-          <t>Corentin.Balluais@ch-toulon.fr</t>
+          <t>secretariat-dsqgr@ch-montauban.fr</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -15678,42 +15674,42 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Var</t>
+          <t>Tarn-et-Garonne</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>C.H.I.T.S. Hôpital Sainte Musse (Toulon)</t>
+          <t>Centre Hospitalier Général (MONTAUBAN)</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2284-establishment2219</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2269-establishment5994</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Unité de Soins intensifs cardiologiques (USIC)</t>
+          <t>Soins Intensifs Neuro-Cardio-Vasculaires</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Dr Farid CHALLAL</t>
+          <t>Dr Nouredinne EL HAJJAJI</t>
         </is>
       </c>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>farid.challal@ch-toulon.fr</t>
+          <t>n.elhajjaji@ch-montauban.fr</t>
         </is>
       </c>
       <c r="H370" s="2" t="inlineStr">
         <is>
-          <t>Corentin.Balluais@ch-toulon.fr</t>
+          <t>secretariat-dsqgr@ch-montauban.fr</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -15735,30 +15731,34 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Intercommunal (FREJUS)</t>
+          <t>C.H.I.T.S. Hôpital Sainte Musse (Toulon)</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2302-establishment6026</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2284-establishment2219</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie A</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Dr Hélène ZAKARIAN</t>
+          <t>Dr Jean-Michel TARTIERE</t>
         </is>
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>zakarian-h@chi-fsr.fr</t>
-        </is>
-      </c>
-      <c r="H371" t="inlineStr"/>
+          <t>jean-michel.tartiere@ch-toulon.fr</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>Corentin.Balluais@ch-toulon.fr</t>
+        </is>
+      </c>
       <c r="I371" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15778,30 +15778,34 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Hôpital National d'Instruction des armées SAINTE ANNE (TOULON)</t>
+          <t>C.H.I.T.S. Hôpital Sainte Musse (Toulon)</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8042</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2284-establishment2219</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE ET MALADIES VASCULAIRES HIA Sainte-Anne</t>
+          <t>Unité de Soins intensifs cardiologiques (USIC)</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Pr Gilles CELLARIER</t>
+          <t>Dr Farid CHALLAL</t>
         </is>
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>cardiologie@hia-sainte-anne.ssa.msante.fr</t>
-        </is>
-      </c>
-      <c r="H372" t="inlineStr"/>
+          <t>farid.challal@ch-toulon.fr</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>Corentin.Balluais@ch-toulon.fr</t>
+        </is>
+      </c>
       <c r="I372" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15821,12 +15825,12 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de la Dracénie (Draguignan)</t>
+          <t>Centre Hospitalier Intercommunal (FREJUS)</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2283-establishment6008</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2302-establishment6026</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -15834,8 +15838,16 @@
           <t>Cardiologie</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr"/>
-      <c r="G373" t="inlineStr"/>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Dr Hélène ZAKARIAN</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>zakarian-h@chi-fsr.fr</t>
+        </is>
+      </c>
       <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr">
         <is>
@@ -15856,27 +15868,27 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>HCL Hôpital Renée Sabran (Giens)</t>
+          <t>Hôpital National d'Instruction des armées SAINTE ANNE (TOULON)</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2294-establishment6018</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8042</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Consultations Cardiologie</t>
+          <t>CARDIOLOGIE ET MALADIES VASCULAIRES HIA Sainte-Anne</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Mme Daniele RAUFAST</t>
+          <t>Pr Gilles CELLARIER</t>
         </is>
       </c>
       <c r="G374" s="2" t="inlineStr">
         <is>
-          <t>daniele.raufast@chu-lyon.fr</t>
+          <t>cardiologie@hia-sainte-anne.ssa.msante.fr</t>
         </is>
       </c>
       <c r="H374" t="inlineStr"/>
@@ -15889,22 +15901,22 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Vaucluse</t>
+          <t>Var</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Henri Duffaut (Avignon)</t>
+          <t>Centre Hospitalier de la Dracénie (Draguignan)</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2347-establishment6067</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2283-establishment6008</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -15914,11 +15926,7 @@
       </c>
       <c r="F375" t="inlineStr"/>
       <c r="G375" t="inlineStr"/>
-      <c r="H375" s="2" t="inlineStr">
-        <is>
-          <t>baratier.aurelie@ch-avignon.fr</t>
-        </is>
-      </c>
+      <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15928,44 +15936,40 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Vaucluse</t>
+          <t>Var</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Centre hospitalier intercommunal de Cavaillon - Lauris (Cavaillon)</t>
+          <t>HCL Hôpital Renée Sabran (Giens)</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2329-establishment6052</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2294-establishment6018</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Service de médecine A - Cardiologie</t>
+          <t>Consultations Cardiologie</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Dr Patrick GIRAUD</t>
+          <t>Mme Daniele RAUFAST</t>
         </is>
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>p.giraud@ch-cavaillon.fr</t>
-        </is>
-      </c>
-      <c r="H376" s="2" t="inlineStr">
-        <is>
-          <t>anne.desroche@ch-cavaillon.fr</t>
-        </is>
-      </c>
+          <t>daniele.raufast@chu-lyon.fr</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -15975,22 +15979,22 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Vendée</t>
+          <t>Vaucluse</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Départemental Vendée, site de La Roche-sur-Yon (La Roche-sur-Yon)</t>
+          <t>Centre Hospitalier Henri Duffaut (Avignon)</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2349-establishment6069</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2347-establishment6067</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -16000,7 +16004,11 @@
       </c>
       <c r="F377" t="inlineStr"/>
       <c r="G377" t="inlineStr"/>
-      <c r="H377" t="inlineStr"/>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>baratier.aurelie@ch-avignon.fr</t>
+        </is>
+      </c>
       <c r="I377" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16010,36 +16018,44 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Vendée</t>
+          <t>Vaucluse</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Côte de Lumière (LES SABLES D'OLONNE)</t>
+          <t>Centre hospitalier intercommunal de Cavaillon - Lauris (Cavaillon)</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2352-establishment6071</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2329-establishment6052</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Service de médecine A - Cardiologie</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Dr Claire BOIVINEAU</t>
-        </is>
-      </c>
-      <c r="G378" t="inlineStr"/>
-      <c r="H378" t="inlineStr"/>
+          <t>Dr Patrick GIRAUD</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>p.giraud@ch-cavaillon.fr</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>anne.desroche@ch-cavaillon.fr</t>
+        </is>
+      </c>
       <c r="I378" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16059,24 +16075,20 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Côte de Lumière (LES SABLES D'OLONNE)</t>
+          <t>Centre Hospitalier Départemental Vendée, site de La Roche-sur-Yon (La Roche-sur-Yon)</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2352-establishment6071</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2349-establishment6069</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Unité de Soins Intensifs de Cardiologie (USIC)</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>Dr Patrice PERNOLLET</t>
-        </is>
-      </c>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr"/>
       <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr">
@@ -16098,12 +16110,12 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Loire Vendée Océan - site de Challans (CHALLANS)</t>
+          <t>Centre Hospitalier Côte de Lumière (LES SABLES D'OLONNE)</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2365-establishment6082</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2352-establishment6071</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -16111,7 +16123,11 @@
           <t>Cardiologie</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr"/>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Dr Claire BOIVINEAU</t>
+        </is>
+      </c>
       <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr">
@@ -16133,26 +16149,26 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Centre hospitalier (FONTENAY LE COMTE)</t>
+          <t>Centre Hospitalier Côte de Lumière (LES SABLES D'OLONNE)</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2356-establishment6075</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2352-establishment6071</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Cardiologie et neuro-vasculaire</t>
-        </is>
-      </c>
-      <c r="F381" t="inlineStr"/>
+          <t>Unité de Soins Intensifs de Cardiologie (USIC)</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Dr Patrice PERNOLLET</t>
+        </is>
+      </c>
       <c r="G381" t="inlineStr"/>
-      <c r="H381" s="2" t="inlineStr">
-        <is>
-          <t>corentin.ringot@ght85.fr</t>
-        </is>
-      </c>
+      <c r="H381" t="inlineStr"/>
       <c r="I381" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16162,44 +16178,32 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Vendée</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Site hospitalier de Poitiers La Miletrie (Poitiers)</t>
+          <t>Centre Hospitalier Loire Vendée Océan - site de Challans (CHALLANS)</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment1364</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2365-establishment6082</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Chirurgie cardio-thoracique</t>
-        </is>
-      </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>Pr Pierre CORBI</t>
-        </is>
-      </c>
-      <c r="G382" s="2" t="inlineStr">
-        <is>
-          <t>pierre.corbi@chu-poitiers.fr</t>
-        </is>
-      </c>
-      <c r="H382" s="2" t="inlineStr">
-        <is>
-          <t>heloise.baux@chu-poitiers.fr</t>
-        </is>
-      </c>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr"/>
       <c r="I382" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16209,42 +16213,34 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Vendée</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Site hospitalier de Poitiers La Miletrie (Poitiers)</t>
+          <t>Centre hospitalier (FONTENAY LE COMTE)</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment1364</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2356-establishment6075</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Service médico-chirurgical de Cardiologie</t>
-        </is>
-      </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>Pr Luc-Philippe CHRISTIAENS</t>
-        </is>
-      </c>
-      <c r="G383" s="2" t="inlineStr">
-        <is>
-          <t>luc-philippe.christiaens@chu-poitiers.fr</t>
-        </is>
-      </c>
+          <t>Cardiologie et neuro-vasculaire</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr"/>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>heloise.baux@chu-poitiers.fr</t>
+          <t>corentin.ringot@ght85.fr</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -16266,30 +16262,34 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Site hospitalier de Châtellerault (Chatellerault)</t>
+          <t>Site hospitalier de Poitiers La Miletrie (Poitiers)</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment6093</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment1364</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Chirurgie cardio-thoracique</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Dr Damien COISNE</t>
+          <t>Pr Pierre CORBI</t>
         </is>
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>cardiologie@ghnv.fr</t>
-        </is>
-      </c>
-      <c r="H384" t="inlineStr"/>
+          <t>pierre.corbi@chu-poitiers.fr</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>heloise.baux@chu-poitiers.fr</t>
+        </is>
+      </c>
       <c r="I384" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16309,30 +16309,34 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Site hospitalier de Montmorillon (Montmorillon)</t>
+          <t>Site hospitalier de Poitiers La Miletrie (Poitiers)</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment6098</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment1364</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Médecine générale - Cardiologie - Rhumatologie - Angiologie - Diabétologie/endocrinologie - Douleur</t>
+          <t>Service médico-chirurgical de Cardiologie</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Dr Jean-Claude LORENZO</t>
+          <t>Pr Luc-Philippe CHRISTIAENS</t>
         </is>
       </c>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>jean-claude.lorenzo@ch-montmorillon.fr</t>
-        </is>
-      </c>
-      <c r="H385" t="inlineStr"/>
+          <t>luc-philippe.christiaens@chu-poitiers.fr</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>heloise.baux@chu-poitiers.fr</t>
+        </is>
+      </c>
       <c r="I385" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16342,22 +16346,22 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Haute-Vienne</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>CHU Dupuytren 1 (Limoges)</t>
+          <t>Site hospitalier de Châtellerault (Chatellerault)</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2386-establishment1372</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment6093</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -16367,10 +16371,14 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Pr Victor ABOYANS</t>
-        </is>
-      </c>
-      <c r="G386" t="inlineStr"/>
+          <t>Dr Damien COISNE</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>cardiologie@ghnv.fr</t>
+        </is>
+      </c>
       <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr">
         <is>
@@ -16381,36 +16389,40 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Vosges</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Centre hospitalier Nouvel Hôpital d'Epinal - plateau de la justice (Epinal)</t>
+          <t>Site hospitalier de Montmorillon (Montmorillon)</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2413-establishment6126</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2376-establishment6098</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Cardiologie USIC Plateau Technique</t>
-        </is>
-      </c>
-      <c r="F387" t="inlineStr"/>
-      <c r="G387" t="inlineStr"/>
-      <c r="H387" s="2" t="inlineStr">
-        <is>
-          <t>sec.direction@ch-ed.fr</t>
-        </is>
-      </c>
+          <t>Médecine générale - Cardiologie - Rhumatologie - Angiologie - Diabétologie/endocrinologie - Douleur</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Dr Jean-Claude LORENZO</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>jean-claude.lorenzo@ch-montmorillon.fr</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16420,36 +16432,36 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Vosges</t>
+          <t>Haute-Vienne</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Centre hospitalier Nouvel Hôpital d'Epinal - plateau de la justice (Epinal)</t>
+          <t>CHU Dupuytren 1 (Limoges)</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2413-establishment6126</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2386-establishment1372</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Unité de Soins Intensifs de Cardiologie</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr"/>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Pr Victor ABOYANS</t>
+        </is>
+      </c>
       <c r="G388" t="inlineStr"/>
-      <c r="H388" s="2" t="inlineStr">
-        <is>
-          <t>sec.direction@ch-ed.fr</t>
-        </is>
-      </c>
+      <c r="H388" t="inlineStr"/>
       <c r="I388" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16469,24 +16481,24 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Centre hospitalier (Remiremont)</t>
+          <t>Centre hospitalier Nouvel Hôpital d'Epinal - plateau de la justice (Epinal)</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2425-establishment6138</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2413-establishment6126</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Médecine orientation Cardiologie</t>
+          <t>Cardiologie USIC Plateau Technique</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr"/>
       <c r="H389" s="2" t="inlineStr">
         <is>
-          <t>helene.marion@ch-remiremont.fr</t>
+          <t>sec.direction@ch-ed.fr</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -16508,32 +16520,24 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Site Hospitalier de Neufchâteau Siège Social (Neufchâteau)</t>
+          <t>Centre hospitalier Nouvel Hôpital d'Epinal - plateau de la justice (Epinal)</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2435-establishment6148</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2413-establishment6126</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE ET SOINS INTENSIFS CARDIAQUES</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>Dr Jean-Louis MEREGNANI</t>
-        </is>
-      </c>
-      <c r="G390" s="2" t="inlineStr">
-        <is>
-          <t>jl.meregnani@ch-ouestvosgien.fr</t>
-        </is>
-      </c>
+          <t>Unité de Soins Intensifs de Cardiologie</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr"/>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>e.andrique@ch-ouestvosgien.fr</t>
+          <t>sec.direction@ch-ed.fr</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -16545,32 +16549,36 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Yonne</t>
+          <t>Vosges</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Centre hospitalier Centre hospitalier d'Auxerre (Auxerre)</t>
+          <t>Centre hospitalier (Remiremont)</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2462-establishment6170</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2425-establishment6138</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Cardiologie et unité de soins intensifs cardiologiques</t>
+          <t>Médecine orientation Cardiologie</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr"/>
-      <c r="H391" t="inlineStr"/>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>helene.marion@ch-remiremont.fr</t>
+        </is>
+      </c>
       <c r="I391" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16580,42 +16588,42 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Yonne</t>
+          <t>Vosges</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Hopital Gaston Ramon (Sens)</t>
+          <t>Site Hospitalier de Neufchâteau Siège Social (Neufchâteau)</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2465-establishment6172</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2435-establishment6148</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Médecine cardiologie et soins intensifs</t>
+          <t>CARDIOLOGIE ET SOINS INTENSIFS CARDIAQUES</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Dr Didier PACAUD</t>
+          <t>Dr Jean-Louis MEREGNANI</t>
         </is>
       </c>
       <c r="G392" s="2" t="inlineStr">
         <is>
-          <t>dpacaud@ch-sens.fr</t>
+          <t>jl.meregnani@ch-ouestvosgien.fr</t>
         </is>
       </c>
       <c r="H392" s="2" t="inlineStr">
         <is>
-          <t>drh@ch-sens.fr</t>
+          <t>e.andrique@ch-ouestvosgien.fr</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -16637,29 +16645,21 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER (JOIGNY)</t>
+          <t>Centre hospitalier Centre hospitalier d'Auxerre (Auxerre)</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2477-establishment6183</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2462-establishment6170</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Plateau Technique de Cardiologie</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>Dr Yan MORVAN</t>
-        </is>
-      </c>
-      <c r="G393" s="2" t="inlineStr">
-        <is>
-          <t>morvan@ch-joigny.fr</t>
-        </is>
-      </c>
+          <t>Cardiologie et unité de soins intensifs cardiologiques</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr"/>
       <c r="I393" t="inlineStr">
         <is>
@@ -16680,30 +16680,34 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER (JOIGNY)</t>
+          <t>Hopital Gaston Ramon (Sens)</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2477-establishment6183</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2465-establishment6172</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>SMR des affections cardio-vasculaires</t>
+          <t>Médecine cardiologie et soins intensifs</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Dr Yan MORVAN</t>
+          <t>Dr Didier PACAUD</t>
         </is>
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>morvan@ch-joigny.fr</t>
-        </is>
-      </c>
-      <c r="H394" t="inlineStr"/>
+          <t>dpacaud@ch-sens.fr</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>drh@ch-sens.fr</t>
+        </is>
+      </c>
       <c r="I394" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16723,25 +16727,29 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER (AVALLON)</t>
+          <t>CENTRE HOSPITALIER (JOIGNY)</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2826-establishment6392</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2477-establishment6183</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>médecine 2 à orientation pneumologique et cardiologique</t>
+          <t>Plateau Technique de Cardiologie</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Dr Brahim BOUKHELOUA</t>
-        </is>
-      </c>
-      <c r="G395" t="inlineStr"/>
+          <t>Dr Yan MORVAN</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>morvan@ch-joigny.fr</t>
+        </is>
+      </c>
       <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr">
         <is>
@@ -16752,37 +16760,37 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Territoire de Belfort</t>
+          <t>Yonne</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Hôpital Nord Franche-Comté (TREVENANS)</t>
+          <t>CENTRE HOSPITALIER (JOIGNY)</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2497-establishment6201</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2477-establishment6183</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>SMR des affections cardio-vasculaires</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Dr Yoann LEFRANCOIS</t>
+          <t>Dr Yan MORVAN</t>
         </is>
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>yoann.lefrancois@hnfc.fr</t>
+          <t>morvan@ch-joigny.fr</t>
         </is>
       </c>
       <c r="H396" t="inlineStr"/>
@@ -16795,44 +16803,36 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Essonne</t>
+          <t>Yonne</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Sud Francilien (Corbeil-Essonnes)</t>
+          <t>CENTRE HOSPITALIER (AVALLON)</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2501-establishment10188</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2826-establishment6392</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
+          <t>médecine 2 à orientation pneumologique et cardiologique</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Dr Brahim MEFTOUT</t>
-        </is>
-      </c>
-      <c r="G397" s="2" t="inlineStr">
-        <is>
-          <t>brahim.meftout@chsf.fr</t>
-        </is>
-      </c>
-      <c r="H397" s="2" t="inlineStr">
-        <is>
-          <t>antoine.vallauri@chsf.fr</t>
-        </is>
-      </c>
+          <t>Dr Brahim BOUKHELOUA</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr"/>
       <c r="I397" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16842,44 +16842,40 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Essonne</t>
+          <t>Territoire de Belfort</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Sud Francilien (Corbeil-Essonnes)</t>
+          <t>Hôpital Nord Franche-Comté (TREVENANS)</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2501-establishment10188</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2497-establishment6201</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>SMR READAPTATION CARDIO VASCULAIRE</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Dr François KOUKOUI</t>
+          <t>Dr Yoann LEFRANCOIS</t>
         </is>
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>francois.koukoui@ch-sud-francilien.fr</t>
-        </is>
-      </c>
-      <c r="H398" s="2" t="inlineStr">
-        <is>
-          <t>antoine.vallauri@chsf.fr</t>
-        </is>
-      </c>
+          <t>yoann.lefrancois@hnfc.fr</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16899,26 +16895,34 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Hôpital Paris-Saclay (ORSAY)</t>
+          <t>Centre Hospitalier Sud Francilien (Corbeil-Essonnes)</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2505-establishment7767</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2501-establishment10188</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Cardiologie et Unité de Soins Intensifs de Cardiologie (USIC)</t>
+          <t>CARDIOLOGIE</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Dr Maruan BARRI</t>
-        </is>
-      </c>
-      <c r="G399" t="inlineStr"/>
-      <c r="H399" t="inlineStr"/>
+          <t>Dr Brahim MEFTOUT</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>brahim.meftout@chsf.fr</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>antoine.vallauri@chsf.fr</t>
+        </is>
+      </c>
       <c r="I399" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16938,26 +16942,34 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>CENTRE HOSPITALIER DE BLIGNY (BRIIS SOUS FORGES)</t>
+          <t>Centre Hospitalier Sud Francilien (Corbeil-Essonnes)</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3248-establishment7081</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2501-establishment10188</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>READAPTATION CARDIAQUE ET SOINS DE SUITE CARDIOLOGIQUES</t>
+          <t>SMR READAPTATION CARDIO VASCULAIRE</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Dr Titi FARROKHI</t>
-        </is>
-      </c>
-      <c r="G400" t="inlineStr"/>
-      <c r="H400" t="inlineStr"/>
+          <t>Dr François KOUKOUI</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>francois.koukoui@ch-sud-francilien.fr</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>antoine.vallauri@chsf.fr</t>
+        </is>
+      </c>
       <c r="I400" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -16967,32 +16979,32 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Hauts-de-Seine</t>
+          <t>Essonne</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Hôpital Ambroise-Paré AP-HP (Boulogne-Billancourt)</t>
+          <t>Hôpital Paris-Saclay (ORSAY)</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2524-establishment6228</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2505-establishment7767</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Cardiologie et maladies vasculaires</t>
+          <t>Cardiologie et Unité de Soins Intensifs de Cardiologie (USIC)</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Dr MARIE HAUGUEL-MOREAU</t>
+          <t>Dr Maruan BARRI</t>
         </is>
       </c>
       <c r="G401" t="inlineStr"/>
@@ -17006,32 +17018,32 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Hauts-de-Seine</t>
+          <t>Essonne</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Hôpital Antoine Béclère AP-HP (Clamart)</t>
+          <t>CENTRE HOSPITALIER DE BLIGNY (BRIIS SOUS FORGES)</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2531-establishment6235</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure3248-establishment7081</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>READAPTATION CARDIAQUE ET SOINS DE SUITE CARDIOLOGIQUES</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Dr CLAUDIUS STATESCU</t>
+          <t>Dr Titi FARROKHI</t>
         </is>
       </c>
       <c r="G402" t="inlineStr"/>
@@ -17055,30 +17067,26 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Beaujon (Clichy)</t>
+          <t>Hôpital Ambroise-Paré AP-HP (Boulogne-Billancourt)</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2526-establishment6230</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2524-establishment6228</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie et maladies vasculaires</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Dr AGNES CACHIER</t>
+          <t>Dr MARIE HAUGUEL-MOREAU</t>
         </is>
       </c>
       <c r="G403" t="inlineStr"/>
-      <c r="H403" s="2" t="inlineStr">
-        <is>
-          <t>marie.hiance@aphp.fr</t>
-        </is>
-      </c>
+      <c r="H403" t="inlineStr"/>
       <c r="I403" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17098,20 +17106,24 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Hôpital National d'Instruction des Armées PERCY (CLAMART)</t>
+          <t>Hôpital Antoine Béclère AP-HP (Clamart)</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8044</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2531-establishment6235</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE/MEDECINE AERONAUTIQUE 92</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr"/>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Dr CLAUDIUS STATESCU</t>
+        </is>
+      </c>
       <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr">
@@ -17133,22 +17145,30 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Hôpital National d'Instruction des Armées PERCY (CLAMART)</t>
+          <t>AP-HP Hôpital Beaujon (Clichy)</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8044</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2526-establishment6230</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>CHIRURGIE THORACIQUE ET CARDIO-VASCULAIRE 92</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr"/>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Dr AGNES CACHIER</t>
+        </is>
+      </c>
       <c r="G405" t="inlineStr"/>
-      <c r="H405" t="inlineStr"/>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>marie.hiance@aphp.fr</t>
+        </is>
+      </c>
       <c r="I405" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17168,29 +17188,21 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Centre d'accueil et de soins hospitaliers CASH (Nanterre)</t>
+          <t>Hôpital National d'Instruction des Armées PERCY (CLAMART)</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2522-establishment6226</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8044</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>Dr Mohand GOUDJIL</t>
-        </is>
-      </c>
-      <c r="G406" s="2" t="inlineStr">
-        <is>
-          <t>mohand.goudjil@ch-nanterre.fr</t>
-        </is>
-      </c>
+          <t>CARDIOLOGIE/MEDECINE AERONAUTIQUE 92</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr"/>
       <c r="I406" t="inlineStr">
         <is>
@@ -17211,29 +17223,21 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Centre d'accueil et de soins hospitaliers CASH (Nanterre)</t>
+          <t>Hôpital National d'Instruction des Armées PERCY (CLAMART)</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2522-establishment6226</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure5561-establishment8044</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Unité de Soins Intensifs de Cardiologie</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>Dr Mohand GOUDJIL</t>
-        </is>
-      </c>
-      <c r="G407" s="2" t="inlineStr">
-        <is>
-          <t>mohand.goudjil@ch-nanterre.fr</t>
-        </is>
-      </c>
+          <t>CHIRURGIE THORACIQUE ET CARDIO-VASCULAIRE 92</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr"/>
       <c r="H407" t="inlineStr"/>
       <c r="I407" t="inlineStr">
         <is>
@@ -17254,34 +17258,30 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Centre Hospitalier Stell (Rueil-Malmaison)</t>
+          <t>Centre d'accueil et de soins hospitaliers CASH (Nanterre)</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2547-establishment6249</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2522-establishment6226</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Hôpital de jour de Soins de suite et de réadaptation cardio-vasculaires</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Dr Fatima BOUKHSIBI</t>
+          <t>Dr Mohand GOUDJIL</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>fatima.boukhsibi@ch-rueil.fr</t>
-        </is>
-      </c>
-      <c r="H408" s="2" t="inlineStr">
-        <is>
-          <t>drh@ch-rueil.fr</t>
-        </is>
-      </c>
+          <t>mohand.goudjil@ch-nanterre.fr</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr"/>
       <c r="I408" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17301,34 +17301,30 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Centre Hospitalier Stell (Rueil-Malmaison)</t>
+          <t>Centre d'accueil et de soins hospitaliers CASH (Nanterre)</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2547-establishment6249</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2522-establishment6226</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Soins de Suite et de Réadaptation Cardiovasculaire</t>
+          <t>Unité de Soins Intensifs de Cardiologie</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Dr Fatima BOUKHSIBI</t>
+          <t>Dr Mohand GOUDJIL</t>
         </is>
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>fatima.boukhsibi@ch-rueil.fr</t>
-        </is>
-      </c>
-      <c r="H409" s="2" t="inlineStr">
-        <is>
-          <t>drh@ch-rueil.fr</t>
-        </is>
-      </c>
+          <t>mohand.goudjil@ch-nanterre.fr</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr"/>
       <c r="I409" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17348,32 +17344,32 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Site Hospitalier de Neuilly-sur-Seine (Siège Social) (Neuilly-sur-Seine)</t>
+          <t>Centre Hospitalier Centre Hospitalier Stell (Rueil-Malmaison)</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2537-establishment6240</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2547-establishment6249</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Spécialités médicales (Cardiologie)</t>
+          <t>Hôpital de jour de Soins de suite et de réadaptation cardio-vasculaires</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Dr Camille BOTELLA</t>
+          <t>Dr Fatima BOUKHSIBI</t>
         </is>
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>cbotella@ch-rivesdeseine.fr</t>
+          <t>fatima.boukhsibi@ch-rueil.fr</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
-          <t>direction@ch-rivesdeseine.fr</t>
+          <t>drh@ch-rueil.fr</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -17385,42 +17381,42 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Seine-Saint-Denis</t>
+          <t>Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Centre hospitalier Intercommunal (Aulnay-sous-Bois)</t>
+          <t>Centre Hospitalier Centre Hospitalier Stell (Rueil-Malmaison)</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2573-establishment6274</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2547-establishment6249</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Soins de Suite et de Réadaptation Cardiovasculaire</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Dr François WALYLO</t>
+          <t>Dr Fatima BOUKHSIBI</t>
         </is>
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>francois.walylo@ch-aulnay.fr</t>
+          <t>fatima.boukhsibi@ch-rueil.fr</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
         <is>
-          <t>maxime.lemee@ght-gpne.fr</t>
+          <t>drh@ch-rueil.fr</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -17432,36 +17428,44 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Seine-Saint-Denis</t>
+          <t>Hauts-de-Seine</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Hôpital Avicenne - AP-HP.Hôpitaux Universitaires Paris Seine-Saint-Denis (Bobigny)</t>
+          <t>Site Hospitalier de Neuilly-sur-Seine (Siège Social) (Neuilly-sur-Seine)</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2552-establishment6254</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2537-establishment6240</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Spécialités médicales (Cardiologie)</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>NATHALIE AZOPPARDI</t>
-        </is>
-      </c>
-      <c r="G412" t="inlineStr"/>
-      <c r="H412" t="inlineStr"/>
+          <t>Dr Camille BOTELLA</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>cbotella@ch-rivesdeseine.fr</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>direction@ch-rivesdeseine.fr</t>
+        </is>
+      </c>
       <c r="I412" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17481,12 +17485,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Centre hospitalier intercommunal André Grégoire (Montreuil-sous-Bois)</t>
+          <t>Centre hospitalier Intercommunal (Aulnay-sous-Bois)</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2568-establishment6255</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2573-establishment6274</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -17496,15 +17500,19 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Dr Albert BOCCARA</t>
+          <t>Dr François WALYLO</t>
         </is>
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>albert.boccara@ght-gpne.fr</t>
-        </is>
-      </c>
-      <c r="H413" t="inlineStr"/>
+          <t>francois.walylo@ch-aulnay.fr</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>maxime.lemee@ght-gpne.fr</t>
+        </is>
+      </c>
       <c r="I413" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17524,12 +17532,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Groupement Hospitalier de Territoire Grand Paris Nord Est (Montfermeil)</t>
+          <t>Hôpital Avicenne - AP-HP.Hôpitaux Universitaires Paris Seine-Saint-Denis (Bobigny)</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2568-establishment6269</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2552-establishment6254</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -17539,19 +17547,11 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>M. Olivier NALLET</t>
-        </is>
-      </c>
-      <c r="G414" s="2" t="inlineStr">
-        <is>
-          <t>olivier.nallet@ght-gpne.fr</t>
-        </is>
-      </c>
-      <c r="H414" s="2" t="inlineStr">
-        <is>
-          <t>maxime.lemee@ght-gpne.fr</t>
-        </is>
-      </c>
+          <t>NATHALIE AZOPPARDI</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr"/>
       <c r="I414" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17561,22 +17561,22 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Val-de-Marne</t>
+          <t>Seine-Saint-Denis</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Hôpital Bicêtre AP-HP (Le Kremlin-Bicêtre)</t>
+          <t>Centre hospitalier intercommunal André Grégoire (Montreuil-sous-Bois)</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2589-establishment6290</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2568-establishment6255</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -17586,10 +17586,14 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Dr SAFA JEBALI</t>
-        </is>
-      </c>
-      <c r="G415" t="inlineStr"/>
+          <t>Dr Albert BOCCARA</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>albert.boccara@ght-gpne.fr</t>
+        </is>
+      </c>
       <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr">
         <is>
@@ -17600,36 +17604,44 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Val-de-Marne</t>
+          <t>Seine-Saint-Denis</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Hôpital Bicêtre AP-HP (Le Kremlin-Bicêtre)</t>
+          <t>Groupement Hospitalier de Territoire Grand Paris Nord Est (Montfermeil)</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2589-establishment6290</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2568-establishment6269</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Explorations fonctionnelles cardio-vasculaires</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Dr OLIVIER CHOURAQUI</t>
-        </is>
-      </c>
-      <c r="G416" t="inlineStr"/>
-      <c r="H416" t="inlineStr"/>
+          <t>M. Olivier NALLET</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>olivier.nallet@ght-gpne.fr</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>maxime.lemee@ght-gpne.fr</t>
+        </is>
+      </c>
       <c r="I416" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17649,12 +17661,12 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Henri Mondor (Créteil)</t>
+          <t>Hôpital Bicêtre AP-HP (Le Kremlin-Bicêtre)</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2577-establishment6278</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2589-establishment6290</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -17664,15 +17676,11 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Dr ALBAN COPIE</t>
+          <t>Dr SAFA JEBALI</t>
         </is>
       </c>
       <c r="G417" t="inlineStr"/>
-      <c r="H417" s="2" t="inlineStr">
-        <is>
-          <t>adeline.rouby@aphp.fr</t>
-        </is>
-      </c>
+      <c r="H417" t="inlineStr"/>
       <c r="I417" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17692,33 +17700,29 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Henri Mondor (Créteil)</t>
+          <t>Hôpital Bicêtre AP-HP (Le Kremlin-Bicêtre)</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2577-establishment6278</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2589-establishment6290</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Cardiologie interventionnelle</t>
+          <t>Explorations fonctionnelles cardio-vasculaires</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Pr EMMANUEL TEIGER</t>
+          <t>Dr OLIVIER CHOURAQUI</t>
         </is>
       </c>
       <c r="G418" t="inlineStr"/>
-      <c r="H418" s="2" t="inlineStr">
-        <is>
-          <t>adeline.rouby@aphp.fr</t>
-        </is>
-      </c>
+      <c r="H418" t="inlineStr"/>
       <c r="I418" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non spécifié / Non</t>
         </is>
       </c>
     </row>
@@ -17745,12 +17749,12 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Chirurgie cardio-vasculaire</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>MORGANE ARNOUX</t>
+          <t>Dr ALBAN COPIE</t>
         </is>
       </c>
       <c r="G419" t="inlineStr"/>
@@ -17788,12 +17792,12 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Exploration fonctionnelle cardiovasculaire non invasive et de cardiologie ambulatoire</t>
+          <t>Cardiologie interventionnelle</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Pr GENEVIEVE DERUMEAUX</t>
+          <t>Pr EMMANUEL TEIGER</t>
         </is>
       </c>
       <c r="G420" t="inlineStr"/>
@@ -17804,7 +17808,7 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>Non spécifié / Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -17821,22 +17825,30 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Hôpital Paul-Brousse AP-HP (Villejuif)</t>
+          <t>AP-HP Hôpital Henri Mondor (Créteil)</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2596-establishment6296</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2577-establishment6278</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr"/>
+          <t>Chirurgie cardio-vasculaire</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>MORGANE ARNOUX</t>
+        </is>
+      </c>
       <c r="G421" t="inlineStr"/>
-      <c r="H421" t="inlineStr"/>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>adeline.rouby@aphp.fr</t>
+        </is>
+      </c>
       <c r="I421" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17856,28 +17868,28 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Charles Foix (Ivry-sur-Seine)</t>
+          <t>AP-HP Hôpital Henri Mondor (Créteil)</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2584-establishment6285</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2577-establishment6278</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>court séjour gériatrique à orientation cardiologie et neuro-psycho</t>
+          <t>Exploration fonctionnelle cardiovasculaire non invasive et de cardiologie ambulatoire</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Dr SONIA ADRAR</t>
+          <t>Pr GENEVIEVE DERUMEAUX</t>
         </is>
       </c>
       <c r="G422" t="inlineStr"/>
       <c r="H422" s="2" t="inlineStr">
         <is>
-          <t>choella.akbaraly@aphp.fr</t>
+          <t>adeline.rouby@aphp.fr</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -17899,30 +17911,22 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>AP-HP Hôpital Charles Foix (Ivry-sur-Seine)</t>
+          <t>Hôpital Paul-Brousse AP-HP (Villejuif)</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2584-establishment6285</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2596-establishment6296</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Soins de suite et de réadapation à orientation cardiologie et neuro-psycho-gériatrique</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>Dr CARMELO LAFUENTE LAFUENTE</t>
-        </is>
-      </c>
+          <t>CARDIOLOGIE</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr"/>
-      <c r="H423" s="2" t="inlineStr">
-        <is>
-          <t>choella.akbaraly@aphp.fr</t>
-        </is>
-      </c>
+      <c r="H423" t="inlineStr"/>
       <c r="I423" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -17942,32 +17946,28 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Intercommunal de Villeneuve-Saint-Georges Lucie &amp; Raymond Aubrac (Villeneuve-Saint-Georges)</t>
+          <t>AP-HP Hôpital Charles Foix (Ivry-sur-Seine)</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2583-establishment6284</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2584-establishment6285</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Cardiologie et urgences cardio-vasculaires</t>
+          <t>court séjour gériatrique à orientation cardiologie et neuro-psycho</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Dr Emmanuel SALENGRO</t>
-        </is>
-      </c>
-      <c r="G424" s="2" t="inlineStr">
-        <is>
-          <t>emmanuel.salengro@chiv.fr</t>
-        </is>
-      </c>
+          <t>Dr SONIA ADRAR</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr"/>
       <c r="H424" s="2" t="inlineStr">
         <is>
-          <t>elena.ketterer@chiv.fr</t>
+          <t>choella.akbaraly@aphp.fr</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -17979,40 +17979,40 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Val-d'Oise</t>
+          <t>Val-de-Marne</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Hôpital NOVO - Site de Pontoise (CERGY PONTOISE)</t>
+          <t>AP-HP Hôpital Charles Foix (Ivry-sur-Seine)</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2605-establishment6305</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2584-establishment6285</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Soins de suite et de réadapation à orientation cardiologie et neuro-psycho-gériatrique</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Dr Véronique DECALF</t>
-        </is>
-      </c>
-      <c r="G425" s="2" t="inlineStr">
-        <is>
-          <t>veronique.decalf@ght-novo.fr</t>
-        </is>
-      </c>
-      <c r="H425" t="inlineStr"/>
+          <t>Dr CARMELO LAFUENTE LAFUENTE</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>choella.akbaraly@aphp.fr</t>
+        </is>
+      </c>
       <c r="I425" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18022,40 +18022,44 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Val-d'Oise</t>
+          <t>Val-de-Marne</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de Gonesse (Gonesse)</t>
+          <t>Centre Hospitalier Intercommunal de Villeneuve-Saint-Georges Lucie &amp; Raymond Aubrac (Villeneuve-Saint-Georges)</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2610-establishment6309</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2583-establishment6284</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Cardiologie et urgences cardio-vasculaires</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Dr Nabil POULOS</t>
+          <t>Dr Emmanuel SALENGRO</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>nabil.poulos@ch-gonesse.fr</t>
-        </is>
-      </c>
-      <c r="H426" t="inlineStr"/>
+          <t>emmanuel.salengro@chiv.fr</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>elena.ketterer@chiv.fr</t>
+        </is>
+      </c>
       <c r="I426" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18075,29 +18079,33 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Groupement hospitalier Eaubonne - Montmorency - Hôpital Simone Veil (EAUBONNE)</t>
+          <t>Hôpital NOVO - Site de Pontoise (CERGY PONTOISE)</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2600-establishment6300</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2605-establishment6305</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Cardiologie - Cardiologie interventionnelle - USIC</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr"/>
-      <c r="G427" t="inlineStr"/>
-      <c r="H427" s="2" t="inlineStr">
-        <is>
-          <t>sec.drh@ch-simoneveil.fr</t>
-        </is>
-      </c>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Dr Véronique DECALF</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>veronique.decalf@ght-novo.fr</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr"/>
       <c r="I427" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non spécifié / Non</t>
         </is>
       </c>
     </row>
@@ -18114,34 +18122,30 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Centre hospitalier Victor Dupouy (Argenteuil)</t>
+          <t>Centre Hospitalier de Gonesse (Gonesse)</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2598-establishment6298</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2610-establishment6309</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Dr François DUCLOS</t>
+          <t>Dr Nabil POULOS</t>
         </is>
       </c>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>francois.duclos@ch-argenteuil.fr</t>
-        </is>
-      </c>
-      <c r="H428" s="2" t="inlineStr">
-        <is>
-          <t>bianca.dasilvabarreto@ch-argenteuil.fr</t>
-        </is>
-      </c>
+          <t>nabil.poulos@ch-gonesse.fr</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr"/>
       <c r="I428" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18161,75 +18165,71 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Hôpital Le Parc (Taverny)</t>
+          <t>Groupement hospitalier Eaubonne - Montmorency - Hôpital Simone Veil (EAUBONNE)</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2599-establishment6299</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2600-establishment6300</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>CARDIOLOGIE</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>Dr Ioana MORARU</t>
-        </is>
-      </c>
-      <c r="G429" s="2" t="inlineStr">
-        <is>
-          <t>i.moraru@hopital-parc-taverny.fr</t>
-        </is>
-      </c>
-      <c r="H429" t="inlineStr"/>
+          <t>Cardiologie - Cardiologie interventionnelle - USIC</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>sec.drh@ch-simoneveil.fr</t>
+        </is>
+      </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>Non spécifié / Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Guadeloupe</t>
+          <t>Val-d'Oise</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Universitaire de la Guadeloupe (Pointe-à-Pitre)</t>
+          <t>Centre hospitalier Victor Dupouy (Argenteuil)</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2624-establishment6323</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2598-establishment6298</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>CARDIOLOGIE</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Pr Annie LANNUZEL</t>
+          <t>Dr François DUCLOS</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>annie.lannuzel@chu-guadeloupe.fr</t>
+          <t>francois.duclos@ch-argenteuil.fr</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
-          <t>christiana.cologer@chu-guadeloupe.fr</t>
+          <t>bianca.dasilvabarreto@ch-argenteuil.fr</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -18241,36 +18241,40 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Guadeloupe</t>
+          <t>Val-d'Oise</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Universitaire de la Guadeloupe (Pointe-à-Pitre)</t>
+          <t>Hôpital Le Parc (Taverny)</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2624-establishment6323</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2599-establishment6299</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Chirurgie thoracique et cardio-vasculaire</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr"/>
-      <c r="H431" s="2" t="inlineStr">
-        <is>
-          <t>christiana.cologer@chu-guadeloupe.fr</t>
-        </is>
-      </c>
+          <t>CARDIOLOGIE</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Dr Ioana MORARU</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>i.moraru@hopital-parc-taverny.fr</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr"/>
       <c r="I431" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18280,40 +18284,44 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>971</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Martinique</t>
+          <t>Guadeloupe</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Hôpital Pierre Zobda-Quitman (Fort-de-France)</t>
+          <t>Centre Hospitalier Universitaire de la Guadeloupe (Pointe-à-Pitre)</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2640-establishment1385</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2624-establishment6323</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Département de Cardiologie - Soins Intensifs 7B</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Pr Jocelyn INAMO</t>
+          <t>Pr Annie LANNUZEL</t>
         </is>
       </c>
       <c r="G432" s="2" t="inlineStr">
         <is>
-          <t>jocelyn.inamo@chu-martinique.fr</t>
-        </is>
-      </c>
-      <c r="H432" t="inlineStr"/>
+          <t>annie.lannuzel@chu-guadeloupe.fr</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>christiana.cologer@chu-guadeloupe.fr</t>
+        </is>
+      </c>
       <c r="I432" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18323,40 +18331,36 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>971</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Martinique</t>
+          <t>Guadeloupe</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Hôpital Pierre Zobda-Quitman (Fort-de-France)</t>
+          <t>Centre Hospitalier Universitaire de la Guadeloupe (Pointe-à-Pitre)</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2640-establishment1385</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2624-establishment6323</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Département de Cardiologie 7D</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>Pr Jocelyn INAMO</t>
-        </is>
-      </c>
-      <c r="G433" s="2" t="inlineStr">
-        <is>
-          <t>jocelyn.inamo@chu-martinique.fr</t>
-        </is>
-      </c>
-      <c r="H433" t="inlineStr"/>
+          <t>Chirurgie thoracique et cardio-vasculaire</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>christiana.cologer@chu-guadeloupe.fr</t>
+        </is>
+      </c>
       <c r="I433" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18366,37 +18370,37 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>972</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Guyane</t>
+          <t>Martinique</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de Cayenne Andrée Rosemon (Cayenne)</t>
+          <t>Hôpital Pierre Zobda-Quitman (Fort-de-France)</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2645-establishment6342</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2640-establishment1385</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Département de Cardiologie - Soins Intensifs 7B</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Dr Yves-Kénol FRANCK</t>
+          <t>Pr Jocelyn INAMO</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr">
         <is>
-          <t>yves-kenol.franck@ch-cayenne.fr</t>
+          <t>jocelyn.inamo@chu-martinique.fr</t>
         </is>
       </c>
       <c r="H434" t="inlineStr"/>
@@ -18409,44 +18413,40 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>972</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Guyane</t>
+          <t>Martinique</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de l'Ouest Guyanais Franck Joly (Saint-Laurent-du-Maroni)</t>
+          <t>Hôpital Pierre Zobda-Quitman (Fort-de-France)</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2646-establishment6343</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2640-establishment1385</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Département de Cardiologie 7D</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Dr Grace-À-Dieu YABETA</t>
+          <t>Pr Jocelyn INAMO</t>
         </is>
       </c>
       <c r="G435" s="2" t="inlineStr">
         <is>
-          <t>g.yabeta@ch-ouestguyane.fr</t>
-        </is>
-      </c>
-      <c r="H435" s="2" t="inlineStr">
-        <is>
-          <t>s.lavenaire@ch-ouestguyane.fr</t>
-        </is>
-      </c>
+          <t>jocelyn.inamo@chu-martinique.fr</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr"/>
       <c r="I435" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18456,31 +18456,39 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>973</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>La Réunion</t>
+          <t>Guyane</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Centre Hospitalier Universitaire Sud Réunion (Saint-Pierre)</t>
+          <t>Centre Hospitalier de Cayenne Andrée Rosemon (Cayenne)</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2651-establishment6347</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2645-establishment6342</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Cardiologie (Sud)</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr"/>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Dr Yves-Kénol FRANCK</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>yves-kenol.franck@ch-cayenne.fr</t>
+        </is>
+      </c>
       <c r="H436" t="inlineStr"/>
       <c r="I436" t="inlineStr">
         <is>
@@ -18491,40 +18499,44 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>973</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>La Réunion</t>
+          <t>Guyane</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Centre hospitalier Felix Guyon (Saint-Denis)</t>
+          <t>Centre Hospitalier de l'Ouest Guyanais Franck Joly (Saint-Laurent-du-Maroni)</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2651-establishment6344</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2646-establishment6343</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Cardiologie (Nord)</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Dr Christian KICHENIN</t>
+          <t>Dr Grace-À-Dieu YABETA</t>
         </is>
       </c>
       <c r="G437" s="2" t="inlineStr">
         <is>
-          <t>cardiologie@chd-fguyon.fr</t>
-        </is>
-      </c>
-      <c r="H437" t="inlineStr"/>
+          <t>g.yabeta@ch-ouestguyane.fr</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>s.lavenaire@ch-ouestguyane.fr</t>
+        </is>
+      </c>
       <c r="I437" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18544,29 +18556,21 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Centre hospitalier Felix Guyon (Saint-Denis)</t>
+          <t>Centre Hospitalier Universitaire Sud Réunion (Saint-Pierre)</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2651-establishment6344</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2651-establishment6347</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Chir. Thoracique et Cardiovasculaire</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>M. Jean-François DELAMBRE</t>
-        </is>
-      </c>
-      <c r="G438" s="2" t="inlineStr">
-        <is>
-          <t>jf-delambre@chd-fguyon.fr</t>
-        </is>
-      </c>
+          <t>Cardiologie (Sud)</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr"/>
       <c r="I438" t="inlineStr">
         <is>
@@ -18587,34 +18591,30 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Centre hospitalier Ouest Réunion (Saint-Paul)</t>
+          <t>Centre hospitalier Felix Guyon (Saint-Denis)</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2656-establishment6352</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2651-establishment6344</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Médecine à orientation Cardiologie et Neurologie</t>
+          <t>Cardiologie (Nord)</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Dr Fanny LE MEE</t>
+          <t>Dr Christian KICHENIN</t>
         </is>
       </c>
       <c r="G439" s="2" t="inlineStr">
         <is>
-          <t>secretariat.cardiologie@chor.re</t>
-        </is>
-      </c>
-      <c r="H439" s="2" t="inlineStr">
-        <is>
-          <t>Ol.MANICON@pso.re</t>
-        </is>
-      </c>
+          <t>cardiologie@chd-fguyon.fr</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr"/>
       <c r="I439" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18624,41 +18624,131 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>974</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Polynésie Française</t>
+          <t>La Réunion</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de Polynésie française (Papeete)</t>
+          <t>Centre hospitalier Felix Guyon (Saint-Denis)</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2771-establishment7816</t>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2651-establishment6344</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Chir. Thoracique et Cardiovasculaire</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>M. Christophe LEGOANVIC</t>
+          <t>M. Jean-François DELAMBRE</t>
         </is>
       </c>
       <c r="G440" s="2" t="inlineStr">
         <is>
-          <t>christophe.legoanvic@cht.pf</t>
+          <t>jf-delambre@chd-fguyon.fr</t>
         </is>
       </c>
       <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr">
+        <is>
+          <t>Non spécifié / Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>La Réunion</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Centre hospitalier Ouest Réunion (Saint-Paul)</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2656-establishment6352</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Médecine à orientation Cardiologie et Neurologie</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Dr Fanny LE MEE</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>secretariat.cardiologie@chor.re</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>Ol.MANICON@pso.re</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Non spécifié / Non</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Polynésie Française</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Centre Hospitalier de Polynésie française (Papeete)</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>https://etablissements.fhf.fr/annuaire/establishment/structure2771-establishment7816</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Cardiologie</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>M. Christophe LEGOANVIC</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>christophe.legoanvic@cht.pf</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
         </is>
@@ -19078,269 +19168,269 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId410"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId411"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId490"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId491"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId515"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId516"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId555"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId556"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId557"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId558"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId562"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId563"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId566"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId567"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId574"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId575"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId576"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H326" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId652"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId653"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId660"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId661"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G346" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G349" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H349" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId675"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId676"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId677"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId678"/>
@@ -19349,175 +19439,180 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId681"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId682"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H355" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D361" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G361" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G362" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H366" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G367" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H367" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G356" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D361" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId705"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G368" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G369" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G369" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId716"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId717"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D373" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H375" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G376" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H376" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D373" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G373" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G376" r:id="rId726"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H381" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G382" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H382" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G378" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId735"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G383" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId740"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId741"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H387" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H388" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G390" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G386" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G387" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId751"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId752"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G393" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId758"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId759"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G396" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D397" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G397" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G395" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G396" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D397" r:id="rId766"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D398" r:id="rId767"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G398" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D399" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D400" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D401" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D402" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D403" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G406" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G407" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G408" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H408" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D399" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G399" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D400" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G400" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D401" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D402" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D403" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G408" r:id="rId784"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId785"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G409" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G410" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D411" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G411" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D412" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D413" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G413" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D414" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G414" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H414" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G410" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D411" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G411" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D412" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G412" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D413" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G413" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D414" r:id="rId799"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D415" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D416" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D417" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H417" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D418" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H418" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D419" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D420" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D421" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D422" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D423" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D424" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G424" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G415" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D416" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G416" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D417" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D418" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D419" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D420" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D421" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D422" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D423" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D424" r:id="rId816"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId817"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D425" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G425" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId819"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D426" r:id="rId820"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G426" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D427" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H427" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D428" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H428" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D427" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G427" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D428" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId826"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D429" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G429" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId828"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D430" r:id="rId829"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G430" r:id="rId830"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId831"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D431" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H431" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G431" r:id="rId833"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D432" r:id="rId834"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G432" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D433" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G433" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D434" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G434" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D435" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G435" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H435" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D433" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D434" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G434" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D435" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G435" r:id="rId842"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D436" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D437" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G437" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D438" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G438" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D439" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G439" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G436" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D437" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G437" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D438" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D439" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G439" r:id="rId850"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D440" r:id="rId851"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G440" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D441" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G441" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D442" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G442" r:id="rId857"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fhf_cardiologie.xlsx
+++ b/fhf_cardiologie.xlsx
@@ -4516,11 +4516,7 @@
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>p.clavaison@ch-hdn.fr</t>
-        </is>
-      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Non spécifié / Non</t>
@@ -18958,661 +18954,660 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G356" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D361" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G369" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D373" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G373" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G376" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G378" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G386" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G387" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G395" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G396" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D397" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D398" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G398" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D399" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G399" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D400" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G400" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D401" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D402" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D403" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G408" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G409" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G410" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D411" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G411" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D412" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G412" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D413" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G413" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D414" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D415" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G415" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D416" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G416" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D417" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D418" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D419" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D420" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D421" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D422" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D423" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D424" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D425" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D426" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G426" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D427" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G427" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D428" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D429" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D430" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G430" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D431" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G431" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D432" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G432" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D433" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D434" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G434" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D435" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G435" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D436" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G436" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D437" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G437" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D438" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D439" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G439" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D440" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G440" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D441" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G441" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D442" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G442" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G356" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D357" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D358" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D359" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D360" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D361" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D362" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D363" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D364" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D365" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D366" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D367" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D368" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D369" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G369" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D370" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D371" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D372" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D373" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G373" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D374" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D375" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D376" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G376" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D377" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D378" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G378" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D379" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D380" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D381" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D382" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D383" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D384" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D385" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D386" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G386" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D387" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G387" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D388" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D389" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D390" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D391" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D392" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D393" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D394" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D395" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G395" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D396" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G396" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D397" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D398" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G398" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D399" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G399" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D400" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G400" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D401" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D402" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D403" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D404" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D405" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D406" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G408" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G409" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G410" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D411" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G411" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D412" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G412" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D413" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G413" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D414" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D415" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G415" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D416" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G416" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D417" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D418" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D419" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D420" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D421" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D422" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D423" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D424" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D425" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D426" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G426" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D427" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G427" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D428" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D429" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D430" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G430" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D431" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G431" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D432" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G432" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D433" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D434" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G434" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D435" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G435" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D436" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G436" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D437" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G437" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D438" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D439" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G439" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D440" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G440" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D441" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G441" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D442" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G442" r:id="rId856"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
